--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -146,6 +146,9 @@
     <t>友方所受伤害减少95%</t>
   </si>
   <si>
+    <t>1918,1918,1918,401,802,134</t>
+  </si>
+  <si>
     <t>14,15,16,10,11</t>
   </si>
   <si>
@@ -239,6 +242,9 @@
     <t>40,40,40,2,8,2</t>
   </si>
   <si>
+    <t>1941,1941,1941,163,597,134</t>
+  </si>
+  <si>
     <t>14,15,16,27,28</t>
   </si>
   <si>
@@ -294,6 +300,9 @@
   </si>
   <si>
     <t>友方闪避概率增加95%</t>
+  </si>
+  <si>
+    <t>1941,1941,1941,1941,1941,134</t>
   </si>
   <si>
     <t>14,15,16,18,20</t>
@@ -1310,7 +1319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC156"/>
+  <dimension ref="A1:AC178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1319,7 +1328,7 @@
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="7.75" style="2" customWidth="1"/>
@@ -1709,27 +1718,27 @@
         <v>27</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q12" si="0">Q6+(F6-E6)*X6+X7</f>
+        <f t="shared" ref="Q7:Q13" si="0">Q6+(F6-E6)*X6+X7</f>
         <v>20</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" ref="R7:R12" si="1">R6+(F6-E6)*Y6+Y7</f>
+        <f t="shared" ref="R7:R13" si="1">R6+(F6-E6)*Y6+Y7</f>
         <v>20</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S12" si="2">S6+(F6-E6)*Z6+Z7</f>
+        <f t="shared" ref="S7:S13" si="2">S6+(F6-E6)*Z6+Z7</f>
         <v>20</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T12" si="3">T6+(F6-E6)*AA6+AA7</f>
+        <f t="shared" ref="T7:T13" si="3">T6+(F6-E6)*AA6+AA7</f>
         <v>15</v>
       </c>
       <c r="U7" s="1">
-        <f t="shared" ref="U7:U12" si="4">U6+(F6-E6)*AB6+AB7</f>
+        <f t="shared" ref="U7:U13" si="4">U6+(F6-E6)*AB6+AB7</f>
         <v>30</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:V12" si="5">V6+(F6-E6)*AC6+AC7</f>
+        <f t="shared" ref="V7:V13" si="5">V6+(F6-E6)*AC6+AC7</f>
         <v>0</v>
       </c>
       <c r="W7" s="7"/>
@@ -1784,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" ref="M8:M12" si="6">M7+(F7-E7)*N7+N8</f>
+        <f t="shared" ref="M8:M13" si="6">M7+(F7-E7)*N7+N8</f>
         <v>120000</v>
       </c>
       <c r="N8" s="1">
@@ -2192,2509 +2201,2046 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C13" s="1">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>121</v>
+      </c>
+      <c r="F13" s="1">
+        <v>135</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>86</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <f t="shared" si="6"/>
+        <v>11060000</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="1">
+        <f t="shared" si="0"/>
+        <v>1918</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="1"/>
+        <v>1918</v>
+      </c>
+      <c r="S13" s="1">
+        <f t="shared" si="2"/>
+        <v>1918</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" si="3"/>
+        <v>401</v>
+      </c>
+      <c r="U13" s="1">
+        <f t="shared" si="4"/>
+        <v>802</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" si="5"/>
+        <v>134</v>
+      </c>
       <c r="W13" s="7"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C14" s="1">
+      <c r="X13" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W14" s="7"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W15" s="7"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W16" s="7"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C17" s="1">
         <v>201</v>
       </c>
-      <c r="D14" s="1">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>9</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="G17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
         <v>3000</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N17" s="1">
         <v>3000</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="O17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W17" s="7"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C18" s="1">
+        <v>202</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1">
+        <v>19</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="Q14" s="1">
-        <v>10</v>
-      </c>
-      <c r="R14" s="1">
-        <v>10</v>
-      </c>
-      <c r="S14" s="1">
-        <v>10</v>
-      </c>
-      <c r="T14" s="1">
-        <v>5</v>
-      </c>
-      <c r="U14" s="1">
-        <v>10</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C15" s="1">
-        <v>202</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1">
-        <v>19</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="1">
-        <v>2</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="J18" s="1">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <v>30000</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N18" s="1">
         <v>30000</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P15" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W15" s="7"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C16" s="1">
+      <c r="P18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C19" s="1">
         <v>203</v>
       </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
         <v>20</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F19" s="1">
         <v>29</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="8" t="s">
+      <c r="G19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="1">
-        <v>2</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
         <v>11</v>
       </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <f t="shared" ref="M16:M19" si="7">M15+(F15-E15)*N15+N16</f>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" ref="M19:M23" si="7">M18+(F18-E18)*N18+N19</f>
         <v>350000</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N19" s="1">
         <v>50000</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P16" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W16" s="7"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C17" s="1">
+      <c r="P19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C20" s="1">
         <v>204</v>
       </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
         <v>30</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F20" s="1">
         <v>49</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="G20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="1">
-        <v>2</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1">
         <v>21</v>
       </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1">
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="7"/>
         <v>900000</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N20" s="1">
         <v>100000</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="O20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C21" s="1">
+        <v>205</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1">
+        <v>79</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1">
         <v>41</v>
       </c>
-      <c r="P17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W17" s="7"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C18" s="1">
-        <v>205</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>50</v>
-      </c>
-      <c r="F18" s="1">
-        <v>79</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2</v>
-      </c>
-      <c r="K18" s="1">
-        <v>41</v>
-      </c>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1">
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="7"/>
         <v>3000000</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N21" s="1">
         <v>200000</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P18" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W18" s="7"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C19" s="1">
+      <c r="P21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C22" s="1">
         <v>206</v>
       </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
         <v>80</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F22" s="1">
         <v>120</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="G22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="1">
-        <v>2</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J22" s="1">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1">
         <v>70</v>
       </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="7"/>
         <v>9200000</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N22" s="1">
         <v>400000</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P19" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W19" s="7"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W20" s="7"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C21" s="1">
-        <v>301</v>
-      </c>
-      <c r="D21" s="1">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>9</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>6000</v>
-      </c>
-      <c r="N21" s="1">
-        <v>6000</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="W21" s="7"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C22" s="1">
-        <v>302</v>
-      </c>
-      <c r="D22" s="1">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>10</v>
-      </c>
-      <c r="F22" s="1">
-        <v>19</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="1">
-        <v>3</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1">
-        <v>60000</v>
-      </c>
-      <c r="N22" s="1">
-        <v>50000</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="P22" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
       <c r="W22" s="7"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C23" s="1">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="D23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="F23" s="1">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>110</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="7"/>
+        <v>27200000</v>
+      </c>
+      <c r="N23" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W24" s="7"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W25" s="7"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W26" s="7"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C27" s="1">
+        <v>301</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>9</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>6000</v>
+      </c>
+      <c r="N27" s="1">
+        <v>6000</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W27" s="7"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C28" s="1">
+        <v>302</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1">
+        <v>19</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="1">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>60000</v>
+      </c>
+      <c r="N28" s="1">
+        <v>50000</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W28" s="7"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C29" s="1">
+        <v>303</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>20</v>
+      </c>
+      <c r="F29" s="1">
+        <v>29</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I29" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J29" s="1">
         <v>3</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K29" s="1">
         <v>11</v>
       </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" ref="M23:M26" si="8">M22+(F22-E22)*N22+N23</f>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" ref="M29:M33" si="8">M28+(F28-E28)*N28+N29</f>
         <v>590000</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N29" s="1">
         <v>80000</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W23" s="7"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C24" s="1">
+      <c r="P29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W29" s="7"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C30" s="1">
         <v>304</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D30" s="1">
         <v>3</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E30" s="1">
         <v>30</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F30" s="1">
         <v>49</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="G30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I30" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J30" s="1">
         <v>3</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K30" s="1">
         <v>21</v>
       </c>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1">
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="8"/>
         <v>1470000</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N30" s="1">
         <v>160000</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P24" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W24" s="7"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C25" s="1">
+      <c r="P30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W30" s="7"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C31" s="1">
         <v>305</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D31" s="1">
         <v>3</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E31" s="1">
         <v>50</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F31" s="1">
         <v>79</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="G31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J31" s="1">
         <v>3</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K31" s="1">
         <v>41</v>
       </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
         <f t="shared" si="8"/>
         <v>4830000</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N31" s="1">
         <v>320000</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W25" s="7"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C26" s="1">
+      <c r="P31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W31" s="7"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C32" s="1">
         <v>306</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D32" s="1">
         <v>3</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E32" s="1">
         <v>80</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F32" s="1">
         <v>120</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="G32" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J32" s="1">
         <v>3</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K32" s="1">
         <v>70</v>
       </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1">
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="8"/>
         <v>14750000</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N32" s="1">
         <v>640000</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P26" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W26" s="7"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W27" s="7"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C28" s="1">
+      <c r="P32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W32" s="7"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C33" s="1">
+        <v>307</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>121</v>
+      </c>
+      <c r="F33" s="1">
+        <v>135</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="1">
+        <v>3</v>
+      </c>
+      <c r="K33" s="1">
+        <v>110</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <f t="shared" si="8"/>
+        <v>43350000</v>
+      </c>
+      <c r="N33" s="1">
+        <v>3000000</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W33" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W34" s="7"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W35" s="7"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W36" s="7"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C37" s="1">
         <v>401</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D37" s="1">
         <v>4</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
         <v>9</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G37" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N37" s="1">
+        <v>10000</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="W37" s="7"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C38" s="1">
+        <v>402</v>
+      </c>
+      <c r="D38" s="1">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1">
+        <v>19</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
+        <v>100000</v>
+      </c>
+      <c r="N38" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="7"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C39" s="1">
+        <v>403</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1">
+        <v>29</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>11</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <f t="shared" ref="M39:M43" si="9">M38+(F38-E38)*N38+N39</f>
+        <v>970000</v>
+      </c>
+      <c r="N39" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W39" s="7"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C40" s="1">
+        <v>404</v>
+      </c>
+      <c r="D40" s="1">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1">
         <v>49</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="G40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" s="1">
         <v>21</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="N28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W28" s="7"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C29" s="1">
-        <v>402</v>
-      </c>
-      <c r="D29" s="1">
-        <v>4</v>
-      </c>
-      <c r="E29" s="1">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1">
-        <v>19</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="1">
-        <v>4</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <v>1</v>
-      </c>
-      <c r="M29" s="1">
-        <v>100000</v>
-      </c>
-      <c r="N29" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W29" s="7"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C30" s="1">
-        <v>403</v>
-      </c>
-      <c r="D30" s="1">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1">
-        <v>20</v>
-      </c>
-      <c r="F30" s="1">
-        <v>29</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="1">
-        <v>4</v>
-      </c>
-      <c r="K30" s="1">
-        <v>11</v>
-      </c>
-      <c r="L30" s="1">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1">
-        <f t="shared" ref="M30:M33" si="9">M29+(F29-E29)*N29+N30</f>
-        <v>970000</v>
-      </c>
-      <c r="N30" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W30" s="7"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C31" s="1">
-        <v>404</v>
-      </c>
-      <c r="D31" s="1">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1">
-        <v>30</v>
-      </c>
-      <c r="F31" s="1">
-        <v>49</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="1">
-        <v>4</v>
-      </c>
-      <c r="K31" s="1">
-        <v>21</v>
-      </c>
-      <c r="L31" s="1">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
         <f t="shared" si="9"/>
         <v>2620000</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N40" s="1">
         <v>300000</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P31" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W31" s="7"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C32" s="1">
+      <c r="P40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W40" s="7"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C41" s="1">
         <v>405</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D41" s="1">
         <v>4</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E41" s="1">
         <v>50</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F41" s="1">
         <v>79</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H32" s="8" t="s">
+      <c r="G41" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H41" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I41" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J41" s="1">
         <v>4</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K41" s="1">
         <v>41</v>
       </c>
-      <c r="L32" s="1">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
         <f t="shared" si="9"/>
         <v>8920000</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N41" s="1">
         <v>600000</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P32" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W32" s="7"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C33" s="1">
+      <c r="P41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W41" s="7"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C42" s="1">
         <v>406</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D42" s="1">
         <v>4</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E42" s="1">
         <v>80</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F42" s="1">
         <v>120</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H33" s="8" t="s">
+      <c r="G42" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I42" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J42" s="1">
         <v>4</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K42" s="1">
         <v>70</v>
       </c>
-      <c r="L33" s="1">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
         <f t="shared" si="9"/>
         <v>27520000</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N42" s="1">
         <v>1200000</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P33" s="1" t="s">
+      <c r="O42" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W33" s="7"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W34" s="7"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C35" s="1">
+      <c r="P42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W42" s="7"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C43" s="1">
+        <v>407</v>
+      </c>
+      <c r="D43" s="1">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1">
+        <v>121</v>
+      </c>
+      <c r="F43" s="1">
+        <v>135</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" s="1">
+        <v>110</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <f t="shared" si="9"/>
+        <v>79520000</v>
+      </c>
+      <c r="N43" s="1">
+        <v>4000000</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W43" s="7"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W44" s="7"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W45" s="7"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W46" s="7"/>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C47" s="1">
         <v>501</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D47" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
         <v>9</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H35" s="8" t="s">
+      <c r="G47" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="H47" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
+      <c r="I47" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
         <v>20000</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N47" s="1">
         <v>20000</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="O47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>15</v>
+      </c>
+      <c r="R47" s="1">
+        <v>15</v>
+      </c>
+      <c r="S47" s="1">
+        <v>15</v>
+      </c>
+      <c r="T47" s="1">
+        <v>1</v>
+      </c>
+      <c r="U47" s="1">
+        <v>15</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="7"/>
+      <c r="X47" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C48" s="1">
+        <v>502</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5</v>
+      </c>
+      <c r="E48" s="1">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1">
+        <v>19</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="Q35" s="1">
-        <v>15</v>
-      </c>
-      <c r="R35" s="1">
-        <v>15</v>
-      </c>
-      <c r="S35" s="1">
-        <v>15</v>
-      </c>
-      <c r="T35" s="1">
-        <v>1</v>
-      </c>
-      <c r="U35" s="1">
-        <v>15</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
-      </c>
-      <c r="W35" s="7"/>
-      <c r="X35" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z35" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C36" s="1">
-        <v>502</v>
-      </c>
-      <c r="D36" s="1">
+      <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="E36" s="1">
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>200000</v>
+      </c>
+      <c r="N48" s="1">
+        <v>150000</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q48" s="1">
+        <f t="shared" ref="Q48:Q53" si="10">Q47+(F47-E47)*X47+X48</f>
+        <v>33</v>
+      </c>
+      <c r="R48" s="1">
+        <f t="shared" ref="R48:R53" si="11">R47+(F47-E47)*Y47+Y48</f>
+        <v>33</v>
+      </c>
+      <c r="S48" s="1">
+        <f t="shared" ref="S48:S53" si="12">S47+(F47-E47)*Z47+Z48</f>
+        <v>33</v>
+      </c>
+      <c r="T48" s="1">
+        <f t="shared" ref="T48:T53" si="13">T47+(F47-E47)*AA47+AA48</f>
         <v>10</v>
       </c>
-      <c r="F36" s="1">
-        <v>19</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="U48" s="1">
+        <f t="shared" ref="U48:U53" si="14">U47+(F47-E47)*AB47+AB48</f>
+        <v>33</v>
+      </c>
+      <c r="V48" s="1">
+        <f t="shared" ref="V48:V53" si="15">V47+(F47-E47)*AC47+AC48</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="7"/>
+      <c r="X48" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C49" s="1">
+        <v>503</v>
+      </c>
+      <c r="D49" s="1">
         <v>5</v>
       </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1">
-        <v>200000</v>
-      </c>
-      <c r="N36" s="1">
-        <v>150000</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P36" s="1" t="s">
+      <c r="E49" s="1">
+        <v>20</v>
+      </c>
+      <c r="F49" s="1">
+        <v>29</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="1">
+        <v>11</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" ref="M49:M53" si="16">M48+(F48-E48)*N48+N49</f>
+        <v>1800000</v>
+      </c>
+      <c r="N49" s="1">
+        <v>250000</v>
+      </c>
+      <c r="O49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q36" s="1">
-        <f t="shared" ref="Q36:Q40" si="10">Q35+(F35-E35)*X35+X36</f>
-        <v>33</v>
-      </c>
-      <c r="R36" s="1">
-        <f t="shared" ref="R36:R40" si="11">R35+(F35-E35)*Y35+Y36</f>
-        <v>33</v>
-      </c>
-      <c r="S36" s="1">
-        <f t="shared" ref="S36:S40" si="12">S35+(F35-E35)*Z35+Z36</f>
-        <v>33</v>
-      </c>
-      <c r="T36" s="1">
-        <f t="shared" ref="T36:T40" si="13">T35+(F35-E35)*AA35+AA36</f>
-        <v>10</v>
-      </c>
-      <c r="U36" s="1">
-        <f t="shared" ref="U36:U40" si="14">U35+(F35-E35)*AB35+AB36</f>
-        <v>33</v>
-      </c>
-      <c r="V36" s="1">
-        <f t="shared" ref="V36:V40" si="15">V35+(F35-E35)*AC35+AC36</f>
-        <v>0</v>
-      </c>
-      <c r="W36" s="7"/>
-      <c r="X36" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C37" s="1">
-        <v>503</v>
-      </c>
-      <c r="D37" s="1">
-        <v>5</v>
-      </c>
-      <c r="E37" s="1">
-        <v>20</v>
-      </c>
-      <c r="F37" s="1">
-        <v>29</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H37" s="9" t="s">
+      <c r="P49" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J37" s="1">
-        <v>5</v>
-      </c>
-      <c r="K37" s="1">
-        <v>11</v>
-      </c>
-      <c r="L37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <f t="shared" ref="M37:M40" si="16">M36+(F36-E36)*N36+N37</f>
-        <v>1800000</v>
-      </c>
-      <c r="N37" s="1">
-        <v>250000</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q37" s="1">
+      <c r="Q49" s="1">
         <f t="shared" si="10"/>
         <v>54</v>
       </c>
-      <c r="R37" s="1">
+      <c r="R49" s="1">
         <f t="shared" si="11"/>
         <v>54</v>
       </c>
-      <c r="S37" s="1">
+      <c r="S49" s="1">
         <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="T37" s="1">
+      <c r="T49" s="1">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U49" s="1">
         <f t="shared" si="14"/>
         <v>54</v>
       </c>
-      <c r="V37" s="1">
+      <c r="V49" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="W37" s="7"/>
-      <c r="X37" s="1">
+      <c r="W49" s="7"/>
+      <c r="X49" s="1">
         <v>3</v>
       </c>
-      <c r="Y37" s="1">
+      <c r="Y49" s="1">
         <v>3</v>
       </c>
-      <c r="Z37" s="1">
+      <c r="Z49" s="1">
         <v>3</v>
       </c>
-      <c r="AA37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="1">
+      <c r="AA49" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="1">
         <v>3</v>
       </c>
-      <c r="AC37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C38" s="1">
+      <c r="AC49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C50" s="1">
         <v>504</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D50" s="1">
         <v>5</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E50" s="1">
         <v>30</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F50" s="1">
         <v>49</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="9" t="s">
+      <c r="G50" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="H50" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="J38" s="1">
+      <c r="I50" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J50" s="1">
         <v>5</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K50" s="1">
         <v>21</v>
       </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1">
         <f t="shared" si="16"/>
         <v>4550000</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N50" s="1">
         <v>500000</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P38" s="1" t="s">
+      <c r="O50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="P50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q50" s="1">
         <f t="shared" si="10"/>
         <v>84</v>
       </c>
-      <c r="R38" s="1">
+      <c r="R50" s="1">
         <f t="shared" si="11"/>
         <v>84</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S50" s="1">
         <f t="shared" si="12"/>
         <v>84</v>
       </c>
-      <c r="T38" s="1">
+      <c r="T50" s="1">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U50" s="1">
         <f t="shared" si="14"/>
         <v>84</v>
       </c>
-      <c r="V38" s="1">
+      <c r="V50" s="1">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="W38" s="7"/>
-      <c r="X38" s="1">
+      <c r="W50" s="7"/>
+      <c r="X50" s="1">
         <v>3</v>
       </c>
-      <c r="Y38" s="1">
+      <c r="Y50" s="1">
         <v>3</v>
       </c>
-      <c r="Z38" s="1">
+      <c r="Z50" s="1">
         <v>3</v>
       </c>
-      <c r="AA38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="1">
+      <c r="AA50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="1">
         <v>3</v>
       </c>
-      <c r="AC38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C39" s="1">
+      <c r="AC50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C51" s="1">
         <v>505</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D51" s="1">
         <v>5</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E51" s="1">
         <v>50</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F51" s="1">
         <v>79</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I39" s="8" t="s">
+      <c r="G51" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J39" s="1">
+      <c r="I51" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J51" s="1">
         <v>5</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K51" s="1">
         <v>41</v>
       </c>
-      <c r="L39" s="1">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1">
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
         <f t="shared" si="16"/>
         <v>15050000</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N51" s="1">
         <v>1000000</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P39" s="1" t="s">
+      <c r="O51" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="P51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q51" s="1">
         <f t="shared" si="10"/>
         <v>145</v>
       </c>
-      <c r="R39" s="1">
+      <c r="R51" s="1">
         <f t="shared" si="11"/>
         <v>145</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S51" s="1">
         <f t="shared" si="12"/>
         <v>145</v>
       </c>
-      <c r="T39" s="1">
+      <c r="T51" s="1">
         <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U51" s="1">
         <f t="shared" si="14"/>
         <v>145</v>
       </c>
-      <c r="V39" s="1">
+      <c r="V51" s="1">
         <f t="shared" si="15"/>
         <v>21</v>
       </c>
-      <c r="W39" s="7"/>
-      <c r="X39" s="1">
+      <c r="W51" s="7"/>
+      <c r="X51" s="1">
         <v>4</v>
       </c>
-      <c r="Y39" s="1">
+      <c r="Y51" s="1">
         <v>4</v>
       </c>
-      <c r="Z39" s="1">
+      <c r="Z51" s="1">
         <v>4</v>
       </c>
-      <c r="AA39" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="1">
+      <c r="AA51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="1">
         <v>4</v>
       </c>
-      <c r="AC39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C40" s="1">
+      <c r="AC51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C52" s="1">
         <v>506</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D52" s="1">
         <v>5</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E52" s="1">
         <v>80</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F52" s="1">
         <v>120</v>
       </c>
-      <c r="G40" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I40" s="8" t="s">
+      <c r="G52" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="J40" s="1">
+      <c r="I52" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J52" s="1">
         <v>5</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K52" s="1">
         <v>70</v>
       </c>
-      <c r="L40" s="1">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1">
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
         <f t="shared" si="16"/>
         <v>45050000</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N52" s="1">
         <v>1000000</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P40" s="1" t="s">
+      <c r="O52" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="P52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q52" s="1">
         <f t="shared" si="10"/>
         <v>301</v>
       </c>
-      <c r="R40" s="1">
+      <c r="R52" s="1">
         <f t="shared" si="11"/>
         <v>301</v>
       </c>
-      <c r="S40" s="1">
+      <c r="S52" s="1">
         <f t="shared" si="12"/>
         <v>301</v>
       </c>
-      <c r="T40" s="1">
+      <c r="T52" s="1">
         <f t="shared" si="13"/>
         <v>81</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U52" s="1">
         <f t="shared" si="14"/>
         <v>269</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V52" s="1">
         <f t="shared" si="15"/>
         <v>52</v>
       </c>
-      <c r="W40" s="7"/>
-      <c r="X40" s="1">
+      <c r="W52" s="7"/>
+      <c r="X52" s="1">
         <v>40</v>
       </c>
-      <c r="Y40" s="1">
+      <c r="Y52" s="1">
         <v>40</v>
       </c>
-      <c r="Z40" s="1">
+      <c r="Z52" s="1">
         <v>40</v>
       </c>
-      <c r="AA40" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB40" s="1">
+      <c r="AA52" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB52" s="1">
         <v>8</v>
       </c>
-      <c r="AC40" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W41" s="7"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C42" s="1">
+      <c r="AC52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C53" s="1">
+        <v>507</v>
+      </c>
+      <c r="D53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="1">
+        <v>121</v>
+      </c>
+      <c r="F53" s="1">
+        <v>135</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J53" s="1">
+        <v>5</v>
+      </c>
+      <c r="K53" s="1">
+        <v>110</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1">
+        <f t="shared" si="16"/>
+        <v>90050000</v>
+      </c>
+      <c r="N53" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q53" s="1">
+        <f t="shared" si="10"/>
+        <v>1941</v>
+      </c>
+      <c r="R53" s="1">
+        <f t="shared" si="11"/>
+        <v>1941</v>
+      </c>
+      <c r="S53" s="1">
+        <f t="shared" si="12"/>
+        <v>1941</v>
+      </c>
+      <c r="T53" s="1">
+        <f t="shared" si="13"/>
+        <v>163</v>
+      </c>
+      <c r="U53" s="1">
+        <f t="shared" si="14"/>
+        <v>597</v>
+      </c>
+      <c r="V53" s="1">
+        <f t="shared" si="15"/>
+        <v>134</v>
+      </c>
+      <c r="W53" s="7"/>
+      <c r="X53" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA53" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB53" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W54" s="7"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W55" s="7"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="W56" s="7"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C57" s="1">
         <v>601</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D57" s="1">
         <v>6</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1">
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
         <v>9</v>
       </c>
-      <c r="G42" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
+      <c r="H57" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
         <v>40000</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N57" s="1">
         <v>40000</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q42" s="1">
+      <c r="O57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q57" s="1">
         <v>15</v>
       </c>
-      <c r="R42" s="1">
+      <c r="R57" s="1">
         <v>15</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S57" s="1">
         <v>15</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T57" s="1">
         <v>15</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U57" s="1">
         <v>15</v>
       </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="7"/>
-      <c r="X42" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C43" s="1">
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="7"/>
+      <c r="X57" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C58" s="1">
         <v>602</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D58" s="1">
         <v>6</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E58" s="1">
         <v>10</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F58" s="1">
         <v>19</v>
       </c>
-      <c r="G43" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="9" t="s">
+      <c r="G58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I58" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="J58" s="1">
+        <v>6</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1">
+        <v>400000</v>
+      </c>
+      <c r="N58" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" ref="Q58:Q64" si="17">Q57+(F57-E57)*X57+X58</f>
+        <v>33</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" ref="R58:R64" si="18">R57+(F57-E57)*Y57+Y58</f>
+        <v>33</v>
+      </c>
+      <c r="S58" s="1">
+        <f t="shared" ref="S58:S64" si="19">S57+(F57-E57)*Z57+Z58</f>
+        <v>33</v>
+      </c>
+      <c r="T58" s="1">
+        <f t="shared" ref="T58:T64" si="20">T57+(F57-E57)*AA57+AA58</f>
+        <v>33</v>
+      </c>
+      <c r="U58" s="1">
+        <f t="shared" ref="U58:U64" si="21">U57+(F57-E57)*AB57+AB58</f>
+        <v>33</v>
+      </c>
+      <c r="V58" s="1">
+        <f t="shared" ref="V58:V64" si="22">V57+(F57-E57)*AC57+AC58</f>
+        <v>0</v>
+      </c>
+      <c r="W58" s="7"/>
+      <c r="X58" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB58" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C59" s="1">
+        <v>603</v>
+      </c>
+      <c r="D59" s="1">
+        <v>6</v>
+      </c>
+      <c r="E59" s="1">
+        <v>20</v>
+      </c>
+      <c r="F59" s="1">
+        <v>29</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J43" s="1">
+      <c r="H59" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J59" s="1">
         <v>6</v>
       </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <v>1</v>
-      </c>
-      <c r="M43" s="1">
+      <c r="K59" s="1">
+        <v>11</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" ref="M59:M64" si="23">M58+(F58-E58)*N58+N59</f>
+        <v>2600000</v>
+      </c>
+      <c r="N59" s="1">
         <v>400000</v>
       </c>
-      <c r="N43" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q43" s="1">
-        <f t="shared" ref="Q43:Q48" si="17">Q42+(F42-E42)*X42+X43</f>
-        <v>33</v>
-      </c>
-      <c r="R43" s="1">
-        <f t="shared" ref="R43:R48" si="18">R42+(F42-E42)*Y42+Y43</f>
-        <v>33</v>
-      </c>
-      <c r="S43" s="1">
-        <f t="shared" ref="S43:S48" si="19">S42+(F42-E42)*Z42+Z43</f>
-        <v>33</v>
-      </c>
-      <c r="T43" s="1">
-        <f t="shared" ref="T43:T48" si="20">T42+(F42-E42)*AA42+AA43</f>
-        <v>33</v>
-      </c>
-      <c r="U43" s="1">
-        <f t="shared" ref="U43:U48" si="21">U42+(F42-E42)*AB42+AB43</f>
-        <v>33</v>
-      </c>
-      <c r="V43" s="1">
-        <f t="shared" ref="V43:V48" si="22">V42+(F42-E42)*AC42+AC43</f>
-        <v>0</v>
-      </c>
-      <c r="W43" s="7"/>
-      <c r="X43" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA43" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB43" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C44" s="1">
-        <v>603</v>
-      </c>
-      <c r="D44" s="1">
-        <v>6</v>
-      </c>
-      <c r="E44" s="1">
-        <v>20</v>
-      </c>
-      <c r="F44" s="1">
-        <v>29</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H44" s="9" t="s">
+      <c r="O59" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="P59" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J44" s="1">
-        <v>6</v>
-      </c>
-      <c r="K44" s="1">
-        <v>11</v>
-      </c>
-      <c r="L44" s="1">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1">
-        <f t="shared" ref="M44:M48" si="23">M43+(F43-E43)*N43+N44</f>
-        <v>2600000</v>
-      </c>
-      <c r="N44" s="1">
-        <v>400000</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q44" s="1">
+      <c r="Q59" s="1">
         <f t="shared" si="17"/>
         <v>54</v>
       </c>
-      <c r="R44" s="1">
+      <c r="R59" s="1">
         <f t="shared" si="18"/>
         <v>54</v>
       </c>
-      <c r="S44" s="1">
+      <c r="S59" s="1">
         <f t="shared" si="19"/>
         <v>54</v>
       </c>
-      <c r="T44" s="1">
+      <c r="T59" s="1">
         <f t="shared" si="20"/>
         <v>54</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U59" s="1">
         <f t="shared" si="21"/>
         <v>54</v>
       </c>
-      <c r="V44" s="1">
+      <c r="V59" s="1">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="7"/>
-      <c r="X44" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C45" s="1">
-        <v>604</v>
-      </c>
-      <c r="D45" s="1">
-        <v>6</v>
-      </c>
-      <c r="E45" s="1">
-        <v>30</v>
-      </c>
-      <c r="F45" s="1">
-        <v>49</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="J45" s="1">
-        <v>6</v>
-      </c>
-      <c r="K45" s="1">
-        <v>21</v>
-      </c>
-      <c r="L45" s="1">
-        <v>1</v>
-      </c>
-      <c r="M45" s="1">
-        <f t="shared" si="23"/>
-        <v>7000000</v>
-      </c>
-      <c r="N45" s="1">
-        <v>800000</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q45" s="1">
-        <f t="shared" si="17"/>
-        <v>84</v>
-      </c>
-      <c r="R45" s="1">
-        <f t="shared" si="18"/>
-        <v>84</v>
-      </c>
-      <c r="S45" s="1">
-        <f t="shared" si="19"/>
-        <v>84</v>
-      </c>
-      <c r="T45" s="1">
-        <f t="shared" si="20"/>
-        <v>84</v>
-      </c>
-      <c r="U45" s="1">
-        <f t="shared" si="21"/>
-        <v>84</v>
-      </c>
-      <c r="V45" s="1">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="W45" s="7"/>
-      <c r="X45" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y45" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C46" s="1">
-        <v>605</v>
-      </c>
-      <c r="D46" s="1">
-        <v>6</v>
-      </c>
-      <c r="E46" s="1">
-        <v>50</v>
-      </c>
-      <c r="F46" s="1">
-        <v>79</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J46" s="1">
-        <v>6</v>
-      </c>
-      <c r="K46" s="1">
-        <v>41</v>
-      </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <f t="shared" si="23"/>
-        <v>23800000</v>
-      </c>
-      <c r="N46" s="2">
-        <v>1600000</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q46" s="1">
-        <f t="shared" si="17"/>
-        <v>145</v>
-      </c>
-      <c r="R46" s="1">
-        <f t="shared" si="18"/>
-        <v>145</v>
-      </c>
-      <c r="S46" s="1">
-        <f t="shared" si="19"/>
-        <v>145</v>
-      </c>
-      <c r="T46" s="1">
-        <f t="shared" si="20"/>
-        <v>145</v>
-      </c>
-      <c r="U46" s="1">
-        <f t="shared" si="21"/>
-        <v>145</v>
-      </c>
-      <c r="V46" s="1">
-        <f t="shared" si="22"/>
-        <v>21</v>
-      </c>
-      <c r="W46" s="7"/>
-      <c r="X46" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>4</v>
-      </c>
-      <c r="AA46" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB46" s="1">
-        <v>4</v>
-      </c>
-      <c r="AC46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C47" s="1">
-        <v>606</v>
-      </c>
-      <c r="D47" s="1">
-        <v>6</v>
-      </c>
-      <c r="E47" s="1">
-        <v>80</v>
-      </c>
-      <c r="F47" s="1">
-        <v>95</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J47" s="1">
-        <v>6</v>
-      </c>
-      <c r="K47" s="1">
-        <v>70</v>
-      </c>
-      <c r="L47" s="1">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1">
-        <f t="shared" si="23"/>
-        <v>73400000</v>
-      </c>
-      <c r="N47" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q47" s="1">
-        <f t="shared" si="17"/>
-        <v>301</v>
-      </c>
-      <c r="R47" s="1">
-        <f t="shared" si="18"/>
-        <v>301</v>
-      </c>
-      <c r="S47" s="1">
-        <f t="shared" si="19"/>
-        <v>301</v>
-      </c>
-      <c r="T47" s="1">
-        <f t="shared" si="20"/>
-        <v>301</v>
-      </c>
-      <c r="U47" s="1">
-        <f t="shared" si="21"/>
-        <v>301</v>
-      </c>
-      <c r="V47" s="1">
-        <f t="shared" si="22"/>
-        <v>52</v>
-      </c>
-      <c r="W47" s="7"/>
-      <c r="X47" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y47" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z47" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA47" s="1">
-        <v>40</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>40</v>
-      </c>
-      <c r="AC47" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C48" s="1">
-        <v>607</v>
-      </c>
-      <c r="D48" s="1">
-        <v>6</v>
-      </c>
-      <c r="E48" s="1">
-        <v>96</v>
-      </c>
-      <c r="F48" s="1">
-        <v>120</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J48" s="1">
-        <v>6</v>
-      </c>
-      <c r="K48" s="1">
-        <v>86</v>
-      </c>
-      <c r="L48" s="1">
-        <v>0</v>
-      </c>
-      <c r="M48" s="1">
-        <f t="shared" si="23"/>
-        <v>124600000</v>
-      </c>
-      <c r="N48" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q48" s="1">
-        <f t="shared" si="17"/>
-        <v>941</v>
-      </c>
-      <c r="R48" s="1">
-        <f t="shared" si="18"/>
-        <v>941</v>
-      </c>
-      <c r="S48" s="1">
-        <f t="shared" si="19"/>
-        <v>941</v>
-      </c>
-      <c r="T48" s="1">
-        <f t="shared" si="20"/>
-        <v>941</v>
-      </c>
-      <c r="U48" s="1">
-        <f t="shared" si="21"/>
-        <v>941</v>
-      </c>
-      <c r="V48" s="1">
-        <f t="shared" si="22"/>
-        <v>84</v>
-      </c>
-      <c r="W48" s="7"/>
-      <c r="X48" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y48" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z48" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA48" s="1">
-        <v>40</v>
-      </c>
-      <c r="AB48" s="1">
-        <v>40</v>
-      </c>
-      <c r="AC48" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="W49" s="7"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C50" s="1">
-        <v>701</v>
-      </c>
-      <c r="D50" s="1">
-        <v>7</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="1">
-        <v>9</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>80000</v>
-      </c>
-      <c r="N50" s="1">
-        <v>80000</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="W50" s="7"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C51" s="1">
-        <v>702</v>
-      </c>
-      <c r="D51" s="1">
-        <v>7</v>
-      </c>
-      <c r="E51" s="1">
-        <v>10</v>
-      </c>
-      <c r="F51" s="1">
-        <v>19</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J51" s="1">
-        <v>7</v>
-      </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
-        <v>1</v>
-      </c>
-      <c r="M51" s="1">
-        <v>800000</v>
-      </c>
-      <c r="N51" s="1">
-        <v>300000</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W51" s="7"/>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C52" s="1">
-        <v>703</v>
-      </c>
-      <c r="D52" s="1">
-        <v>7</v>
-      </c>
-      <c r="E52" s="1">
-        <v>20</v>
-      </c>
-      <c r="F52" s="1">
-        <v>29</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J52" s="1">
-        <v>7</v>
-      </c>
-      <c r="K52" s="1">
-        <v>11</v>
-      </c>
-      <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1">
-        <f t="shared" ref="M52:M55" si="24">M51+(F51-E51)*N51+N52</f>
-        <v>4100000</v>
-      </c>
-      <c r="N52" s="1">
-        <v>600000</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W52" s="7"/>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C53" s="1">
-        <v>704</v>
-      </c>
-      <c r="D53" s="1">
-        <v>7</v>
-      </c>
-      <c r="E53" s="1">
-        <v>30</v>
-      </c>
-      <c r="F53" s="1">
-        <v>49</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="J53" s="1">
-        <v>7</v>
-      </c>
-      <c r="K53" s="1">
-        <v>21</v>
-      </c>
-      <c r="L53" s="1">
-        <v>1</v>
-      </c>
-      <c r="M53" s="1">
-        <f t="shared" si="24"/>
-        <v>10500000</v>
-      </c>
-      <c r="N53" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W53" s="7"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C54" s="1">
-        <v>705</v>
-      </c>
-      <c r="D54" s="1">
-        <v>7</v>
-      </c>
-      <c r="E54" s="1">
-        <v>50</v>
-      </c>
-      <c r="F54" s="1">
-        <v>79</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J54" s="1">
-        <v>7</v>
-      </c>
-      <c r="K54" s="1">
-        <v>41</v>
-      </c>
-      <c r="L54" s="1">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="24"/>
-        <v>31500000</v>
-      </c>
-      <c r="N54" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W54" s="7"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C55" s="1">
-        <v>706</v>
-      </c>
-      <c r="D55" s="1">
-        <v>7</v>
-      </c>
-      <c r="E55" s="1">
-        <v>80</v>
-      </c>
-      <c r="F55" s="1">
-        <v>120</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J55" s="1">
-        <v>7</v>
-      </c>
-      <c r="K55" s="1">
-        <v>70</v>
-      </c>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="24"/>
-        <v>91500000</v>
-      </c>
-      <c r="N55" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="W55" s="7"/>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="8:23">
-      <c r="H56" s="5"/>
-      <c r="W56" s="7"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C57" s="1">
-        <v>801</v>
-      </c>
-      <c r="D57" s="1">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="1">
-        <v>9</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>200000</v>
-      </c>
-      <c r="N57" s="1">
-        <v>200000</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>15</v>
-      </c>
-      <c r="R57" s="1">
-        <v>15</v>
-      </c>
-      <c r="S57" s="1">
-        <v>15</v>
-      </c>
-      <c r="T57" s="1">
-        <v>15</v>
-      </c>
-      <c r="U57" s="1">
-        <v>15</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="7"/>
-      <c r="X57" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C58" s="1">
-        <v>802</v>
-      </c>
-      <c r="D58" s="1">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1">
-        <v>10</v>
-      </c>
-      <c r="F58" s="1">
-        <v>19</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J58" s="1">
-        <v>8</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1</v>
-      </c>
-      <c r="L58" s="1">
-        <v>1</v>
-      </c>
-      <c r="M58" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="N58" s="1">
-        <v>500000</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" ref="Q58:Q63" si="25">Q57+(F57-E57)*X57+X58</f>
-        <v>33</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" ref="R58:R63" si="26">R57+(F57-E57)*Y57+Y58</f>
-        <v>33</v>
-      </c>
-      <c r="S58" s="1">
-        <f t="shared" ref="S58:S63" si="27">S57+(F57-E57)*Z57+Z58</f>
-        <v>33</v>
-      </c>
-      <c r="T58" s="1">
-        <f t="shared" ref="T58:T63" si="28">T57+(F57-E57)*AA57+AA58</f>
-        <v>33</v>
-      </c>
-      <c r="U58" s="1">
-        <f t="shared" ref="U58:U63" si="29">U57+(F57-E57)*AB57+AB58</f>
-        <v>33</v>
-      </c>
-      <c r="V58" s="1">
-        <f t="shared" ref="V58:V63" si="30">V57+(F57-E57)*AC57+AC58</f>
-        <v>0</v>
-      </c>
-      <c r="W58" s="7"/>
-      <c r="X58" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C59" s="1">
-        <v>803</v>
-      </c>
-      <c r="D59" s="1">
-        <v>8</v>
-      </c>
-      <c r="E59" s="1">
-        <v>20</v>
-      </c>
-      <c r="F59" s="1">
-        <v>29</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J59" s="1">
-        <v>8</v>
-      </c>
-      <c r="K59" s="1">
-        <v>11</v>
-      </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="1">
-        <f t="shared" ref="M59:M62" si="31">M58+(F58-E58)*N58+N59</f>
-        <v>7500000</v>
-      </c>
-      <c r="N59" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q59" s="1">
-        <f t="shared" si="25"/>
-        <v>54</v>
-      </c>
-      <c r="R59" s="1">
-        <f t="shared" si="26"/>
-        <v>54</v>
-      </c>
-      <c r="S59" s="1">
-        <f t="shared" si="27"/>
-        <v>54</v>
-      </c>
-      <c r="T59" s="1">
-        <f t="shared" si="28"/>
-        <v>54</v>
-      </c>
-      <c r="U59" s="1">
-        <f t="shared" si="29"/>
-        <v>54</v>
-      </c>
-      <c r="V59" s="1">
-        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W59" s="7"/>
@@ -4719,10 +4265,10 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C60" s="1">
-        <v>804</v>
+        <v>604</v>
       </c>
       <c r="D60" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" s="1">
         <v>30</v>
@@ -4731,16 +4277,16 @@
         <v>49</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J60" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K60" s="1">
         <v>21</v>
@@ -4749,40 +4295,40 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="31"/>
-        <v>18500000</v>
+        <f t="shared" si="23"/>
+        <v>7000000</v>
       </c>
       <c r="N60" s="1">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="Q60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="R60" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="18"/>
         <v>84</v>
       </c>
       <c r="S60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="19"/>
         <v>84</v>
       </c>
       <c r="T60" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="U60" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>84</v>
       </c>
       <c r="V60" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="W60" s="7"/>
@@ -4807,10 +4353,10 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C61" s="1">
-        <v>805</v>
+        <v>605</v>
       </c>
       <c r="D61" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E61" s="1">
         <v>50</v>
@@ -4819,16 +4365,16 @@
         <v>79</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J61" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K61" s="1">
         <v>41</v>
@@ -4837,40 +4383,40 @@
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="31"/>
-        <v>60500000</v>
-      </c>
-      <c r="N61" s="1">
-        <v>4000000</v>
+        <f t="shared" si="23"/>
+        <v>23800000</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1600000</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="Q61" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="17"/>
         <v>145</v>
       </c>
       <c r="R61" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="18"/>
         <v>145</v>
       </c>
       <c r="S61" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="19"/>
         <v>145</v>
       </c>
       <c r="T61" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="20"/>
         <v>145</v>
       </c>
       <c r="U61" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>145</v>
       </c>
       <c r="V61" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>21</v>
       </c>
       <c r="W61" s="7"/>
@@ -4895,28 +4441,28 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C62" s="1">
-        <v>806</v>
+        <v>606</v>
       </c>
       <c r="D62" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E62" s="1">
         <v>80</v>
       </c>
       <c r="F62" s="1">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J62" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K62" s="1">
         <v>70</v>
@@ -4925,40 +4471,40 @@
         <v>1</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="31"/>
-        <v>178500000</v>
-      </c>
-      <c r="N62" s="1">
-        <v>2000000</v>
+        <f t="shared" si="23"/>
+        <v>73400000</v>
+      </c>
+      <c r="N62" s="2">
+        <v>3200000</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="17"/>
         <v>301</v>
       </c>
       <c r="R62" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="18"/>
         <v>301</v>
       </c>
       <c r="S62" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="19"/>
         <v>301</v>
       </c>
       <c r="T62" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="20"/>
         <v>301</v>
       </c>
       <c r="U62" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
         <v>301</v>
       </c>
       <c r="V62" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="22"/>
         <v>52</v>
       </c>
       <c r="W62" s="7"/>
@@ -4981,297 +4527,1187 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="8:23">
-      <c r="H63" s="5"/>
-      <c r="N63" s="2"/>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C63" s="1">
+        <v>607</v>
+      </c>
+      <c r="D63" s="1">
+        <v>6</v>
+      </c>
+      <c r="E63" s="1">
+        <v>96</v>
+      </c>
+      <c r="F63" s="1">
+        <v>120</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J63" s="1">
+        <v>6</v>
+      </c>
+      <c r="K63" s="1">
+        <v>86</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="23"/>
+        <v>124600000</v>
+      </c>
+      <c r="N63" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q63" s="1">
+        <f t="shared" si="17"/>
+        <v>941</v>
+      </c>
+      <c r="R63" s="1">
+        <f t="shared" si="18"/>
+        <v>941</v>
+      </c>
+      <c r="S63" s="1">
+        <f t="shared" si="19"/>
+        <v>941</v>
+      </c>
+      <c r="T63" s="1">
+        <f t="shared" si="20"/>
+        <v>941</v>
+      </c>
+      <c r="U63" s="1">
+        <f t="shared" si="21"/>
+        <v>941</v>
+      </c>
+      <c r="V63" s="1">
+        <f t="shared" si="22"/>
+        <v>84</v>
+      </c>
       <c r="W63" s="7"/>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="X63" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA63" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB63" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C64" s="1">
+        <v>608</v>
+      </c>
+      <c r="D64" s="1">
+        <v>6</v>
+      </c>
+      <c r="E64" s="1">
+        <v>121</v>
+      </c>
+      <c r="F64" s="1">
+        <v>135</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J64" s="1">
+        <v>6</v>
+      </c>
+      <c r="K64" s="1">
+        <v>86</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="23"/>
+        <v>207400000</v>
+      </c>
+      <c r="N64" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q64" s="1">
+        <f t="shared" si="17"/>
+        <v>1941</v>
+      </c>
+      <c r="R64" s="1">
+        <f t="shared" si="18"/>
+        <v>1941</v>
+      </c>
+      <c r="S64" s="1">
+        <f t="shared" si="19"/>
+        <v>1941</v>
+      </c>
+      <c r="T64" s="1">
+        <f t="shared" si="20"/>
+        <v>1941</v>
+      </c>
+      <c r="U64" s="1">
+        <f t="shared" si="21"/>
+        <v>1941</v>
+      </c>
+      <c r="V64" s="1">
+        <f t="shared" si="22"/>
+        <v>134</v>
+      </c>
       <c r="W64" s="7"/>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="23:23">
+      <c r="X64" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z64" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA64" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB64" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
       <c r="W65" s="7"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A66" s="2"/>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="W66" s="7"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A67" s="2"/>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
       <c r="W67" s="7"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A68" s="2"/>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
       <c r="W68" s="7"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C69" s="1">
+        <v>701</v>
+      </c>
+      <c r="D69" s="1">
+        <v>7</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>9</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>80000</v>
+      </c>
+      <c r="N69" s="1">
+        <v>80000</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="W69" s="7"/>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C70" s="1">
+        <v>702</v>
+      </c>
+      <c r="D70" s="1">
+        <v>7</v>
+      </c>
+      <c r="E70" s="1">
+        <v>10</v>
+      </c>
+      <c r="F70" s="1">
+        <v>19</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J70" s="1">
+        <v>7</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <v>800000</v>
+      </c>
+      <c r="N70" s="1">
+        <v>300000</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="W70" s="7"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C71" s="1">
+        <v>703</v>
+      </c>
+      <c r="D71" s="1">
+        <v>7</v>
+      </c>
+      <c r="E71" s="1">
+        <v>20</v>
+      </c>
+      <c r="F71" s="1">
+        <v>29</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J71" s="1">
+        <v>7</v>
+      </c>
+      <c r="K71" s="1">
+        <v>11</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" ref="M71:M75" si="24">M70+(F70-E70)*N70+N71</f>
+        <v>4100000</v>
+      </c>
+      <c r="N71" s="1">
+        <v>600000</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="W71" s="7"/>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C72" s="1">
+        <v>704</v>
+      </c>
+      <c r="D72" s="1">
+        <v>7</v>
+      </c>
+      <c r="E72" s="1">
+        <v>30</v>
+      </c>
+      <c r="F72" s="1">
+        <v>49</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J72" s="1">
+        <v>7</v>
+      </c>
+      <c r="K72" s="1">
+        <v>21</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="24"/>
+        <v>10500000</v>
+      </c>
+      <c r="N72" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="W72" s="7"/>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C73" s="1">
+        <v>705</v>
+      </c>
+      <c r="D73" s="1">
+        <v>7</v>
+      </c>
+      <c r="E73" s="1">
+        <v>50</v>
+      </c>
+      <c r="F73" s="1">
+        <v>79</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J73" s="1">
+        <v>7</v>
+      </c>
+      <c r="K73" s="1">
+        <v>41</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="24"/>
+        <v>31500000</v>
+      </c>
+      <c r="N73" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="W73" s="7"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C74" s="1">
+        <v>706</v>
+      </c>
+      <c r="D74" s="1">
+        <v>7</v>
+      </c>
+      <c r="E74" s="1">
+        <v>80</v>
+      </c>
+      <c r="F74" s="1">
+        <v>120</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J74" s="1">
+        <v>7</v>
+      </c>
+      <c r="K74" s="1">
+        <v>70</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="24"/>
+        <v>93500000</v>
+      </c>
+      <c r="N74" s="1">
+        <v>4000000</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="W74" s="7"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C75" s="1">
+        <v>707</v>
+      </c>
+      <c r="D75" s="1">
+        <v>7</v>
+      </c>
+      <c r="E75" s="1">
+        <v>121</v>
+      </c>
+      <c r="F75" s="1">
+        <v>135</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J75" s="1">
+        <v>7</v>
+      </c>
+      <c r="K75" s="1">
+        <v>110</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="24"/>
+        <v>260500000</v>
+      </c>
+      <c r="N75" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="W75" s="7"/>
     </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="8:23">
+      <c r="H76" s="5"/>
       <c r="N76" s="2"/>
       <c r="W76" s="7"/>
     </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="8:23">
+      <c r="H77" s="5"/>
       <c r="W77" s="7"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="8:23">
+      <c r="H78" s="5"/>
       <c r="W78" s="7"/>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C79" s="1">
+        <v>801</v>
+      </c>
+      <c r="D79" s="1">
+        <v>8</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1">
+        <v>9</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>200000</v>
+      </c>
+      <c r="N79" s="1">
+        <v>200000</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>15</v>
+      </c>
+      <c r="R79" s="1">
+        <v>15</v>
+      </c>
+      <c r="S79" s="1">
+        <v>15</v>
+      </c>
+      <c r="T79" s="1">
+        <v>15</v>
+      </c>
+      <c r="U79" s="1">
+        <v>15</v>
+      </c>
+      <c r="V79" s="1">
+        <v>0</v>
+      </c>
       <c r="W79" s="7"/>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
+      <c r="X79" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z79" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA79" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB79" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C80" s="1">
+        <v>802</v>
+      </c>
+      <c r="D80" s="1">
+        <v>8</v>
+      </c>
+      <c r="E80" s="1">
+        <v>10</v>
+      </c>
+      <c r="F80" s="1">
+        <v>19</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J80" s="1">
+        <v>8</v>
+      </c>
+      <c r="K80" s="1">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1">
+        <v>1</v>
+      </c>
+      <c r="M80" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="N80" s="1">
+        <v>500000</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q80" s="1">
+        <f t="shared" ref="Q80:Q85" si="25">Q79+(F79-E79)*X79+X80</f>
+        <v>33</v>
+      </c>
+      <c r="R80" s="1">
+        <f t="shared" ref="R80:R85" si="26">R79+(F79-E79)*Y79+Y80</f>
+        <v>33</v>
+      </c>
+      <c r="S80" s="1">
+        <f t="shared" ref="S80:S85" si="27">S79+(F79-E79)*Z79+Z80</f>
+        <v>33</v>
+      </c>
+      <c r="T80" s="1">
+        <f t="shared" ref="T80:T85" si="28">T79+(F79-E79)*AA79+AA80</f>
+        <v>33</v>
+      </c>
+      <c r="U80" s="1">
+        <f t="shared" ref="U80:U85" si="29">U79+(F79-E79)*AB79+AB80</f>
+        <v>33</v>
+      </c>
+      <c r="V80" s="1">
+        <f t="shared" ref="V80:V85" si="30">V79+(F79-E79)*AC79+AC80</f>
+        <v>0</v>
+      </c>
       <c r="W80" s="7"/>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
+      <c r="X80" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB80" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C81" s="1">
+        <v>803</v>
+      </c>
+      <c r="D81" s="1">
+        <v>8</v>
+      </c>
+      <c r="E81" s="1">
+        <v>20</v>
+      </c>
+      <c r="F81" s="1">
+        <v>29</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J81" s="1">
+        <v>8</v>
+      </c>
+      <c r="K81" s="1">
+        <v>11</v>
+      </c>
+      <c r="L81" s="1">
+        <v>1</v>
+      </c>
+      <c r="M81" s="1">
+        <f t="shared" ref="M81:M85" si="31">M80+(F80-E80)*N80+N81</f>
+        <v>7500000</v>
+      </c>
+      <c r="N81" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q81" s="1">
+        <f t="shared" si="25"/>
+        <v>54</v>
+      </c>
+      <c r="R81" s="1">
+        <f t="shared" si="26"/>
+        <v>54</v>
+      </c>
+      <c r="S81" s="1">
+        <f t="shared" si="27"/>
+        <v>54</v>
+      </c>
+      <c r="T81" s="1">
+        <f t="shared" si="28"/>
+        <v>54</v>
+      </c>
+      <c r="U81" s="1">
+        <f t="shared" si="29"/>
+        <v>54</v>
+      </c>
+      <c r="V81" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="W81" s="7"/>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
+      <c r="X81" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C82" s="1">
+        <v>804</v>
+      </c>
+      <c r="D82" s="1">
+        <v>8</v>
+      </c>
+      <c r="E82" s="1">
+        <v>30</v>
+      </c>
+      <c r="F82" s="1">
+        <v>49</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J82" s="1">
+        <v>8</v>
+      </c>
+      <c r="K82" s="1">
+        <v>21</v>
+      </c>
+      <c r="L82" s="1">
+        <v>1</v>
+      </c>
+      <c r="M82" s="1">
+        <f t="shared" si="31"/>
+        <v>18500000</v>
+      </c>
+      <c r="N82" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q82" s="1">
+        <f t="shared" si="25"/>
+        <v>84</v>
+      </c>
+      <c r="R82" s="1">
+        <f t="shared" si="26"/>
+        <v>84</v>
+      </c>
+      <c r="S82" s="1">
+        <f t="shared" si="27"/>
+        <v>84</v>
+      </c>
+      <c r="T82" s="1">
+        <f t="shared" si="28"/>
+        <v>84</v>
+      </c>
+      <c r="U82" s="1">
+        <f t="shared" si="29"/>
+        <v>84</v>
+      </c>
+      <c r="V82" s="1">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
       <c r="W82" s="7"/>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
+      <c r="X82" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y82" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z82" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA82" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C83" s="1">
+        <v>805</v>
+      </c>
+      <c r="D83" s="1">
+        <v>8</v>
+      </c>
+      <c r="E83" s="1">
+        <v>50</v>
+      </c>
+      <c r="F83" s="1">
+        <v>79</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J83" s="1">
+        <v>8</v>
+      </c>
+      <c r="K83" s="1">
+        <v>41</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="31"/>
+        <v>60500000</v>
+      </c>
+      <c r="N83" s="1">
+        <v>4000000</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q83" s="1">
+        <f t="shared" si="25"/>
+        <v>145</v>
+      </c>
+      <c r="R83" s="1">
+        <f t="shared" si="26"/>
+        <v>145</v>
+      </c>
+      <c r="S83" s="1">
+        <f t="shared" si="27"/>
+        <v>145</v>
+      </c>
+      <c r="T83" s="1">
+        <f t="shared" si="28"/>
+        <v>145</v>
+      </c>
+      <c r="U83" s="1">
+        <f t="shared" si="29"/>
+        <v>145</v>
+      </c>
+      <c r="V83" s="1">
+        <f t="shared" si="30"/>
+        <v>21</v>
+      </c>
       <c r="W83" s="7"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
+      <c r="X83" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C84" s="1">
+        <v>806</v>
+      </c>
+      <c r="D84" s="1">
+        <v>8</v>
+      </c>
+      <c r="E84" s="1">
+        <v>80</v>
+      </c>
+      <c r="F84" s="1">
+        <v>120</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J84" s="1">
+        <v>8</v>
+      </c>
+      <c r="K84" s="1">
+        <v>70</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1">
+        <f t="shared" si="31"/>
+        <v>182500000</v>
+      </c>
+      <c r="N84" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q84" s="1">
+        <f t="shared" si="25"/>
+        <v>301</v>
+      </c>
+      <c r="R84" s="1">
+        <f t="shared" si="26"/>
+        <v>301</v>
+      </c>
+      <c r="S84" s="1">
+        <f t="shared" si="27"/>
+        <v>301</v>
+      </c>
+      <c r="T84" s="1">
+        <f t="shared" si="28"/>
+        <v>301</v>
+      </c>
+      <c r="U84" s="1">
+        <f t="shared" si="29"/>
+        <v>301</v>
+      </c>
+      <c r="V84" s="1">
+        <f t="shared" si="30"/>
+        <v>52</v>
+      </c>
       <c r="W84" s="7"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
+      <c r="X84" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y84" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z84" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA84" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB84" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C85" s="1">
+        <v>807</v>
+      </c>
+      <c r="D85" s="1">
+        <v>8</v>
+      </c>
+      <c r="E85" s="1">
+        <v>121</v>
+      </c>
+      <c r="F85" s="1">
+        <v>135</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J85" s="1">
+        <v>8</v>
+      </c>
+      <c r="K85" s="1">
+        <v>110</v>
+      </c>
+      <c r="L85" s="1">
+        <v>1</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" si="31"/>
+        <v>430500000</v>
+      </c>
+      <c r="N85" s="1">
+        <v>8000000</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P85" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q85" s="1">
+        <f t="shared" si="25"/>
+        <v>1941</v>
+      </c>
+      <c r="R85" s="1">
+        <f t="shared" si="26"/>
+        <v>1941</v>
+      </c>
+      <c r="S85" s="1">
+        <f t="shared" si="27"/>
+        <v>1941</v>
+      </c>
+      <c r="T85" s="1">
+        <f t="shared" si="28"/>
+        <v>1941</v>
+      </c>
+      <c r="U85" s="1">
+        <f t="shared" si="29"/>
+        <v>1941</v>
+      </c>
+      <c r="V85" s="1">
+        <f t="shared" si="30"/>
+        <v>134</v>
+      </c>
       <c r="W85" s="7"/>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
+      <c r="X85" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y85" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z85" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA85" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB85" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="14:23">
       <c r="N86" s="2"/>
       <c r="W86" s="7"/>
     </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W87" s="7"/>
     </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A88" s="2"/>
       <c r="W88" s="7"/>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
       <c r="W89" s="7"/>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
       <c r="W90" s="7"/>
     </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W91" s="7"/>
     </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W92" s="7"/>
     </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -5282,9 +5718,7 @@
       <c r="N93" s="2"/>
       <c r="W93" s="7"/>
     </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -5295,9 +5729,7 @@
       <c r="N94" s="2"/>
       <c r="W94" s="7"/>
     </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -5308,9 +5740,7 @@
       <c r="N95" s="2"/>
       <c r="W95" s="7"/>
     </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -5321,9 +5751,7 @@
       <c r="N96" s="2"/>
       <c r="W96" s="7"/>
     </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -5334,9 +5762,7 @@
       <c r="N97" s="2"/>
       <c r="W97" s="7"/>
     </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -5347,9 +5773,7 @@
       <c r="N98" s="2"/>
       <c r="W98" s="7"/>
     </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -5360,9 +5784,7 @@
       <c r="N99" s="2"/>
       <c r="W99" s="7"/>
     </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -5373,9 +5795,7 @@
       <c r="N100" s="2"/>
       <c r="W100" s="7"/>
     </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -5386,8 +5806,7 @@
       <c r="N101" s="2"/>
       <c r="W101" s="7"/>
     </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A102" s="2"/>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -5399,8 +5818,7 @@
       <c r="N102" s="2"/>
       <c r="W102" s="7"/>
     </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A103" s="2"/>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5412,8 +5830,7 @@
       <c r="N103" s="2"/>
       <c r="W103" s="7"/>
     </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A104" s="2"/>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5425,8 +5842,7 @@
       <c r="N104" s="2"/>
       <c r="W104" s="7"/>
     </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A105" s="2"/>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5438,8 +5854,7 @@
       <c r="N105" s="2"/>
       <c r="W105" s="7"/>
     </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A106" s="2"/>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5451,8 +5866,7 @@
       <c r="N106" s="2"/>
       <c r="W106" s="7"/>
     </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A107" s="2"/>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5464,8 +5878,7 @@
       <c r="N107" s="2"/>
       <c r="W107" s="7"/>
     </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A108" s="2"/>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -5477,8 +5890,7 @@
       <c r="N108" s="2"/>
       <c r="W108" s="7"/>
     </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A109" s="2"/>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -5490,8 +5902,7 @@
       <c r="N109" s="2"/>
       <c r="W109" s="7"/>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A110" s="2"/>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="2:23">
       <c r="B110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5802,6 +6213,45 @@
       <c r="N133" s="2"/>
       <c r="W133" s="7"/>
     </row>
+    <row r="134" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2"/>
+      <c r="W134" s="7"/>
+    </row>
+    <row r="135" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2"/>
+      <c r="W135" s="7"/>
+    </row>
+    <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2"/>
+      <c r="W136" s="7"/>
+    </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
@@ -6049,18 +6499,265 @@
       <c r="N155" s="2"/>
       <c r="W155" s="7"/>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="2"/>
-      <c r="J156" s="2"/>
-      <c r="K156" s="2"/>
-      <c r="L156" s="2"/>
-      <c r="M156" s="2"/>
-      <c r="N156" s="2"/>
-      <c r="W156" s="7"/>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
+      <c r="M159" s="2"/>
+      <c r="N159" s="2"/>
+      <c r="W159" s="7"/>
+    </row>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
+      <c r="M160" s="2"/>
+      <c r="N160" s="2"/>
+      <c r="W160" s="7"/>
+    </row>
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+      <c r="M161" s="2"/>
+      <c r="N161" s="2"/>
+      <c r="W161" s="7"/>
+    </row>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
+      <c r="M162" s="2"/>
+      <c r="N162" s="2"/>
+      <c r="W162" s="7"/>
+    </row>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+      <c r="M163" s="2"/>
+      <c r="N163" s="2"/>
+      <c r="W163" s="7"/>
+    </row>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+      <c r="M164" s="2"/>
+      <c r="N164" s="2"/>
+      <c r="W164" s="7"/>
+    </row>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+      <c r="M165" s="2"/>
+      <c r="N165" s="2"/>
+      <c r="W165" s="7"/>
+    </row>
+    <row r="166" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
+      <c r="M166" s="2"/>
+      <c r="N166" s="2"/>
+      <c r="W166" s="7"/>
+    </row>
+    <row r="167" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
+      <c r="M167" s="2"/>
+      <c r="N167" s="2"/>
+      <c r="W167" s="7"/>
+    </row>
+    <row r="168" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2"/>
+      <c r="W168" s="7"/>
+    </row>
+    <row r="169" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
+      <c r="M169" s="2"/>
+      <c r="N169" s="2"/>
+      <c r="W169" s="7"/>
+    </row>
+    <row r="170" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+      <c r="N170" s="2"/>
+      <c r="W170" s="7"/>
+    </row>
+    <row r="171" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2"/>
+      <c r="W171" s="7"/>
+    </row>
+    <row r="172" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
+      <c r="M172" s="2"/>
+      <c r="N172" s="2"/>
+      <c r="W172" s="7"/>
+    </row>
+    <row r="173" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
+      <c r="M173" s="2"/>
+      <c r="N173" s="2"/>
+      <c r="W173" s="7"/>
+    </row>
+    <row r="174" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+      <c r="N174" s="2"/>
+      <c r="W174" s="7"/>
+    </row>
+    <row r="175" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
+      <c r="M175" s="2"/>
+      <c r="N175" s="2"/>
+      <c r="W175" s="7"/>
+    </row>
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
+      <c r="M176" s="2"/>
+      <c r="N176" s="2"/>
+      <c r="W176" s="7"/>
+    </row>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
+      <c r="M177" s="2"/>
+      <c r="N177" s="2"/>
+      <c r="W177" s="7"/>
+    </row>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
+      <c r="M178" s="2"/>
+      <c r="N178" s="2"/>
+      <c r="W178" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -294,12 +294,6 @@
   </si>
   <si>
     <t>941,941,941,941,941,84</t>
-  </si>
-  <si>
-    <t>闪避光环(满级)</t>
-  </si>
-  <si>
-    <t>友方闪避概率增加95%</t>
   </si>
   <si>
     <t>1941,1941,1941,1941,1941,134</t>
@@ -2339,9 +2333,6 @@
         <v>41</v>
       </c>
       <c r="W17" s="7"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
       <c r="AA17" s="1">
         <v>1</v>
       </c>
@@ -2395,16 +2386,7 @@
       <c r="P18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
       <c r="W18" s="7"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
       <c r="AA18" s="1">
         <v>2</v>
       </c>
@@ -2459,16 +2441,7 @@
       <c r="P19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
       <c r="W19" s="7"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
       <c r="AA19" s="1">
         <v>2</v>
       </c>
@@ -2523,16 +2496,7 @@
       <c r="P20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
       <c r="W20" s="7"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
       <c r="AA20" s="1">
         <v>3</v>
       </c>
@@ -2587,16 +2551,7 @@
       <c r="P21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
       <c r="AA21" s="1">
         <v>4</v>
       </c>
@@ -2651,16 +2606,7 @@
       <c r="P22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
       <c r="AA22" s="1">
         <v>4</v>
       </c>
@@ -2697,7 +2643,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L23" s="1">
         <v>1</v>
@@ -2715,16 +2661,7 @@
       <c r="P23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
       <c r="W23" s="7"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
       <c r="AA23" s="1">
         <v>4</v>
       </c>
@@ -3041,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
@@ -3367,7 +3304,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L43" s="1">
         <v>1</v>
@@ -3939,7 +3876,7 @@
         <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
@@ -4556,7 +4493,7 @@
         <v>86</v>
       </c>
       <c r="L63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="1">
         <f t="shared" si="23"/>
@@ -4566,10 +4503,10 @@
         <v>3200000</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="Q63" s="1">
         <f t="shared" si="17"/>
@@ -4632,7 +4569,7 @@
         <v>81</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>87</v>
@@ -4641,10 +4578,10 @@
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="L64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="1">
         <f t="shared" si="23"/>
@@ -4654,10 +4591,10 @@
         <v>6000000</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="Q64" s="1">
         <f t="shared" si="17"/>
@@ -4761,7 +4698,7 @@
         <v>9</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>73</v>
@@ -4785,7 +4722,7 @@
         <v>80000</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="W69" s="7"/>
     </row>
@@ -4803,7 +4740,7 @@
         <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>76</v>
@@ -4827,10 +4764,10 @@
         <v>300000</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W70" s="7"/>
     </row>
@@ -4848,7 +4785,7 @@
         <v>29</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>79</v>
@@ -4873,10 +4810,10 @@
         <v>600000</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W71" s="7"/>
     </row>
@@ -4894,7 +4831,7 @@
         <v>49</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>82</v>
@@ -4919,10 +4856,10 @@
         <v>1000000</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W72" s="7"/>
     </row>
@@ -4940,7 +4877,7 @@
         <v>79</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H73" s="9" t="s">
         <v>84</v>
@@ -4965,10 +4902,10 @@
         <v>2000000</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W73" s="7"/>
     </row>
@@ -4986,7 +4923,7 @@
         <v>120</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>86</v>
@@ -5011,10 +4948,10 @@
         <v>4000000</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="W74" s="7"/>
     </row>
@@ -5032,10 +4969,10 @@
         <v>135</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>87</v>
@@ -5044,7 +4981,7 @@
         <v>7</v>
       </c>
       <c r="K75" s="1">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -5057,10 +4994,10 @@
         <v>7000000</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="W75" s="7"/>
     </row>
@@ -5091,7 +5028,7 @@
         <v>9</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H79" s="8" t="s">
         <v>73</v>
@@ -5115,7 +5052,7 @@
         <v>200000</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q79" s="1">
         <v>15</v>
@@ -5169,7 +5106,7 @@
         <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>76</v>
@@ -5193,10 +5130,10 @@
         <v>500000</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q80" s="1">
         <f t="shared" ref="Q80:Q85" si="25">Q79+(F79-E79)*X79+X80</f>
@@ -5256,7 +5193,7 @@
         <v>29</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>79</v>
@@ -5281,10 +5218,10 @@
         <v>1000000</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q81" s="1">
         <f t="shared" si="25"/>
@@ -5344,7 +5281,7 @@
         <v>49</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>82</v>
@@ -5369,10 +5306,10 @@
         <v>2000000</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q82" s="1">
         <f t="shared" si="25"/>
@@ -5432,7 +5369,7 @@
         <v>79</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H83" s="9" t="s">
         <v>84</v>
@@ -5457,10 +5394,10 @@
         <v>4000000</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q83" s="1">
         <f t="shared" si="25"/>
@@ -5520,7 +5457,7 @@
         <v>120</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>86</v>
@@ -5545,10 +5482,10 @@
         <v>6000000</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q84" s="1">
         <f t="shared" si="25"/>
@@ -5608,10 +5545,10 @@
         <v>135</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>87</v>
@@ -5620,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="K85" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L85" s="1">
         <v>1</v>
@@ -5633,10 +5570,10 @@
         <v>8000000</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q85" s="1">
         <f t="shared" si="25"/>

--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2206,7 +2206,7 @@
         <v>121</v>
       </c>
       <c r="F13" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>29</v>
@@ -2628,7 +2628,7 @@
         <v>121</v>
       </c>
       <c r="F23" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>44</v>
@@ -2963,7 +2963,7 @@
         <v>121</v>
       </c>
       <c r="F33" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>49</v>
@@ -3289,7 +3289,7 @@
         <v>121</v>
       </c>
       <c r="F43" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>54</v>
@@ -3861,7 +3861,7 @@
         <v>121</v>
       </c>
       <c r="F53" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>64</v>
@@ -4563,7 +4563,7 @@
         <v>121</v>
       </c>
       <c r="F64" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>81</v>
@@ -4966,7 +4966,7 @@
         <v>121</v>
       </c>
       <c r="F75" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>94</v>
@@ -5542,7 +5542,7 @@
         <v>121</v>
       </c>
       <c r="F85" s="1">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>100</v>

--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -149,6 +149,15 @@
     <t>1918,1918,1918,401,802,134</t>
   </si>
   <si>
+    <t>14,15,16,8,9,33,2007</t>
+  </si>
+  <si>
+    <t>3118,3188,3118,521,1042,194,2</t>
+  </si>
+  <si>
+    <t>80,80,80,8,16,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,10,11</t>
   </si>
   <si>
@@ -164,6 +173,9 @@
     <t>14,15,16,10,11,34</t>
   </si>
   <si>
+    <t>14,15,16,10,11,34,2008</t>
+  </si>
+  <si>
     <t>14,15,16,12,19</t>
   </si>
   <si>
@@ -179,6 +191,9 @@
     <t>14,15,16,12,19,35</t>
   </si>
   <si>
+    <t>14,15,16,12,19,35,2009</t>
+  </si>
+  <si>
     <t>14,15,16,13,24</t>
   </si>
   <si>
@@ -194,6 +209,9 @@
     <t>14,15,16,13,24,2003</t>
   </si>
   <si>
+    <t>14,15,16,13,24,2003,2002</t>
+  </si>
+  <si>
     <t>14,15,16,7,26</t>
   </si>
   <si>
@@ -245,6 +263,15 @@
     <t>1941,1941,1941,163,597,134</t>
   </si>
   <si>
+    <t>14,15,16,7,26,2002,2012</t>
+  </si>
+  <si>
+    <t>3141,3141,3141,223,837,194,2</t>
+  </si>
+  <si>
+    <t>80,80,80,4,16,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,27,28</t>
   </si>
   <si>
@@ -299,6 +326,15 @@
     <t>1941,1941,1941,1941,1941,134</t>
   </si>
   <si>
+    <t>14,15,16,27,28,2004,2003</t>
+  </si>
+  <si>
+    <t>3141,3141,3141,3141,3141,194,2</t>
+  </si>
+  <si>
+    <t>80,80,80,80,80,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,18,20</t>
   </si>
   <si>
@@ -320,6 +356,9 @@
     <t>友方减伤倍率增加70%</t>
   </si>
   <si>
+    <t>14,15,16,18,20,2005,2010</t>
+  </si>
+  <si>
     <t>10级解锁命中光环</t>
   </si>
   <si>
@@ -330,6 +369,9 @@
   </si>
   <si>
     <t>14,15,16,18,20,2006</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,2006,2001</t>
   </si>
 </sst>
 </file>
@@ -1316,31 +1358,31 @@
   <dimension ref="A1:AC178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.8761061946903" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3893805309735" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.3451327433628" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.8141592920354" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.6283185840708" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.75221238938053" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.50442477876106" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.3716814159292" style="2" customWidth="1"/>
     <col min="14" max="14" width="9" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
-    <col min="19" max="22" width="4.375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="4.375" style="3" customWidth="1"/>
-    <col min="24" max="24" width="5.125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="4.375" style="2" customWidth="1"/>
-    <col min="26" max="26" width="5.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5044247787611" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.24778761061947" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.12389380530973" style="2" customWidth="1"/>
+    <col min="19" max="22" width="4.3716814159292" style="2" customWidth="1"/>
+    <col min="23" max="23" width="4.3716814159292" style="3" customWidth="1"/>
+    <col min="24" max="24" width="5.12389380530973" style="2" customWidth="1"/>
+    <col min="25" max="25" width="4.3716814159292" style="2" customWidth="1"/>
+    <col min="26" max="26" width="5.24778761061947" style="2" customWidth="1"/>
     <col min="27" max="27" width="5" style="2" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="2" customWidth="1"/>
-    <col min="29" max="29" width="6.125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="5.6283185840708" style="2" customWidth="1"/>
+    <col min="29" max="29" width="6.12389380530973" style="2" customWidth="1"/>
     <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1712,27 +1754,27 @@
         <v>27</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q13" si="0">Q6+(F6-E6)*X6+X7</f>
+        <f t="shared" ref="Q7:Q14" si="0">Q6+(F6-E6)*X6+X7</f>
         <v>20</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" ref="R7:R13" si="1">R6+(F6-E6)*Y6+Y7</f>
+        <f t="shared" ref="R7:R14" si="1">R6+(F6-E6)*Y6+Y7</f>
         <v>20</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S13" si="2">S6+(F6-E6)*Z6+Z7</f>
+        <f t="shared" ref="S7:S14" si="2">S6+(F6-E6)*Z6+Z7</f>
         <v>20</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T13" si="3">T6+(F6-E6)*AA6+AA7</f>
+        <f t="shared" ref="T7:T14" si="3">T6+(F6-E6)*AA6+AA7</f>
         <v>15</v>
       </c>
       <c r="U7" s="1">
-        <f t="shared" ref="U7:U13" si="4">U6+(F6-E6)*AB6+AB7</f>
+        <f t="shared" ref="U7:U14" si="4">U6+(F6-E6)*AB6+AB7</f>
         <v>30</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:V13" si="5">V6+(F6-E6)*AC6+AC7</f>
+        <f t="shared" ref="V7:V14" si="5">V6+(F6-E6)*AC6+AC7</f>
         <v>0</v>
       </c>
       <c r="W7" s="7"/>
@@ -1787,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" ref="M8:M13" si="6">M7+(F7-E7)*N7+N8</f>
+        <f t="shared" ref="M8:M14" si="6">M7+(F7-E7)*N7+N8</f>
         <v>120000</v>
       </c>
       <c r="N8" s="1">
@@ -2283,8 +2325,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C14" s="1">
+        <v>109</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>151</v>
+      </c>
+      <c r="F14" s="1">
+        <v>200</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>86</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" si="6"/>
+        <v>50060000</v>
+      </c>
+      <c r="N14" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="1">
+        <f t="shared" si="0"/>
+        <v>3118</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="1"/>
+        <v>3118</v>
+      </c>
+      <c r="S14" s="1">
+        <f t="shared" si="2"/>
+        <v>3118</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" si="3"/>
+        <v>521</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" si="4"/>
+        <v>1042</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" si="5"/>
+        <v>194</v>
+      </c>
       <c r="W14" s="7"/>
+      <c r="X14" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W15" s="7"/>
@@ -2306,7 +2433,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>21</v>
@@ -2330,7 +2457,7 @@
         <v>3000</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="W17" s="7"/>
       <c r="AA17" s="1">
@@ -2357,7 +2484,7 @@
         <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>24</v>
@@ -2381,10 +2508,10 @@
         <v>30000</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W18" s="7"/>
       <c r="AA18" s="1">
@@ -2411,7 +2538,7 @@
         <v>29</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>28</v>
@@ -2429,17 +2556,17 @@
         <v>1</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" ref="M19:M23" si="7">M18+(F18-E18)*N18+N19</f>
+        <f t="shared" ref="M19:M24" si="7">M18+(F18-E18)*N18+N19</f>
         <v>350000</v>
       </c>
       <c r="N19" s="1">
         <v>50000</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W19" s="7"/>
       <c r="AA19" s="1">
@@ -2466,7 +2593,7 @@
         <v>49</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>30</v>
@@ -2491,10 +2618,10 @@
         <v>100000</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W20" s="7"/>
       <c r="AA20" s="1">
@@ -2521,7 +2648,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>32</v>
@@ -2546,10 +2673,10 @@
         <v>200000</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W21" s="7"/>
       <c r="AA21" s="1">
@@ -2576,7 +2703,7 @@
         <v>120</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>34</v>
@@ -2601,10 +2728,10 @@
         <v>400000</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W22" s="7"/>
       <c r="AA22" s="1">
@@ -2631,7 +2758,7 @@
         <v>150</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>39</v>
@@ -2656,10 +2783,10 @@
         <v>2000000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W23" s="7"/>
       <c r="AA23" s="1">
@@ -2672,8 +2799,60 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C24" s="1">
+        <v>208</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>151</v>
+      </c>
+      <c r="F24" s="1">
+        <v>200</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>141</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="7"/>
+        <v>96200000</v>
+      </c>
+      <c r="N24" s="1">
+        <v>11000000</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="W24" s="7"/>
+      <c r="AA24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W25" s="7"/>
@@ -2695,7 +2874,7 @@
         <v>9</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>21</v>
@@ -2719,7 +2898,7 @@
         <v>6000</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="W27" s="7"/>
     </row>
@@ -2737,7 +2916,7 @@
         <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>24</v>
@@ -2761,10 +2940,10 @@
         <v>50000</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W28" s="7"/>
     </row>
@@ -2782,7 +2961,7 @@
         <v>29</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>28</v>
@@ -2800,17 +2979,17 @@
         <v>1</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" ref="M29:M33" si="8">M28+(F28-E28)*N28+N29</f>
+        <f t="shared" ref="M29:M34" si="8">M28+(F28-E28)*N28+N29</f>
         <v>590000</v>
       </c>
       <c r="N29" s="1">
         <v>80000</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W29" s="7"/>
     </row>
@@ -2828,7 +3007,7 @@
         <v>49</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>30</v>
@@ -2853,10 +3032,10 @@
         <v>160000</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W30" s="7"/>
     </row>
@@ -2874,7 +3053,7 @@
         <v>79</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>32</v>
@@ -2899,10 +3078,10 @@
         <v>320000</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W31" s="7"/>
     </row>
@@ -2920,7 +3099,7 @@
         <v>120</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>34</v>
@@ -2945,10 +3124,10 @@
         <v>640000</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W32" s="7"/>
     </row>
@@ -2966,7 +3145,7 @@
         <v>150</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>39</v>
@@ -2991,14 +3170,57 @@
         <v>3000000</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W33" s="7"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C34" s="1">
+        <v>308</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>151</v>
+      </c>
+      <c r="F34" s="1">
+        <v>200</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="1">
+        <v>3</v>
+      </c>
+      <c r="K34" s="1">
+        <v>141</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1">
+        <f t="shared" si="8"/>
+        <v>142350000</v>
+      </c>
+      <c r="N34" s="1">
+        <v>12000000</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="W34" s="7"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="23:23">
@@ -3021,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>21</v>
@@ -3045,7 +3267,7 @@
         <v>10000</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="W37" s="7"/>
     </row>
@@ -3063,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>24</v>
@@ -3087,10 +3309,10 @@
         <v>80000</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W38" s="7"/>
     </row>
@@ -3108,7 +3330,7 @@
         <v>29</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>28</v>
@@ -3126,17 +3348,17 @@
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" ref="M39:M43" si="9">M38+(F38-E38)*N38+N39</f>
+        <f t="shared" ref="M39:M44" si="9">M38+(F38-E38)*N38+N39</f>
         <v>970000</v>
       </c>
       <c r="N39" s="1">
         <v>150000</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W39" s="7"/>
     </row>
@@ -3154,7 +3376,7 @@
         <v>49</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3179,10 +3401,10 @@
         <v>300000</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W40" s="7"/>
     </row>
@@ -3200,7 +3422,7 @@
         <v>79</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>32</v>
@@ -3225,10 +3447,10 @@
         <v>600000</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W41" s="7"/>
     </row>
@@ -3246,7 +3468,7 @@
         <v>120</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>34</v>
@@ -3271,10 +3493,10 @@
         <v>1200000</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W42" s="7"/>
     </row>
@@ -3292,7 +3514,7 @@
         <v>150</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>39</v>
@@ -3317,14 +3539,57 @@
         <v>4000000</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W43" s="7"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C44" s="1">
+        <v>408</v>
+      </c>
+      <c r="D44" s="1">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1">
+        <v>151</v>
+      </c>
+      <c r="F44" s="1">
+        <v>200</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="1">
+        <v>141</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <f t="shared" si="9"/>
+        <v>208520000</v>
+      </c>
+      <c r="N44" s="1">
+        <v>13000000</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="W44" s="7"/>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="23:23">
@@ -3347,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J47" s="1">
         <v>0</v>
@@ -3371,7 +3636,7 @@
         <v>20000</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q47" s="1">
         <v>15</v>
@@ -3425,13 +3690,13 @@
         <v>19</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J48" s="1">
         <v>5</v>
@@ -3449,33 +3714,33 @@
         <v>150000</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" ref="Q48:Q53" si="10">Q47+(F47-E47)*X47+X48</f>
+        <f t="shared" ref="Q48:Q54" si="10">Q47+(F47-E47)*X47+X48</f>
         <v>33</v>
       </c>
       <c r="R48" s="1">
-        <f t="shared" ref="R48:R53" si="11">R47+(F47-E47)*Y47+Y48</f>
+        <f t="shared" ref="R48:R54" si="11">R47+(F47-E47)*Y47+Y48</f>
         <v>33</v>
       </c>
       <c r="S48" s="1">
-        <f t="shared" ref="S48:S53" si="12">S47+(F47-E47)*Z47+Z48</f>
+        <f t="shared" ref="S48:S54" si="12">S47+(F47-E47)*Z47+Z48</f>
         <v>33</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" ref="T48:T53" si="13">T47+(F47-E47)*AA47+AA48</f>
+        <f t="shared" ref="T48:T54" si="13">T47+(F47-E47)*AA47+AA48</f>
         <v>10</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" ref="U48:U53" si="14">U47+(F47-E47)*AB47+AB48</f>
+        <f t="shared" ref="U48:U54" si="14">U47+(F47-E47)*AB47+AB48</f>
         <v>33</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" ref="V48:V53" si="15">V47+(F47-E47)*AC47+AC48</f>
+        <f t="shared" ref="V48:V54" si="15">V47+(F47-E47)*AC47+AC48</f>
         <v>0</v>
       </c>
       <c r="W48" s="7"/>
@@ -3512,13 +3777,13 @@
         <v>29</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J49" s="1">
         <v>5</v>
@@ -3530,17 +3795,17 @@
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" ref="M49:M53" si="16">M48+(F48-E48)*N48+N49</f>
+        <f t="shared" ref="M49:M54" si="16">M48+(F48-E48)*N48+N49</f>
         <v>1800000</v>
       </c>
       <c r="N49" s="1">
         <v>250000</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q49" s="1">
         <f t="shared" si="10"/>
@@ -3600,13 +3865,13 @@
         <v>49</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J50" s="1">
         <v>5</v>
@@ -3625,10 +3890,10 @@
         <v>500000</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q50" s="1">
         <f t="shared" si="10"/>
@@ -3688,13 +3953,13 @@
         <v>79</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
@@ -3713,10 +3978,10 @@
         <v>1000000</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q51" s="1">
         <f t="shared" si="10"/>
@@ -3776,13 +4041,13 @@
         <v>120</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -3801,10 +4066,10 @@
         <v>1000000</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q52" s="1">
         <f t="shared" si="10"/>
@@ -3864,13 +4129,13 @@
         <v>150</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
@@ -3889,10 +4154,10 @@
         <v>5000000</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q53" s="1">
         <f t="shared" si="10"/>
@@ -3938,8 +4203,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="23:23">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C54" s="1">
+        <v>508</v>
+      </c>
+      <c r="D54" s="1">
+        <v>5</v>
+      </c>
+      <c r="E54" s="1">
+        <v>151</v>
+      </c>
+      <c r="F54" s="1">
+        <v>200</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="1">
+        <v>141</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="16"/>
+        <v>249050000</v>
+      </c>
+      <c r="N54" s="1">
+        <v>14000000</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q54" s="1">
+        <f t="shared" si="10"/>
+        <v>3141</v>
+      </c>
+      <c r="R54" s="1">
+        <f t="shared" si="11"/>
+        <v>3141</v>
+      </c>
+      <c r="S54" s="1">
+        <f t="shared" si="12"/>
+        <v>3141</v>
+      </c>
+      <c r="T54" s="1">
+        <f t="shared" si="13"/>
+        <v>223</v>
+      </c>
+      <c r="U54" s="1">
+        <f t="shared" si="14"/>
+        <v>837</v>
+      </c>
+      <c r="V54" s="1">
+        <f t="shared" si="15"/>
+        <v>194</v>
+      </c>
       <c r="W54" s="7"/>
+      <c r="X54" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W55" s="7"/>
@@ -3961,13 +4311,13 @@
         <v>9</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -3985,7 +4335,7 @@
         <v>40000</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Q57" s="1">
         <v>15</v>
@@ -4039,13 +4389,13 @@
         <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J58" s="1">
         <v>6</v>
@@ -4063,33 +4413,33 @@
         <v>200000</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" ref="Q58:Q64" si="17">Q57+(F57-E57)*X57+X58</f>
+        <f t="shared" ref="Q58:Q65" si="17">Q57+(F57-E57)*X57+X58</f>
         <v>33</v>
       </c>
       <c r="R58" s="1">
-        <f t="shared" ref="R58:R64" si="18">R57+(F57-E57)*Y57+Y58</f>
+        <f t="shared" ref="R58:R65" si="18">R57+(F57-E57)*Y57+Y58</f>
         <v>33</v>
       </c>
       <c r="S58" s="1">
-        <f t="shared" ref="S58:S64" si="19">S57+(F57-E57)*Z57+Z58</f>
+        <f t="shared" ref="S58:S65" si="19">S57+(F57-E57)*Z57+Z58</f>
         <v>33</v>
       </c>
       <c r="T58" s="1">
-        <f t="shared" ref="T58:T64" si="20">T57+(F57-E57)*AA57+AA58</f>
+        <f t="shared" ref="T58:T65" si="20">T57+(F57-E57)*AA57+AA58</f>
         <v>33</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" ref="U58:U64" si="21">U57+(F57-E57)*AB57+AB58</f>
+        <f t="shared" ref="U58:U65" si="21">U57+(F57-E57)*AB57+AB58</f>
         <v>33</v>
       </c>
       <c r="V58" s="1">
-        <f t="shared" ref="V58:V64" si="22">V57+(F57-E57)*AC57+AC58</f>
+        <f t="shared" ref="V58:V65" si="22">V57+(F57-E57)*AC57+AC58</f>
         <v>0</v>
       </c>
       <c r="W58" s="7"/>
@@ -4126,13 +4476,13 @@
         <v>29</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J59" s="1">
         <v>6</v>
@@ -4144,17 +4494,17 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M64" si="23">M58+(F58-E58)*N58+N59</f>
+        <f t="shared" ref="M59:M65" si="23">M58+(F58-E58)*N58+N59</f>
         <v>2600000</v>
       </c>
       <c r="N59" s="1">
         <v>400000</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="17"/>
@@ -4214,13 +4564,13 @@
         <v>49</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J60" s="1">
         <v>6</v>
@@ -4239,10 +4589,10 @@
         <v>800000</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="17"/>
@@ -4302,13 +4652,13 @@
         <v>79</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J61" s="1">
         <v>6</v>
@@ -4327,10 +4677,10 @@
         <v>1600000</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q61" s="1">
         <f t="shared" si="17"/>
@@ -4390,13 +4740,13 @@
         <v>95</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J62" s="1">
         <v>6</v>
@@ -4415,10 +4765,10 @@
         <v>3200000</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q62" s="1">
         <f t="shared" si="17"/>
@@ -4478,13 +4828,13 @@
         <v>120</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J63" s="1">
         <v>6</v>
@@ -4503,10 +4853,10 @@
         <v>3200000</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q63" s="1">
         <f t="shared" si="17"/>
@@ -4566,13 +4916,13 @@
         <v>150</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J64" s="1">
         <v>6</v>
@@ -4591,10 +4941,10 @@
         <v>6000000</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Q64" s="1">
         <f t="shared" si="17"/>
@@ -4640,16 +4990,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C65" s="1">
+        <v>609</v>
+      </c>
+      <c r="D65" s="1">
+        <v>6</v>
+      </c>
+      <c r="E65" s="1">
+        <v>151</v>
+      </c>
+      <c r="F65" s="1">
+        <v>200</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J65" s="1">
+        <v>6</v>
+      </c>
+      <c r="K65" s="1">
+        <v>141</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="23"/>
+        <v>397400000</v>
+      </c>
+      <c r="N65" s="1">
+        <v>16000000</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q65" s="1">
+        <f t="shared" si="17"/>
+        <v>3141</v>
+      </c>
+      <c r="R65" s="1">
+        <f t="shared" si="18"/>
+        <v>3141</v>
+      </c>
+      <c r="S65" s="1">
+        <f t="shared" si="19"/>
+        <v>3141</v>
+      </c>
+      <c r="T65" s="1">
+        <f t="shared" si="20"/>
+        <v>3141</v>
+      </c>
+      <c r="U65" s="1">
+        <f t="shared" si="21"/>
+        <v>3141</v>
+      </c>
+      <c r="V65" s="1">
+        <f t="shared" si="22"/>
+        <v>194</v>
+      </c>
       <c r="W65" s="7"/>
+      <c r="X65" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z65" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA65" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB65" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC65" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="7:23">
       <c r="G66" s="2"/>
@@ -4698,13 +5125,13 @@
         <v>9</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -4722,7 +5149,7 @@
         <v>80000</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="W69" s="7"/>
     </row>
@@ -4740,13 +5167,13 @@
         <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J70" s="1">
         <v>7</v>
@@ -4764,10 +5191,10 @@
         <v>300000</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W70" s="7"/>
     </row>
@@ -4785,13 +5212,13 @@
         <v>29</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J71" s="1">
         <v>7</v>
@@ -4803,17 +5230,17 @@
         <v>1</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" ref="M71:M75" si="24">M70+(F70-E70)*N70+N71</f>
+        <f t="shared" ref="M71:M76" si="24">M70+(F70-E70)*N70+N71</f>
         <v>4100000</v>
       </c>
       <c r="N71" s="1">
         <v>600000</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W71" s="7"/>
     </row>
@@ -4831,13 +5258,13 @@
         <v>49</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J72" s="1">
         <v>7</v>
@@ -4856,10 +5283,10 @@
         <v>1000000</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W72" s="7"/>
     </row>
@@ -4877,13 +5304,13 @@
         <v>79</v>
       </c>
       <c r="G73" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="J73" s="1">
         <v>7</v>
@@ -4902,10 +5329,10 @@
         <v>2000000</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W73" s="7"/>
     </row>
@@ -4923,13 +5350,13 @@
         <v>120</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J74" s="1">
         <v>7</v>
@@ -4948,10 +5375,10 @@
         <v>4000000</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="W74" s="7"/>
     </row>
@@ -4969,13 +5396,13 @@
         <v>150</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J75" s="1">
         <v>7</v>
@@ -4994,16 +5421,57 @@
         <v>7000000</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="W75" s="7"/>
     </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="8:23">
-      <c r="H76" s="5"/>
-      <c r="N76" s="2"/>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C76" s="1">
+        <v>708</v>
+      </c>
+      <c r="D76" s="1">
+        <v>7</v>
+      </c>
+      <c r="E76" s="1">
+        <v>151</v>
+      </c>
+      <c r="F76" s="1">
+        <v>200</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J76" s="1">
+        <v>7</v>
+      </c>
+      <c r="K76" s="1">
+        <v>70</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="24"/>
+        <v>481500000</v>
+      </c>
+      <c r="N76" s="1">
+        <v>18000000</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="W76" s="7"/>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="8:23">
@@ -5028,13 +5496,13 @@
         <v>9</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J79" s="1">
         <v>0</v>
@@ -5052,7 +5520,7 @@
         <v>200000</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="Q79" s="1">
         <v>15</v>
@@ -5106,13 +5574,13 @@
         <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J80" s="1">
         <v>8</v>
@@ -5130,33 +5598,33 @@
         <v>500000</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" ref="Q80:Q85" si="25">Q79+(F79-E79)*X79+X80</f>
+        <f t="shared" ref="Q80:Q86" si="25">Q79+(F79-E79)*X79+X80</f>
         <v>33</v>
       </c>
       <c r="R80" s="1">
-        <f t="shared" ref="R80:R85" si="26">R79+(F79-E79)*Y79+Y80</f>
+        <f t="shared" ref="R80:R86" si="26">R79+(F79-E79)*Y79+Y80</f>
         <v>33</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" ref="S80:S85" si="27">S79+(F79-E79)*Z79+Z80</f>
+        <f t="shared" ref="S80:S86" si="27">S79+(F79-E79)*Z79+Z80</f>
         <v>33</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" ref="T80:T85" si="28">T79+(F79-E79)*AA79+AA80</f>
+        <f t="shared" ref="T80:T86" si="28">T79+(F79-E79)*AA79+AA80</f>
         <v>33</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" ref="U80:U85" si="29">U79+(F79-E79)*AB79+AB80</f>
+        <f t="shared" ref="U80:U86" si="29">U79+(F79-E79)*AB79+AB80</f>
         <v>33</v>
       </c>
       <c r="V80" s="1">
-        <f t="shared" ref="V80:V85" si="30">V79+(F79-E79)*AC79+AC80</f>
+        <f t="shared" ref="V80:V86" si="30">V79+(F79-E79)*AC79+AC80</f>
         <v>0</v>
       </c>
       <c r="W80" s="7"/>
@@ -5193,13 +5661,13 @@
         <v>29</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J81" s="1">
         <v>8</v>
@@ -5211,17 +5679,17 @@
         <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" ref="M81:M85" si="31">M80+(F80-E80)*N80+N81</f>
+        <f t="shared" ref="M81:M86" si="31">M80+(F80-E80)*N80+N81</f>
         <v>7500000</v>
       </c>
       <c r="N81" s="1">
         <v>1000000</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q81" s="1">
         <f t="shared" si="25"/>
@@ -5281,13 +5749,13 @@
         <v>49</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J82" s="1">
         <v>8</v>
@@ -5306,10 +5774,10 @@
         <v>2000000</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q82" s="1">
         <f t="shared" si="25"/>
@@ -5369,13 +5837,13 @@
         <v>79</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J83" s="1">
         <v>8</v>
@@ -5394,10 +5862,10 @@
         <v>4000000</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q83" s="1">
         <f t="shared" si="25"/>
@@ -5457,13 +5925,13 @@
         <v>120</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J84" s="1">
         <v>8</v>
@@ -5482,10 +5950,10 @@
         <v>6000000</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q84" s="1">
         <f t="shared" si="25"/>
@@ -5545,13 +6013,13 @@
         <v>150</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J85" s="1">
         <v>8</v>
@@ -5570,10 +6038,10 @@
         <v>8000000</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Q85" s="1">
         <f t="shared" si="25"/>
@@ -5619,9 +6087,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="14:23">
-      <c r="N86" s="2"/>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C86" s="1">
+        <v>808</v>
+      </c>
+      <c r="D86" s="1">
+        <v>8</v>
+      </c>
+      <c r="E86" s="1">
+        <v>151</v>
+      </c>
+      <c r="F86" s="1">
+        <v>200</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J86" s="1">
+        <v>8</v>
+      </c>
+      <c r="K86" s="1">
+        <v>141</v>
+      </c>
+      <c r="L86" s="1">
+        <v>1</v>
+      </c>
+      <c r="M86" s="1">
+        <f t="shared" si="31"/>
+        <v>682500000</v>
+      </c>
+      <c r="N86" s="1">
+        <v>20000000</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P86" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q86" s="1">
+        <f t="shared" si="25"/>
+        <v>3141</v>
+      </c>
+      <c r="R86" s="1">
+        <f t="shared" si="26"/>
+        <v>3141</v>
+      </c>
+      <c r="S86" s="1">
+        <f t="shared" si="27"/>
+        <v>3141</v>
+      </c>
+      <c r="T86" s="1">
+        <f t="shared" si="28"/>
+        <v>3141</v>
+      </c>
+      <c r="U86" s="1">
+        <f t="shared" si="29"/>
+        <v>3141</v>
+      </c>
+      <c r="V86" s="1">
+        <f t="shared" si="30"/>
+        <v>194</v>
+      </c>
       <c r="W86" s="7"/>
+      <c r="X86" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y86" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z86" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA86" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB86" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC86" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="23:23">
       <c r="W87" s="7"/>

--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="130">
   <si>
     <t>#</t>
   </si>
@@ -86,6 +86,9 @@
     <t>long[]</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -152,12 +155,21 @@
     <t>14,15,16,8,9,33,2007</t>
   </si>
   <si>
-    <t>3118,3188,3118,521,1042,194,2</t>
+    <t>3118,3118,3118,521,1042,194,2</t>
   </si>
   <si>
     <t>80,80,80,8,16,4,2</t>
   </si>
   <si>
+    <t>14,15,16,8,9,33,2007,2004</t>
+  </si>
+  <si>
+    <t>9558,9558,9558,1165,2330,518,164,2</t>
+  </si>
+  <si>
+    <t>80,80,80,8,16,6,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,10,11</t>
   </si>
   <si>
@@ -176,6 +188,9 @@
     <t>14,15,16,10,11,34,2008</t>
   </si>
   <si>
+    <t>14,15,16,10,11,34,2008,2005</t>
+  </si>
+  <si>
     <t>14,15,16,12,19</t>
   </si>
   <si>
@@ -194,6 +209,9 @@
     <t>14,15,16,12,19,35,2009</t>
   </si>
   <si>
+    <t>14,15,16,12,19,35,2009,2006</t>
+  </si>
+  <si>
     <t>14,15,16,13,24</t>
   </si>
   <si>
@@ -212,6 +230,9 @@
     <t>14,15,16,13,24,2003,2002</t>
   </si>
   <si>
+    <t>14,15,16,13,24,2003,2002,2001</t>
+  </si>
+  <si>
     <t>14,15,16,7,26</t>
   </si>
   <si>
@@ -272,6 +293,15 @@
     <t>80,80,80,4,16,4,2</t>
   </si>
   <si>
+    <t>14,15,16,7,26,2002,2012,2010</t>
+  </si>
+  <si>
+    <t>9581,9581,9581,549,2125,518,164,2</t>
+  </si>
+  <si>
+    <t>80,80,80,4,16,6,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,27,28</t>
   </si>
   <si>
@@ -335,6 +365,15 @@
     <t>80,80,80,80,80,4,2</t>
   </si>
   <si>
+    <t>14,15,16,27,28,2004,2003,2001</t>
+  </si>
+  <si>
+    <t>9581,9581,9581,9581,9581,518,164,2</t>
+  </si>
+  <si>
+    <t>80,80,80,80,80,6,4,2</t>
+  </si>
+  <si>
     <t>14,15,16,18,20</t>
   </si>
   <si>
@@ -359,6 +398,9 @@
     <t>14,15,16,18,20,2005,2010</t>
   </si>
   <si>
+    <t>14,15,16,18,20,2005,2010,2013</t>
+  </si>
+  <si>
     <t>10级解锁命中光环</t>
   </si>
   <si>
@@ -372,6 +414,9 @@
   </si>
   <si>
     <t>14,15,16,18,20,2006,2001</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,2006,2001,2013</t>
   </si>
 </sst>
 </file>
@@ -1355,38 +1400,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC178"/>
+  <dimension ref="A1:AE178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.8761061946903" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3893805309735" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30.3451327433628" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.8141592920354" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.6283185840708" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.75221238938053" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.50442477876106" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.3716814159292" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.0833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.3416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.8166666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.50833333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.375" style="2" customWidth="1"/>
     <col min="14" max="14" width="9" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.2477876106195" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5044247787611" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.24778761061947" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.12389380530973" style="2" customWidth="1"/>
-    <col min="19" max="22" width="4.3716814159292" style="2" customWidth="1"/>
-    <col min="23" max="23" width="4.3716814159292" style="3" customWidth="1"/>
-    <col min="24" max="24" width="5.12389380530973" style="2" customWidth="1"/>
-    <col min="25" max="25" width="4.3716814159292" style="2" customWidth="1"/>
-    <col min="26" max="26" width="5.24778761061947" style="2" customWidth="1"/>
-    <col min="27" max="27" width="5" style="2" customWidth="1"/>
-    <col min="28" max="28" width="5.6283185840708" style="2" customWidth="1"/>
-    <col min="29" max="29" width="6.12389380530973" style="2" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="2"/>
+    <col min="15" max="15" width="13.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5083333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.125" style="2" customWidth="1"/>
+    <col min="19" max="22" width="4.375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="9.08333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="4.375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="5.125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="4.375" style="2" customWidth="1"/>
+    <col min="27" max="27" width="5.25" style="2" customWidth="1"/>
+    <col min="28" max="28" width="5" style="2" customWidth="1"/>
+    <col min="29" max="29" width="5.625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="6.125" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="G1" s="2"/>
@@ -1415,10 +1461,10 @@
       <c r="V1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="W1" s="3"/>
-      <c r="X1" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="W1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="3"/>
       <c r="Y1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1434,8 +1480,14 @@
       <c r="AC1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
+      <c r="AD1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="G2" s="2"/>
@@ -1464,10 +1516,10 @@
       <c r="V2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="W2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3"/>
       <c r="Y2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1483,8 +1535,14 @@
       <c r="AC2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="AD2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1531,9 +1589,9 @@
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="W3" s="7"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X3" s="7"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
@@ -1580,9 +1638,9 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="W4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X4" s="7"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
@@ -1616,22 +1674,22 @@
         <v>16</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="W5" s="7"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="X5" s="7"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C6" s="1">
         <v>101</v>
       </c>
@@ -1645,13 +1703,13 @@
         <v>9</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -1669,7 +1727,7 @@
         <v>1000</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q6" s="1">
         <v>10</v>
@@ -1689,10 +1747,10 @@
       <c r="V6" s="1">
         <v>0</v>
       </c>
-      <c r="W6" s="7"/>
-      <c r="X6" s="1">
-        <v>1</v>
-      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="7"/>
       <c r="Y6" s="1">
         <v>1</v>
       </c>
@@ -1703,13 +1761,19 @@
         <v>1</v>
       </c>
       <c r="AB6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1">
         <v>2</v>
       </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C7" s="1">
         <v>102</v>
       </c>
@@ -1723,13 +1787,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
@@ -1748,39 +1812,40 @@
         <v>10000</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q14" si="0">Q6+(F6-E6)*X6+X7</f>
+        <f t="shared" ref="Q7:Q15" si="0">Q6+(F6-E6)*Y6+Y7</f>
         <v>20</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" ref="R7:R14" si="1">R6+(F6-E6)*Y6+Y7</f>
+        <f t="shared" ref="R7:R15" si="1">R6+(F6-E6)*Z6+Z7</f>
         <v>20</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S14" si="2">S6+(F6-E6)*Z6+Z7</f>
+        <f t="shared" ref="S7:S15" si="2">S6+(F6-E6)*AA6+AA7</f>
         <v>20</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T14" si="3">T6+(F6-E6)*AA6+AA7</f>
+        <f t="shared" ref="T7:T15" si="3">T6+(F6-E6)*AB6+AB7</f>
         <v>15</v>
       </c>
       <c r="U7" s="1">
-        <f t="shared" ref="U7:U14" si="4">U6+(F6-E6)*AB6+AB7</f>
+        <f t="shared" ref="U7:U15" si="4">U6+(F6-E6)*AC6+AC7</f>
         <v>30</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:V14" si="5">V6+(F6-E6)*AC6+AC7</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="7"/>
-      <c r="X7" s="1">
-        <v>2</v>
-      </c>
+        <f t="shared" ref="V7:V15" si="5">V6+(F6-E6)*AD6+AD7</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" ref="W7:W15" si="6">W6+(F6-E6)*AE6+AE7</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="7"/>
       <c r="Y7" s="1">
         <v>2</v>
       </c>
@@ -1791,13 +1856,19 @@
         <v>2</v>
       </c>
       <c r="AB7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="1">
         <v>4</v>
       </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C8" s="1">
         <v>103</v>
       </c>
@@ -1811,13 +1882,13 @@
         <v>29</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -1829,17 +1900,17 @@
         <v>1</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" ref="M8:M14" si="6">M7+(F7-E7)*N7+N8</f>
+        <f t="shared" ref="M8:M15" si="7">M7+(F7-E7)*N7+N8</f>
         <v>120000</v>
       </c>
       <c r="N8" s="1">
         <v>20000</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="0"/>
@@ -1865,10 +1936,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W8" s="7"/>
-      <c r="X8" s="1">
-        <v>2</v>
-      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="7"/>
       <c r="Y8" s="1">
         <v>2</v>
       </c>
@@ -1879,13 +1951,19 @@
         <v>2</v>
       </c>
       <c r="AB8" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="1">
         <v>4</v>
       </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C9" s="1">
         <v>104</v>
       </c>
@@ -1899,13 +1977,13 @@
         <v>49</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -1917,17 +1995,17 @@
         <v>1</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>340000</v>
       </c>
       <c r="N9" s="1">
         <v>40000</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="1">
         <f t="shared" si="0"/>
@@ -1953,10 +2031,11 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="W9" s="7"/>
-      <c r="X9" s="1">
-        <v>3</v>
-      </c>
+      <c r="W9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="7"/>
       <c r="Y9" s="1">
         <v>3</v>
       </c>
@@ -1967,13 +2046,19 @@
         <v>3</v>
       </c>
       <c r="AB9" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="1">
         <v>6</v>
       </c>
-      <c r="AC9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C10" s="1">
         <v>105</v>
       </c>
@@ -1987,13 +2072,13 @@
         <v>79</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -2005,17 +2090,17 @@
         <v>1</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1180000</v>
       </c>
       <c r="N10" s="1">
         <v>80000</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q10" s="1">
         <f t="shared" si="0"/>
@@ -2041,10 +2126,11 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="W10" s="7"/>
-      <c r="X10" s="1">
-        <v>4</v>
-      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="7"/>
       <c r="Y10" s="1">
         <v>4</v>
       </c>
@@ -2055,13 +2141,19 @@
         <v>4</v>
       </c>
       <c r="AB10" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="1">
         <v>8</v>
       </c>
-      <c r="AC10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C11" s="1">
         <v>106</v>
       </c>
@@ -2075,13 +2167,13 @@
         <v>95</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -2093,17 +2185,17 @@
         <v>1</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3660000</v>
       </c>
       <c r="N11" s="1">
         <v>160000</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" si="0"/>
@@ -2129,10 +2221,11 @@
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="W11" s="7"/>
-      <c r="X11" s="1">
-        <v>40</v>
-      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="7"/>
       <c r="Y11" s="1">
         <v>40</v>
       </c>
@@ -2140,16 +2233,22 @@
         <v>40</v>
       </c>
       <c r="AA11" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB11" s="1">
         <v>4</v>
       </c>
-      <c r="AB11" s="1">
+      <c r="AC11" s="1">
         <v>8</v>
       </c>
-      <c r="AC11" s="1">
+      <c r="AD11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AE11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C12" s="1">
         <v>107</v>
       </c>
@@ -2163,13 +2262,13 @@
         <v>120</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -2181,17 +2280,17 @@
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6220000</v>
       </c>
       <c r="N12" s="1">
         <v>160000</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="0"/>
@@ -2217,10 +2316,11 @@
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
-      <c r="W12" s="7"/>
-      <c r="X12" s="1">
-        <v>40</v>
-      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="7"/>
       <c r="Y12" s="1">
         <v>40</v>
       </c>
@@ -2228,16 +2328,22 @@
         <v>40</v>
       </c>
       <c r="AA12" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB12" s="1">
         <v>4</v>
       </c>
-      <c r="AB12" s="1">
+      <c r="AC12" s="1">
         <v>8</v>
       </c>
-      <c r="AC12" s="1">
+      <c r="AD12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C13" s="1">
         <v>108</v>
       </c>
@@ -2251,13 +2357,13 @@
         <v>150</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -2269,17 +2375,17 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11060000</v>
       </c>
       <c r="N13" s="1">
         <v>1000000</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="0"/>
@@ -2305,10 +2411,11 @@
         <f t="shared" si="5"/>
         <v>134</v>
       </c>
-      <c r="W13" s="7"/>
-      <c r="X13" s="1">
-        <v>40</v>
-      </c>
+      <c r="W13" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="7"/>
       <c r="Y13" s="1">
         <v>40</v>
       </c>
@@ -2316,16 +2423,22 @@
         <v>40</v>
       </c>
       <c r="AA13" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB13" s="1">
         <v>4</v>
       </c>
-      <c r="AB13" s="1">
+      <c r="AC13" s="1">
         <v>8</v>
       </c>
-      <c r="AC13" s="1">
+      <c r="AD13" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AE13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C14" s="1">
         <v>109</v>
       </c>
@@ -2336,16 +2449,16 @@
         <v>151</v>
       </c>
       <c r="F14" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -2357,69 +2470,168 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50060000</v>
       </c>
       <c r="N14" s="1">
         <v>10000000</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="0"/>
-        <v>3118</v>
+        <v>3158</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="1"/>
-        <v>3118</v>
+        <v>3158</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="2"/>
-        <v>3118</v>
+        <v>3158</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" si="4"/>
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="1">
-        <v>40</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="X14" s="7"/>
       <c r="Y14" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Z14" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AA14" s="1">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="AB14" s="1">
         <v>8</v>
       </c>
       <c r="AC14" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W15" s="7"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W16" s="7"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C15" s="1">
+        <v>110</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>231</v>
+      </c>
+      <c r="F15" s="1">
+        <v>300</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>86</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="7"/>
+        <v>860060000</v>
+      </c>
+      <c r="N15" s="1">
+        <v>20000000</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q15" s="1">
+        <f t="shared" si="0"/>
+        <v>9558</v>
+      </c>
+      <c r="R15" s="1">
+        <f t="shared" si="1"/>
+        <v>9558</v>
+      </c>
+      <c r="S15" s="1">
+        <f t="shared" si="2"/>
+        <v>9558</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" si="3"/>
+        <v>1165</v>
+      </c>
+      <c r="U15" s="1">
+        <f t="shared" si="4"/>
+        <v>2330</v>
+      </c>
+      <c r="V15" s="1">
+        <f t="shared" si="5"/>
+        <v>518</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" si="6"/>
+        <v>164</v>
+      </c>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="1">
+        <v>80</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>80</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>80</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X16" s="7"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C17" s="1">
         <v>201</v>
       </c>
@@ -2433,13 +2645,13 @@
         <v>9</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -2457,20 +2669,20 @@
         <v>3000</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W17" s="7"/>
-      <c r="AA17" s="1">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="X17" s="7"/>
       <c r="AB17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="1">
         <v>2</v>
       </c>
-      <c r="AC17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C18" s="1">
         <v>202</v>
       </c>
@@ -2484,13 +2696,13 @@
         <v>19</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1">
         <v>2</v>
@@ -2508,23 +2720,23 @@
         <v>30000</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W18" s="7"/>
-      <c r="AA18" s="1">
+        <v>50</v>
+      </c>
+      <c r="X18" s="7"/>
+      <c r="AB18" s="1">
         <v>2</v>
       </c>
-      <c r="AB18" s="1">
+      <c r="AC18" s="1">
         <v>4</v>
       </c>
-      <c r="AC18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C19" s="1">
         <v>203</v>
       </c>
@@ -2538,13 +2750,13 @@
         <v>29</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1">
         <v>2</v>
@@ -2556,30 +2768,30 @@
         <v>1</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" ref="M19:M24" si="7">M18+(F18-E18)*N18+N19</f>
+        <f t="shared" ref="M19:M25" si="8">M18+(F18-E18)*N18+N19</f>
         <v>350000</v>
       </c>
       <c r="N19" s="1">
         <v>50000</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W19" s="7"/>
-      <c r="AA19" s="1">
+        <v>50</v>
+      </c>
+      <c r="X19" s="7"/>
+      <c r="AB19" s="1">
         <v>2</v>
       </c>
-      <c r="AB19" s="1">
+      <c r="AC19" s="1">
         <v>4</v>
       </c>
-      <c r="AC19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C20" s="1">
         <v>204</v>
       </c>
@@ -2593,13 +2805,13 @@
         <v>49</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" s="1">
         <v>2</v>
@@ -2611,30 +2823,30 @@
         <v>1</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>900000</v>
       </c>
       <c r="N20" s="1">
         <v>100000</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W20" s="7"/>
-      <c r="AA20" s="1">
+        <v>50</v>
+      </c>
+      <c r="X20" s="7"/>
+      <c r="AB20" s="1">
         <v>3</v>
       </c>
-      <c r="AB20" s="1">
+      <c r="AC20" s="1">
         <v>6</v>
       </c>
-      <c r="AC20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C21" s="1">
         <v>205</v>
       </c>
@@ -2648,13 +2860,13 @@
         <v>79</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21" s="1">
         <v>2</v>
@@ -2666,30 +2878,30 @@
         <v>1</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3000000</v>
       </c>
       <c r="N21" s="1">
         <v>200000</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W21" s="7"/>
-      <c r="AA21" s="1">
+        <v>50</v>
+      </c>
+      <c r="X21" s="7"/>
+      <c r="AB21" s="1">
         <v>4</v>
       </c>
-      <c r="AB21" s="1">
+      <c r="AC21" s="1">
         <v>8</v>
       </c>
-      <c r="AC21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C22" s="1">
         <v>206</v>
       </c>
@@ -2703,13 +2915,13 @@
         <v>120</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J22" s="1">
         <v>2</v>
@@ -2721,30 +2933,30 @@
         <v>1</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9200000</v>
       </c>
       <c r="N22" s="1">
         <v>400000</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W22" s="7"/>
-      <c r="AA22" s="1">
+        <v>50</v>
+      </c>
+      <c r="X22" s="7"/>
+      <c r="AB22" s="1">
         <v>4</v>
       </c>
-      <c r="AB22" s="1">
+      <c r="AC22" s="1">
         <v>8</v>
       </c>
-      <c r="AC22" s="1">
+      <c r="AD22" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C23" s="1">
         <v>207</v>
       </c>
@@ -2758,13 +2970,13 @@
         <v>150</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J23" s="1">
         <v>2</v>
@@ -2776,30 +2988,30 @@
         <v>1</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27200000</v>
       </c>
       <c r="N23" s="1">
         <v>2000000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W23" s="7"/>
-      <c r="AA23" s="1">
+        <v>50</v>
+      </c>
+      <c r="X23" s="7"/>
+      <c r="AB23" s="1">
         <v>4</v>
       </c>
-      <c r="AB23" s="1">
+      <c r="AC23" s="1">
         <v>8</v>
       </c>
-      <c r="AC23" s="1">
+      <c r="AD23" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C24" s="1">
         <v>208</v>
       </c>
@@ -2810,16 +3022,16 @@
         <v>151</v>
       </c>
       <c r="F24" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J24" s="1">
         <v>2</v>
@@ -2831,36 +3043,88 @@
         <v>1</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>96200000</v>
       </c>
       <c r="N24" s="1">
         <v>11000000</v>
       </c>
       <c r="O24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X24" s="7"/>
+      <c r="AB24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C25" s="1">
+        <v>209</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>231</v>
+      </c>
+      <c r="F25" s="1">
+        <v>300</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="I25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W24" s="7"/>
-      <c r="AA24" s="1">
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>221</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="8"/>
+        <v>987200000</v>
+      </c>
+      <c r="N25" s="1">
+        <v>22000000</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X25" s="7"/>
+      <c r="AB25" s="1">
         <v>4</v>
       </c>
-      <c r="AB24" s="1">
+      <c r="AC25" s="1">
         <v>8</v>
       </c>
-      <c r="AC24" s="1">
+      <c r="AD25" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W25" s="7"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W26" s="7"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:23">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X26" s="7"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C27" s="1">
         <v>301</v>
       </c>
@@ -2874,13 +3138,13 @@
         <v>9</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
@@ -2898,11 +3162,11 @@
         <v>6000</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W27" s="7"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>55</v>
+      </c>
+      <c r="X27" s="7"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C28" s="1">
         <v>302</v>
       </c>
@@ -2916,13 +3180,13 @@
         <v>19</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="1">
         <v>3</v>
@@ -2940,14 +3204,14 @@
         <v>50000</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W28" s="7"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X28" s="7"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C29" s="1">
         <v>303</v>
       </c>
@@ -2961,13 +3225,13 @@
         <v>29</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" s="1">
         <v>3</v>
@@ -2979,21 +3243,21 @@
         <v>1</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" ref="M29:M34" si="8">M28+(F28-E28)*N28+N29</f>
+        <f t="shared" ref="M29:M35" si="9">M28+(F28-E28)*N28+N29</f>
         <v>590000</v>
       </c>
       <c r="N29" s="1">
         <v>80000</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W29" s="7"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X29" s="7"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C30" s="1">
         <v>304</v>
       </c>
@@ -3007,13 +3271,13 @@
         <v>49</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J30" s="1">
         <v>3</v>
@@ -3025,21 +3289,21 @@
         <v>1</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1470000</v>
       </c>
       <c r="N30" s="1">
         <v>160000</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W30" s="7"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X30" s="7"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C31" s="1">
         <v>305</v>
       </c>
@@ -3053,13 +3317,13 @@
         <v>79</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J31" s="1">
         <v>3</v>
@@ -3071,21 +3335,21 @@
         <v>1</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4830000</v>
       </c>
       <c r="N31" s="1">
         <v>320000</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W31" s="7"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X31" s="7"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C32" s="1">
         <v>306</v>
       </c>
@@ -3099,13 +3363,13 @@
         <v>120</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J32" s="1">
         <v>3</v>
@@ -3117,21 +3381,21 @@
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14750000</v>
       </c>
       <c r="N32" s="1">
         <v>640000</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W32" s="7"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X32" s="7"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C33" s="1">
         <v>307</v>
       </c>
@@ -3145,13 +3409,13 @@
         <v>150</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J33" s="1">
         <v>3</v>
@@ -3163,21 +3427,21 @@
         <v>1</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>43350000</v>
       </c>
       <c r="N33" s="1">
         <v>3000000</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W33" s="7"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X33" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C34" s="1">
         <v>308</v>
       </c>
@@ -3188,16 +3452,16 @@
         <v>151</v>
       </c>
       <c r="F34" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J34" s="1">
         <v>3</v>
@@ -3209,27 +3473,70 @@
         <v>1</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>142350000</v>
       </c>
       <c r="N34" s="1">
         <v>12000000</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W34" s="7"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W35" s="7"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W36" s="7"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>57</v>
+      </c>
+      <c r="X34" s="7"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C35" s="1">
+        <v>309</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>231</v>
+      </c>
+      <c r="F35" s="1">
+        <v>300</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" s="1">
+        <v>3</v>
+      </c>
+      <c r="K35" s="1">
+        <v>221</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1">
+        <f t="shared" si="9"/>
+        <v>1114350000</v>
+      </c>
+      <c r="N35" s="1">
+        <v>24000000</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="X35" s="7"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X36" s="7"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C37" s="1">
         <v>401</v>
       </c>
@@ -3243,13 +3550,13 @@
         <v>9</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" s="1">
         <v>0</v>
@@ -3267,11 +3574,11 @@
         <v>10000</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W37" s="7"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>62</v>
+      </c>
+      <c r="X37" s="7"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C38" s="1">
         <v>402</v>
       </c>
@@ -3285,13 +3592,13 @@
         <v>19</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" s="1">
         <v>4</v>
@@ -3309,14 +3616,14 @@
         <v>80000</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W38" s="7"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X38" s="7"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C39" s="1">
         <v>403</v>
       </c>
@@ -3330,13 +3637,13 @@
         <v>29</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
@@ -3348,21 +3655,21 @@
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" ref="M39:M44" si="9">M38+(F38-E38)*N38+N39</f>
+        <f t="shared" ref="M39:M45" si="10">M38+(F38-E38)*N38+N39</f>
         <v>970000</v>
       </c>
       <c r="N39" s="1">
         <v>150000</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W39" s="7"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X39" s="7"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C40" s="1">
         <v>404</v>
       </c>
@@ -3376,13 +3683,13 @@
         <v>49</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J40" s="1">
         <v>4</v>
@@ -3394,21 +3701,21 @@
         <v>1</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2620000</v>
       </c>
       <c r="N40" s="1">
         <v>300000</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W40" s="7"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X40" s="7"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C41" s="1">
         <v>405</v>
       </c>
@@ -3422,13 +3729,13 @@
         <v>79</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J41" s="1">
         <v>4</v>
@@ -3440,21 +3747,21 @@
         <v>1</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8920000</v>
       </c>
       <c r="N41" s="1">
         <v>600000</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W41" s="7"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X41" s="7"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C42" s="1">
         <v>406</v>
       </c>
@@ -3468,13 +3775,13 @@
         <v>120</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J42" s="1">
         <v>4</v>
@@ -3486,21 +3793,21 @@
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>27520000</v>
       </c>
       <c r="N42" s="1">
         <v>1200000</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W42" s="7"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X42" s="7"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C43" s="1">
         <v>407</v>
       </c>
@@ -3514,13 +3821,13 @@
         <v>150</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J43" s="1">
         <v>4</v>
@@ -3532,21 +3839,21 @@
         <v>1</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>79520000</v>
       </c>
       <c r="N43" s="1">
         <v>4000000</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W43" s="7"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>64</v>
+      </c>
+      <c r="X43" s="7"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C44" s="1">
         <v>408</v>
       </c>
@@ -3557,16 +3864,16 @@
         <v>151</v>
       </c>
       <c r="F44" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J44" s="1">
         <v>4</v>
@@ -3578,27 +3885,70 @@
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>208520000</v>
       </c>
       <c r="N44" s="1">
         <v>13000000</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W44" s="7"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W45" s="7"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W46" s="7"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>64</v>
+      </c>
+      <c r="X44" s="7"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C45" s="1">
+        <v>409</v>
+      </c>
+      <c r="D45" s="1">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1">
+        <v>231</v>
+      </c>
+      <c r="F45" s="1">
+        <v>300</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+      <c r="K45" s="1">
+        <v>221</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
+        <f t="shared" si="10"/>
+        <v>1261520000</v>
+      </c>
+      <c r="N45" s="1">
+        <v>26000000</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="X45" s="7"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X46" s="7"/>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C47" s="1">
         <v>501</v>
       </c>
@@ -3612,13 +3962,13 @@
         <v>9</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J47" s="1">
         <v>0</v>
@@ -3636,7 +3986,7 @@
         <v>20000</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q47" s="1">
         <v>15</v>
@@ -3656,10 +4006,10 @@
       <c r="V47" s="1">
         <v>0</v>
       </c>
-      <c r="W47" s="7"/>
-      <c r="X47" s="1">
-        <v>2</v>
-      </c>
+      <c r="W47" s="1">
+        <v>0</v>
+      </c>
+      <c r="X47" s="7"/>
       <c r="Y47" s="1">
         <v>2</v>
       </c>
@@ -3667,16 +4017,22 @@
         <v>2</v>
       </c>
       <c r="AA47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="1">
         <v>2</v>
       </c>
-      <c r="AC47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C48" s="1">
         <v>502</v>
       </c>
@@ -3690,13 +4046,13 @@
         <v>19</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J48" s="1">
         <v>5</v>
@@ -3714,39 +4070,40 @@
         <v>150000</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" ref="Q48:Q54" si="10">Q47+(F47-E47)*X47+X48</f>
+        <f t="shared" ref="Q48:Q55" si="11">Q47+(F47-E47)*Y47+Y48</f>
         <v>33</v>
       </c>
       <c r="R48" s="1">
-        <f t="shared" ref="R48:R54" si="11">R47+(F47-E47)*Y47+Y48</f>
+        <f t="shared" ref="R48:R55" si="12">R47+(F47-E47)*Z47+Z48</f>
         <v>33</v>
       </c>
       <c r="S48" s="1">
-        <f t="shared" ref="S48:S54" si="12">S47+(F47-E47)*Z47+Z48</f>
+        <f t="shared" ref="S48:S55" si="13">S47+(F47-E47)*AA47+AA48</f>
         <v>33</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" ref="T48:T54" si="13">T47+(F47-E47)*AA47+AA48</f>
+        <f t="shared" ref="T48:T55" si="14">T47+(F47-E47)*AB47+AB48</f>
         <v>10</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" ref="U48:U54" si="14">U47+(F47-E47)*AB47+AB48</f>
+        <f t="shared" ref="U48:U55" si="15">U47+(F47-E47)*AC47+AC48</f>
         <v>33</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" ref="V48:V54" si="15">V47+(F47-E47)*AC47+AC48</f>
-        <v>0</v>
-      </c>
-      <c r="W48" s="7"/>
-      <c r="X48" s="1">
-        <v>2</v>
-      </c>
+        <f t="shared" ref="V48:V55" si="16">V47+(F47-E47)*AD47+AD48</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="1">
+        <f t="shared" ref="W48:W55" si="17">W47+(F47-E47)*AE47+AE48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="7"/>
       <c r="Y48" s="1">
         <v>2</v>
       </c>
@@ -3754,16 +4111,22 @@
         <v>2</v>
       </c>
       <c r="AA48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB48" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="1">
         <v>2</v>
       </c>
-      <c r="AC48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C49" s="1">
         <v>503</v>
       </c>
@@ -3777,13 +4140,13 @@
         <v>29</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J49" s="1">
         <v>5</v>
@@ -3795,46 +4158,47 @@
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" ref="M49:M54" si="16">M48+(F48-E48)*N48+N49</f>
+        <f t="shared" ref="M49:M55" si="18">M48+(F48-E48)*N48+N49</f>
         <v>1800000</v>
       </c>
       <c r="N49" s="1">
         <v>250000</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="10"/>
-        <v>54</v>
-      </c>
-      <c r="R49" s="1">
         <f t="shared" si="11"/>
         <v>54</v>
       </c>
-      <c r="S49" s="1">
+      <c r="R49" s="1">
         <f t="shared" si="12"/>
         <v>54</v>
       </c>
+      <c r="S49" s="1">
+        <f t="shared" si="13"/>
+        <v>54</v>
+      </c>
       <c r="T49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>54</v>
       </c>
       <c r="V49" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W49" s="7"/>
-      <c r="X49" s="1">
-        <v>3</v>
-      </c>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W49" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X49" s="7"/>
       <c r="Y49" s="1">
         <v>3</v>
       </c>
@@ -3842,16 +4206,22 @@
         <v>3</v>
       </c>
       <c r="AA49" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB49" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="1">
         <v>3</v>
       </c>
-      <c r="AC49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C50" s="1">
         <v>504</v>
       </c>
@@ -3865,13 +4235,13 @@
         <v>49</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J50" s="1">
         <v>5</v>
@@ -3883,46 +4253,47 @@
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>4550000</v>
       </c>
       <c r="N50" s="1">
         <v>500000</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="10"/>
-        <v>84</v>
-      </c>
-      <c r="R50" s="1">
         <f t="shared" si="11"/>
         <v>84</v>
       </c>
-      <c r="S50" s="1">
+      <c r="R50" s="1">
         <f t="shared" si="12"/>
         <v>84</v>
       </c>
+      <c r="S50" s="1">
+        <f t="shared" si="13"/>
+        <v>84</v>
+      </c>
       <c r="T50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="U50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84</v>
       </c>
       <c r="V50" s="1">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="W50" s="7"/>
-      <c r="X50" s="1">
-        <v>3</v>
-      </c>
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="W50" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="7"/>
       <c r="Y50" s="1">
         <v>3</v>
       </c>
@@ -3930,16 +4301,22 @@
         <v>3</v>
       </c>
       <c r="AA50" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="1">
         <v>3</v>
       </c>
-      <c r="AC50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C51" s="1">
         <v>505</v>
       </c>
@@ -3953,13 +4330,13 @@
         <v>79</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
@@ -3971,46 +4348,47 @@
         <v>1</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>15050000</v>
       </c>
       <c r="N51" s="1">
         <v>1000000</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="10"/>
-        <v>145</v>
-      </c>
-      <c r="R51" s="1">
         <f t="shared" si="11"/>
         <v>145</v>
       </c>
-      <c r="S51" s="1">
+      <c r="R51" s="1">
         <f t="shared" si="12"/>
         <v>145</v>
       </c>
+      <c r="S51" s="1">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
       <c r="T51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>145</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>21</v>
       </c>
-      <c r="W51" s="7"/>
-      <c r="X51" s="1">
-        <v>4</v>
-      </c>
+      <c r="W51" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="7"/>
       <c r="Y51" s="1">
         <v>4</v>
       </c>
@@ -4018,16 +4396,22 @@
         <v>4</v>
       </c>
       <c r="AA51" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="1">
         <v>4</v>
       </c>
-      <c r="AC51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AD51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C52" s="1">
         <v>506</v>
       </c>
@@ -4041,13 +4425,13 @@
         <v>120</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -4059,46 +4443,47 @@
         <v>1</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>45050000</v>
       </c>
       <c r="N52" s="1">
         <v>1000000</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="10"/>
-        <v>301</v>
-      </c>
-      <c r="R52" s="1">
         <f t="shared" si="11"/>
         <v>301</v>
       </c>
-      <c r="S52" s="1">
+      <c r="R52" s="1">
         <f t="shared" si="12"/>
         <v>301</v>
       </c>
+      <c r="S52" s="1">
+        <f t="shared" si="13"/>
+        <v>301</v>
+      </c>
       <c r="T52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>81</v>
       </c>
       <c r="U52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>269</v>
       </c>
       <c r="V52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>52</v>
       </c>
-      <c r="W52" s="7"/>
-      <c r="X52" s="1">
-        <v>40</v>
-      </c>
+      <c r="W52" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X52" s="7"/>
       <c r="Y52" s="1">
         <v>40</v>
       </c>
@@ -4106,16 +4491,22 @@
         <v>40</v>
       </c>
       <c r="AA52" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB52" s="1">
         <v>2</v>
       </c>
-      <c r="AB52" s="1">
+      <c r="AC52" s="1">
         <v>8</v>
       </c>
-      <c r="AC52" s="1">
+      <c r="AD52" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C53" s="1">
         <v>507</v>
       </c>
@@ -4129,13 +4520,13 @@
         <v>150</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
@@ -4147,46 +4538,47 @@
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>90050000</v>
       </c>
       <c r="N53" s="1">
         <v>5000000</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="10"/>
-        <v>1941</v>
-      </c>
-      <c r="R53" s="1">
         <f t="shared" si="11"/>
         <v>1941</v>
       </c>
-      <c r="S53" s="1">
+      <c r="R53" s="1">
         <f t="shared" si="12"/>
         <v>1941</v>
       </c>
+      <c r="S53" s="1">
+        <f t="shared" si="13"/>
+        <v>1941</v>
+      </c>
       <c r="T53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>163</v>
       </c>
       <c r="U53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>597</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>134</v>
       </c>
-      <c r="W53" s="7"/>
-      <c r="X53" s="1">
-        <v>40</v>
-      </c>
+      <c r="W53" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X53" s="7"/>
       <c r="Y53" s="1">
         <v>40</v>
       </c>
@@ -4194,16 +4586,22 @@
         <v>40</v>
       </c>
       <c r="AA53" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB53" s="1">
         <v>2</v>
       </c>
-      <c r="AB53" s="1">
+      <c r="AC53" s="1">
         <v>8</v>
       </c>
-      <c r="AC53" s="1">
+      <c r="AD53" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AE53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C54" s="1">
         <v>508</v>
       </c>
@@ -4214,16 +4612,16 @@
         <v>151</v>
       </c>
       <c r="F54" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J54" s="1">
         <v>5</v>
@@ -4235,69 +4633,168 @@
         <v>1</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>249050000</v>
       </c>
       <c r="N54" s="1">
         <v>14000000</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="10"/>
-        <v>3141</v>
+        <f t="shared" si="11"/>
+        <v>3181</v>
       </c>
       <c r="R54" s="1">
+        <f t="shared" si="12"/>
+        <v>3181</v>
+      </c>
+      <c r="S54" s="1">
+        <f t="shared" si="13"/>
+        <v>3181</v>
+      </c>
+      <c r="T54" s="1">
+        <f t="shared" si="14"/>
+        <v>225</v>
+      </c>
+      <c r="U54" s="1">
+        <f t="shared" si="15"/>
+        <v>845</v>
+      </c>
+      <c r="V54" s="1">
+        <f t="shared" si="16"/>
+        <v>196</v>
+      </c>
+      <c r="W54" s="1">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="1">
+        <v>80</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>80</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>80</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C55" s="1">
+        <v>509</v>
+      </c>
+      <c r="D55" s="1">
+        <v>5</v>
+      </c>
+      <c r="E55" s="1">
+        <v>231</v>
+      </c>
+      <c r="F55" s="1">
+        <v>300</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="1">
+        <v>221</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="18"/>
+        <v>1383050000</v>
+      </c>
+      <c r="N55" s="1">
+        <v>28000000</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="1">
         <f t="shared" si="11"/>
-        <v>3141</v>
-      </c>
-      <c r="S54" s="1">
+        <v>9581</v>
+      </c>
+      <c r="R55" s="1">
         <f t="shared" si="12"/>
-        <v>3141</v>
-      </c>
-      <c r="T54" s="1">
+        <v>9581</v>
+      </c>
+      <c r="S55" s="1">
         <f t="shared" si="13"/>
-        <v>223</v>
-      </c>
-      <c r="U54" s="1">
+        <v>9581</v>
+      </c>
+      <c r="T55" s="1">
         <f t="shared" si="14"/>
-        <v>837</v>
-      </c>
-      <c r="V54" s="1">
+        <v>549</v>
+      </c>
+      <c r="U55" s="1">
         <f t="shared" si="15"/>
-        <v>194</v>
-      </c>
-      <c r="W54" s="7"/>
-      <c r="X54" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z54" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA54" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB54" s="1">
+        <v>2125</v>
+      </c>
+      <c r="V55" s="1">
+        <f t="shared" si="16"/>
+        <v>518</v>
+      </c>
+      <c r="W55" s="1">
+        <f t="shared" si="17"/>
+        <v>164</v>
+      </c>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="1">
+        <v>80</v>
+      </c>
+      <c r="Z55" s="1">
+        <v>80</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>80</v>
+      </c>
+      <c r="AB55" s="1">
         <v>8</v>
       </c>
-      <c r="AC54" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W55" s="7"/>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W56" s="7"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AC55" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE55" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X56" s="7"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C57" s="1">
         <v>601</v>
       </c>
@@ -4311,13 +4808,13 @@
         <v>9</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -4335,47 +4832,29 @@
         <v>40000</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>15</v>
-      </c>
-      <c r="R57" s="1">
-        <v>15</v>
-      </c>
-      <c r="S57" s="1">
-        <v>15</v>
-      </c>
-      <c r="T57" s="1">
-        <v>15</v>
-      </c>
-      <c r="U57" s="1">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="V57" s="1">
         <v>0</v>
       </c>
-      <c r="W57" s="7"/>
-      <c r="X57" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>2</v>
-      </c>
+      <c r="W57" s="1">
+        <v>0</v>
+      </c>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
       <c r="AB57" s="1">
         <v>2</v>
       </c>
       <c r="AC57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>2</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C58" s="1">
         <v>602</v>
       </c>
@@ -4389,13 +4868,13 @@
         <v>19</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J58" s="1">
         <v>6</v>
@@ -4413,56 +4892,39 @@
         <v>200000</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" ref="Q58:Q65" si="17">Q57+(F57-E57)*X57+X58</f>
-        <v>33</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" ref="R58:R65" si="18">R57+(F57-E57)*Y57+Y58</f>
-        <v>33</v>
-      </c>
-      <c r="S58" s="1">
-        <f t="shared" ref="S58:S65" si="19">S57+(F57-E57)*Z57+Z58</f>
-        <v>33</v>
-      </c>
-      <c r="T58" s="1">
-        <f t="shared" ref="T58:T65" si="20">T57+(F57-E57)*AA57+AA58</f>
-        <v>33</v>
-      </c>
-      <c r="U58" s="1">
-        <f t="shared" ref="U58:U65" si="21">U57+(F57-E57)*AB57+AB58</f>
-        <v>33</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
       <c r="V58" s="1">
-        <f t="shared" ref="V58:V65" si="22">V57+(F57-E57)*AC57+AC58</f>
-        <v>0</v>
-      </c>
-      <c r="W58" s="7"/>
-      <c r="X58" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>2</v>
-      </c>
+        <f t="shared" ref="V58:V66" si="19">V57+(F57-E57)*AD57+AD58</f>
+        <v>0</v>
+      </c>
+      <c r="W58" s="1" t="e">
+        <f t="shared" ref="W58:W66" si="20">W57+(G57-F57)*AE57+AE58</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X58" s="7"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
       <c r="AB58" s="1">
         <v>2</v>
       </c>
       <c r="AC58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>2</v>
+      </c>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C59" s="1">
         <v>603</v>
       </c>
@@ -4476,13 +4938,13 @@
         <v>29</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J59" s="1">
         <v>6</v>
@@ -4494,63 +4956,46 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M65" si="23">M58+(F58-E58)*N58+N59</f>
+        <f t="shared" ref="M59:M66" si="21">M58+(F58-E58)*N58+N59</f>
         <v>2600000</v>
       </c>
       <c r="N59" s="1">
         <v>400000</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q59" s="1">
-        <f t="shared" si="17"/>
-        <v>54</v>
-      </c>
-      <c r="R59" s="1">
-        <f t="shared" si="18"/>
-        <v>54</v>
-      </c>
-      <c r="S59" s="1">
+        <v>97</v>
+      </c>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1">
         <f t="shared" si="19"/>
-        <v>54</v>
-      </c>
-      <c r="T59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1" t="e">
         <f t="shared" si="20"/>
-        <v>54</v>
-      </c>
-      <c r="U59" s="1">
-        <f t="shared" si="21"/>
-        <v>54</v>
-      </c>
-      <c r="V59" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="W59" s="7"/>
-      <c r="X59" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y59" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA59" s="1">
-        <v>3</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
       <c r="AB59" s="1">
         <v>3</v>
       </c>
       <c r="AC59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>3</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C60" s="1">
         <v>604</v>
       </c>
@@ -4564,13 +5009,13 @@
         <v>49</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J60" s="1">
         <v>6</v>
@@ -4582,327 +5027,259 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>7000000</v>
       </c>
       <c r="N60" s="1">
         <v>800000</v>
       </c>
       <c r="O60" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="W60" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C61" s="1">
+        <v>605</v>
+      </c>
+      <c r="D61" s="1">
+        <v>6</v>
+      </c>
+      <c r="E61" s="1">
+        <v>50</v>
+      </c>
+      <c r="F61" s="1">
+        <v>79</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J61" s="1">
+        <v>6</v>
+      </c>
+      <c r="K61" s="1">
+        <v>41</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="21"/>
+        <v>23800000</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1">
+        <f t="shared" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="W61" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC61" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C62" s="1">
+        <v>606</v>
+      </c>
+      <c r="D62" s="1">
+        <v>6</v>
+      </c>
+      <c r="E62" s="1">
+        <v>80</v>
+      </c>
+      <c r="F62" s="1">
+        <v>95</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J62" s="1">
+        <v>6</v>
+      </c>
+      <c r="K62" s="1">
+        <v>70</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="21"/>
+        <v>73400000</v>
+      </c>
+      <c r="N62" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1">
+        <f t="shared" si="19"/>
+        <v>52</v>
+      </c>
+      <c r="W62" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X62" s="7"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC62" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C63" s="1">
+        <v>607</v>
+      </c>
+      <c r="D63" s="1">
+        <v>6</v>
+      </c>
+      <c r="E63" s="1">
+        <v>96</v>
+      </c>
+      <c r="F63" s="1">
+        <v>120</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J63" s="1">
+        <v>6</v>
+      </c>
+      <c r="K63" s="1">
         <v>86</v>
       </c>
-      <c r="P60" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q60" s="1">
-        <f t="shared" si="17"/>
-        <v>84</v>
-      </c>
-      <c r="R60" s="1">
-        <f t="shared" si="18"/>
-        <v>84</v>
-      </c>
-      <c r="S60" s="1">
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="21"/>
+        <v>124600000</v>
+      </c>
+      <c r="N63" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1">
         <f t="shared" si="19"/>
         <v>84</v>
       </c>
-      <c r="T60" s="1">
+      <c r="W63" s="1" t="e">
         <f t="shared" si="20"/>
-        <v>84</v>
-      </c>
-      <c r="U60" s="1">
-        <f t="shared" si="21"/>
-        <v>84</v>
-      </c>
-      <c r="V60" s="1">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="W60" s="7"/>
-      <c r="X60" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y60" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA60" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C61" s="1">
-        <v>605</v>
-      </c>
-      <c r="D61" s="1">
-        <v>6</v>
-      </c>
-      <c r="E61" s="1">
-        <v>50</v>
-      </c>
-      <c r="F61" s="1">
-        <v>79</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J61" s="1">
-        <v>6</v>
-      </c>
-      <c r="K61" s="1">
-        <v>41</v>
-      </c>
-      <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="1">
-        <f t="shared" si="23"/>
-        <v>23800000</v>
-      </c>
-      <c r="N61" s="2">
-        <v>1600000</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q61" s="1">
-        <f t="shared" si="17"/>
-        <v>145</v>
-      </c>
-      <c r="R61" s="1">
-        <f t="shared" si="18"/>
-        <v>145</v>
-      </c>
-      <c r="S61" s="1">
-        <f t="shared" si="19"/>
-        <v>145</v>
-      </c>
-      <c r="T61" s="1">
-        <f t="shared" si="20"/>
-        <v>145</v>
-      </c>
-      <c r="U61" s="1">
-        <f t="shared" si="21"/>
-        <v>145</v>
-      </c>
-      <c r="V61" s="1">
-        <f t="shared" si="22"/>
-        <v>21</v>
-      </c>
-      <c r="W61" s="7"/>
-      <c r="X61" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y61" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z61" s="1">
-        <v>4</v>
-      </c>
-      <c r="AA61" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB61" s="1">
-        <v>4</v>
-      </c>
-      <c r="AC61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C62" s="1">
-        <v>606</v>
-      </c>
-      <c r="D62" s="1">
-        <v>6</v>
-      </c>
-      <c r="E62" s="1">
-        <v>80</v>
-      </c>
-      <c r="F62" s="1">
-        <v>95</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="J62" s="1">
-        <v>6</v>
-      </c>
-      <c r="K62" s="1">
-        <v>70</v>
-      </c>
-      <c r="L62" s="1">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1">
-        <f t="shared" si="23"/>
-        <v>73400000</v>
-      </c>
-      <c r="N62" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q62" s="1">
-        <f t="shared" si="17"/>
-        <v>301</v>
-      </c>
-      <c r="R62" s="1">
-        <f t="shared" si="18"/>
-        <v>301</v>
-      </c>
-      <c r="S62" s="1">
-        <f t="shared" si="19"/>
-        <v>301</v>
-      </c>
-      <c r="T62" s="1">
-        <f t="shared" si="20"/>
-        <v>301</v>
-      </c>
-      <c r="U62" s="1">
-        <f t="shared" si="21"/>
-        <v>301</v>
-      </c>
-      <c r="V62" s="1">
-        <f t="shared" si="22"/>
-        <v>52</v>
-      </c>
-      <c r="W62" s="7"/>
-      <c r="X62" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y62" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z62" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA62" s="1">
-        <v>40</v>
-      </c>
-      <c r="AB62" s="1">
-        <v>40</v>
-      </c>
-      <c r="AC62" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C63" s="1">
-        <v>607</v>
-      </c>
-      <c r="D63" s="1">
-        <v>6</v>
-      </c>
-      <c r="E63" s="1">
-        <v>96</v>
-      </c>
-      <c r="F63" s="1">
-        <v>120</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="J63" s="1">
-        <v>6</v>
-      </c>
-      <c r="K63" s="1">
-        <v>86</v>
-      </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="23"/>
-        <v>124600000</v>
-      </c>
-      <c r="N63" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q63" s="1">
-        <f t="shared" si="17"/>
-        <v>941</v>
-      </c>
-      <c r="R63" s="1">
-        <f t="shared" si="18"/>
-        <v>941</v>
-      </c>
-      <c r="S63" s="1">
-        <f t="shared" si="19"/>
-        <v>941</v>
-      </c>
-      <c r="T63" s="1">
-        <f t="shared" si="20"/>
-        <v>941</v>
-      </c>
-      <c r="U63" s="1">
-        <f t="shared" si="21"/>
-        <v>941</v>
-      </c>
-      <c r="V63" s="1">
-        <f t="shared" si="22"/>
-        <v>84</v>
-      </c>
-      <c r="W63" s="7"/>
-      <c r="X63" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y63" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z63" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA63" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
       <c r="AB63" s="1">
         <v>40</v>
       </c>
       <c r="AC63" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD63" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C64" s="1">
         <v>608</v>
       </c>
@@ -4916,13 +5293,13 @@
         <v>150</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J64" s="1">
         <v>6</v>
@@ -4934,63 +5311,46 @@
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>207400000</v>
       </c>
       <c r="N64" s="2">
         <v>6000000</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q64" s="1">
-        <f t="shared" si="17"/>
-        <v>1941</v>
-      </c>
-      <c r="R64" s="1">
-        <f t="shared" si="18"/>
-        <v>1941</v>
-      </c>
-      <c r="S64" s="1">
+        <v>97</v>
+      </c>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1">
         <f t="shared" si="19"/>
-        <v>1941</v>
-      </c>
-      <c r="T64" s="1">
+        <v>134</v>
+      </c>
+      <c r="W64" s="1" t="e">
         <f t="shared" si="20"/>
-        <v>1941</v>
-      </c>
-      <c r="U64" s="1">
-        <f t="shared" si="21"/>
-        <v>1941</v>
-      </c>
-      <c r="V64" s="1">
-        <f t="shared" si="22"/>
-        <v>134</v>
-      </c>
-      <c r="W64" s="7"/>
-      <c r="X64" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y64" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z64" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA64" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X64" s="7"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
       <c r="AB64" s="1">
         <v>40</v>
       </c>
       <c r="AC64" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD64" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C65" s="1">
         <v>609</v>
       </c>
@@ -5001,16 +5361,16 @@
         <v>151</v>
       </c>
       <c r="F65" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J65" s="1">
         <v>6</v>
@@ -5022,74 +5382,117 @@
         <v>1</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>397400000</v>
       </c>
       <c r="N65" s="1">
         <v>16000000</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q65" s="1">
-        <f t="shared" si="17"/>
-        <v>3141</v>
-      </c>
-      <c r="R65" s="1">
-        <f t="shared" si="18"/>
-        <v>3141</v>
-      </c>
-      <c r="S65" s="1">
+        <v>97</v>
+      </c>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1">
         <f t="shared" si="19"/>
-        <v>3141</v>
-      </c>
-      <c r="T65" s="1">
+        <v>194</v>
+      </c>
+      <c r="W65" s="1" t="e">
         <f t="shared" si="20"/>
-        <v>3141</v>
-      </c>
-      <c r="U65" s="1">
-        <f t="shared" si="21"/>
-        <v>3141</v>
-      </c>
-      <c r="V65" s="1">
-        <f t="shared" si="22"/>
-        <v>194</v>
-      </c>
-      <c r="W65" s="7"/>
-      <c r="X65" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y65" s="1">
-        <v>40</v>
-      </c>
-      <c r="Z65" s="1">
-        <v>40</v>
-      </c>
-      <c r="AA65" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X65" s="7"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
       <c r="AB65" s="1">
         <v>40</v>
       </c>
       <c r="AC65" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD65" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="7:23">
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="W66" s="7"/>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="7:23">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C66" s="1">
+        <v>610</v>
+      </c>
+      <c r="D66" s="1">
+        <v>6</v>
+      </c>
+      <c r="E66" s="1">
+        <v>231</v>
+      </c>
+      <c r="F66" s="1">
+        <v>300</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J66" s="1">
+        <v>6</v>
+      </c>
+      <c r="K66" s="1">
+        <v>221</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="21"/>
+        <v>1693400000</v>
+      </c>
+      <c r="N66" s="1">
+        <v>32000000</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1">
+        <f t="shared" si="19"/>
+        <v>354</v>
+      </c>
+      <c r="W66" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X66" s="7"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC66" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -5098,9 +5501,9 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="W67" s="7"/>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X67" s="7"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -5109,9 +5512,9 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="W68" s="7"/>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X68" s="7"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C69" s="1">
         <v>701</v>
       </c>
@@ -5125,13 +5528,13 @@
         <v>9</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -5149,11 +5552,11 @@
         <v>80000</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="W69" s="7"/>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>116</v>
+      </c>
+      <c r="X69" s="7"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C70" s="1">
         <v>702</v>
       </c>
@@ -5167,13 +5570,13 @@
         <v>19</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J70" s="1">
         <v>7</v>
@@ -5191,14 +5594,14 @@
         <v>300000</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="W70" s="7"/>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>118</v>
+      </c>
+      <c r="X70" s="7"/>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C71" s="1">
         <v>703</v>
       </c>
@@ -5212,13 +5615,13 @@
         <v>29</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J71" s="1">
         <v>7</v>
@@ -5230,21 +5633,21 @@
         <v>1</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" ref="M71:M76" si="24">M70+(F70-E70)*N70+N71</f>
+        <f t="shared" ref="M71:M77" si="22">M70+(F70-E70)*N70+N71</f>
         <v>4100000</v>
       </c>
       <c r="N71" s="1">
         <v>600000</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="W71" s="7"/>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>118</v>
+      </c>
+      <c r="X71" s="7"/>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C72" s="1">
         <v>704</v>
       </c>
@@ -5258,13 +5661,13 @@
         <v>49</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J72" s="1">
         <v>7</v>
@@ -5276,21 +5679,21 @@
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>10500000</v>
       </c>
       <c r="N72" s="1">
         <v>1000000</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="W72" s="7"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>118</v>
+      </c>
+      <c r="X72" s="7"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C73" s="1">
         <v>705</v>
       </c>
@@ -5304,13 +5707,13 @@
         <v>79</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" s="1">
         <v>7</v>
@@ -5322,21 +5725,21 @@
         <v>1</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>31500000</v>
       </c>
       <c r="N73" s="1">
         <v>2000000</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="W73" s="7"/>
-    </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>118</v>
+      </c>
+      <c r="X73" s="7"/>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C74" s="1">
         <v>706</v>
       </c>
@@ -5350,13 +5753,13 @@
         <v>120</v>
       </c>
       <c r="G74" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I74" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="J74" s="1">
         <v>7</v>
@@ -5368,21 +5771,21 @@
         <v>0</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>93500000</v>
       </c>
       <c r="N74" s="1">
         <v>4000000</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="W74" s="7"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>121</v>
+      </c>
+      <c r="X74" s="7"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C75" s="1">
         <v>707</v>
       </c>
@@ -5396,13 +5799,13 @@
         <v>150</v>
       </c>
       <c r="G75" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I75" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="J75" s="1">
         <v>7</v>
@@ -5414,21 +5817,21 @@
         <v>0</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>260500000</v>
       </c>
       <c r="N75" s="1">
         <v>7000000</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="W75" s="7"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>121</v>
+      </c>
+      <c r="X75" s="7"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C76" s="1">
         <v>708</v>
       </c>
@@ -5439,16 +5842,16 @@
         <v>151</v>
       </c>
       <c r="F76" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J76" s="1">
         <v>7</v>
@@ -5460,29 +5863,71 @@
         <v>0</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>481500000</v>
       </c>
       <c r="N76" s="1">
         <v>18000000</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="W76" s="7"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="8:23">
-      <c r="H77" s="5"/>
-      <c r="W77" s="7"/>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="8:23">
+        <v>121</v>
+      </c>
+      <c r="X76" s="7"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C77" s="1">
+        <v>709</v>
+      </c>
+      <c r="D77" s="1">
+        <v>7</v>
+      </c>
+      <c r="E77" s="1">
+        <v>231</v>
+      </c>
+      <c r="F77" s="1">
+        <v>300</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J77" s="1">
+        <v>7</v>
+      </c>
+      <c r="K77" s="1">
+        <v>70</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="22"/>
+        <v>1939500000</v>
+      </c>
+      <c r="N77" s="1">
+        <v>36000000</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X77" s="7"/>
+    </row>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="8:24">
       <c r="H78" s="5"/>
-      <c r="W78" s="7"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="X78" s="7"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C79" s="1">
         <v>801</v>
       </c>
@@ -5496,13 +5941,13 @@
         <v>9</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J79" s="1">
         <v>0</v>
@@ -5520,7 +5965,7 @@
         <v>200000</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="Q79" s="1">
         <v>15</v>
@@ -5540,10 +5985,10 @@
       <c r="V79" s="1">
         <v>0</v>
       </c>
-      <c r="W79" s="7"/>
-      <c r="X79" s="1">
-        <v>2</v>
-      </c>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+      <c r="X79" s="7"/>
       <c r="Y79" s="1">
         <v>2</v>
       </c>
@@ -5557,10 +6002,13 @@
         <v>2</v>
       </c>
       <c r="AC79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>2</v>
+      </c>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C80" s="1">
         <v>802</v>
       </c>
@@ -5574,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J80" s="1">
         <v>8</v>
@@ -5598,39 +6046,40 @@
         <v>500000</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" ref="Q80:Q86" si="25">Q79+(F79-E79)*X79+X80</f>
+        <f t="shared" ref="Q80:Q87" si="23">Q79+(F79-E79)*Y79+Y80</f>
         <v>33</v>
       </c>
       <c r="R80" s="1">
-        <f t="shared" ref="R80:R86" si="26">R79+(F79-E79)*Y79+Y80</f>
+        <f t="shared" ref="R80:R87" si="24">R79+(F79-E79)*Z79+Z80</f>
         <v>33</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" ref="S80:S86" si="27">S79+(F79-E79)*Z79+Z80</f>
+        <f t="shared" ref="S80:S87" si="25">S79+(F79-E79)*AA79+AA80</f>
         <v>33</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" ref="T80:T86" si="28">T79+(F79-E79)*AA79+AA80</f>
+        <f t="shared" ref="T80:T87" si="26">T79+(F79-E79)*AB79+AB80</f>
         <v>33</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" ref="U80:U86" si="29">U79+(F79-E79)*AB79+AB80</f>
+        <f t="shared" ref="U80:U87" si="27">U79+(F79-E79)*AC79+AC80</f>
         <v>33</v>
       </c>
       <c r="V80" s="1">
-        <f t="shared" ref="V80:V86" si="30">V79+(F79-E79)*AC79+AC80</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="7"/>
-      <c r="X80" s="1">
-        <v>2</v>
-      </c>
+        <f t="shared" ref="V80:V87" si="28">V79+(F79-E79)*AD79+AD80</f>
+        <v>0</v>
+      </c>
+      <c r="W80" s="1" t="e">
+        <f t="shared" ref="W80:W87" si="29">W79+(G79-F79)*AE79+AE80</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X80" s="7"/>
       <c r="Y80" s="1">
         <v>2</v>
       </c>
@@ -5644,10 +6093,13 @@
         <v>2</v>
       </c>
       <c r="AC80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>2</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C81" s="1">
         <v>803</v>
       </c>
@@ -5661,13 +6113,13 @@
         <v>29</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J81" s="1">
         <v>8</v>
@@ -5679,46 +6131,47 @@
         <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" ref="M81:M86" si="31">M80+(F80-E80)*N80+N81</f>
+        <f t="shared" ref="M81:M87" si="30">M80+(F80-E80)*N80+N81</f>
         <v>7500000</v>
       </c>
       <c r="N81" s="1">
         <v>1000000</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q81" s="1">
+        <f t="shared" si="23"/>
+        <v>54</v>
+      </c>
+      <c r="R81" s="1">
+        <f t="shared" si="24"/>
+        <v>54</v>
+      </c>
+      <c r="S81" s="1">
         <f t="shared" si="25"/>
         <v>54</v>
       </c>
-      <c r="R81" s="1">
+      <c r="T81" s="1">
         <f t="shared" si="26"/>
         <v>54</v>
       </c>
-      <c r="S81" s="1">
+      <c r="U81" s="1">
         <f t="shared" si="27"/>
         <v>54</v>
       </c>
-      <c r="T81" s="1">
+      <c r="V81" s="1">
         <f t="shared" si="28"/>
-        <v>54</v>
-      </c>
-      <c r="U81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>54</v>
-      </c>
-      <c r="V81" s="1">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="W81" s="7"/>
-      <c r="X81" s="1">
-        <v>3</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X81" s="7"/>
       <c r="Y81" s="1">
         <v>3</v>
       </c>
@@ -5732,10 +6185,13 @@
         <v>3</v>
       </c>
       <c r="AC81" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>3</v>
+      </c>
+      <c r="AD81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C82" s="1">
         <v>804</v>
       </c>
@@ -5749,13 +6205,13 @@
         <v>49</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J82" s="1">
         <v>8</v>
@@ -5767,46 +6223,47 @@
         <v>1</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>18500000</v>
       </c>
       <c r="N82" s="1">
         <v>2000000</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q82" s="1">
+        <f t="shared" si="23"/>
+        <v>84</v>
+      </c>
+      <c r="R82" s="1">
+        <f t="shared" si="24"/>
+        <v>84</v>
+      </c>
+      <c r="S82" s="1">
         <f t="shared" si="25"/>
         <v>84</v>
       </c>
-      <c r="R82" s="1">
+      <c r="T82" s="1">
         <f t="shared" si="26"/>
         <v>84</v>
       </c>
-      <c r="S82" s="1">
+      <c r="U82" s="1">
         <f t="shared" si="27"/>
         <v>84</v>
       </c>
-      <c r="T82" s="1">
+      <c r="V82" s="1">
         <f t="shared" si="28"/>
-        <v>84</v>
-      </c>
-      <c r="U82" s="1">
+        <v>1</v>
+      </c>
+      <c r="W82" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>84</v>
-      </c>
-      <c r="V82" s="1">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="W82" s="7"/>
-      <c r="X82" s="1">
-        <v>3</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X82" s="7"/>
       <c r="Y82" s="1">
         <v>3</v>
       </c>
@@ -5820,10 +6277,13 @@
         <v>3</v>
       </c>
       <c r="AC82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>3</v>
+      </c>
+      <c r="AD82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C83" s="1">
         <v>805</v>
       </c>
@@ -5837,13 +6297,13 @@
         <v>79</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" s="1">
         <v>8</v>
@@ -5855,46 +6315,47 @@
         <v>1</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>60500000</v>
       </c>
       <c r="N83" s="1">
         <v>4000000</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q83" s="1">
+        <f t="shared" si="23"/>
+        <v>145</v>
+      </c>
+      <c r="R83" s="1">
+        <f t="shared" si="24"/>
+        <v>145</v>
+      </c>
+      <c r="S83" s="1">
         <f t="shared" si="25"/>
         <v>145</v>
       </c>
-      <c r="R83" s="1">
+      <c r="T83" s="1">
         <f t="shared" si="26"/>
         <v>145</v>
       </c>
-      <c r="S83" s="1">
+      <c r="U83" s="1">
         <f t="shared" si="27"/>
         <v>145</v>
       </c>
-      <c r="T83" s="1">
+      <c r="V83" s="1">
         <f t="shared" si="28"/>
-        <v>145</v>
-      </c>
-      <c r="U83" s="1">
+        <v>21</v>
+      </c>
+      <c r="W83" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>145</v>
-      </c>
-      <c r="V83" s="1">
-        <f t="shared" si="30"/>
-        <v>21</v>
-      </c>
-      <c r="W83" s="7"/>
-      <c r="X83" s="1">
-        <v>4</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X83" s="7"/>
       <c r="Y83" s="1">
         <v>4</v>
       </c>
@@ -5908,10 +6369,13 @@
         <v>4</v>
       </c>
       <c r="AC83" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:29">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C84" s="1">
         <v>806</v>
       </c>
@@ -5925,13 +6389,13 @@
         <v>120</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J84" s="1">
         <v>8</v>
@@ -5943,46 +6407,47 @@
         <v>1</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>182500000</v>
       </c>
       <c r="N84" s="1">
         <v>6000000</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q84" s="1">
+        <f t="shared" si="23"/>
+        <v>301</v>
+      </c>
+      <c r="R84" s="1">
+        <f t="shared" si="24"/>
+        <v>301</v>
+      </c>
+      <c r="S84" s="1">
         <f t="shared" si="25"/>
         <v>301</v>
       </c>
-      <c r="R84" s="1">
+      <c r="T84" s="1">
         <f t="shared" si="26"/>
         <v>301</v>
       </c>
-      <c r="S84" s="1">
+      <c r="U84" s="1">
         <f t="shared" si="27"/>
         <v>301</v>
       </c>
-      <c r="T84" s="1">
+      <c r="V84" s="1">
         <f t="shared" si="28"/>
-        <v>301</v>
-      </c>
-      <c r="U84" s="1">
+        <v>52</v>
+      </c>
+      <c r="W84" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>301</v>
-      </c>
-      <c r="V84" s="1">
-        <f t="shared" si="30"/>
-        <v>52</v>
-      </c>
-      <c r="W84" s="7"/>
-      <c r="X84" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X84" s="7"/>
       <c r="Y84" s="1">
         <v>40</v>
       </c>
@@ -5996,10 +6461,13 @@
         <v>40</v>
       </c>
       <c r="AC84" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD84" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C85" s="1">
         <v>807</v>
       </c>
@@ -6013,13 +6481,13 @@
         <v>150</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J85" s="1">
         <v>8</v>
@@ -6031,46 +6499,47 @@
         <v>1</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>430500000</v>
       </c>
       <c r="N85" s="1">
         <v>8000000</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q85" s="1">
+        <f t="shared" si="23"/>
+        <v>1941</v>
+      </c>
+      <c r="R85" s="1">
+        <f t="shared" si="24"/>
+        <v>1941</v>
+      </c>
+      <c r="S85" s="1">
         <f t="shared" si="25"/>
         <v>1941</v>
       </c>
-      <c r="R85" s="1">
+      <c r="T85" s="1">
         <f t="shared" si="26"/>
         <v>1941</v>
       </c>
-      <c r="S85" s="1">
+      <c r="U85" s="1">
         <f t="shared" si="27"/>
         <v>1941</v>
       </c>
-      <c r="T85" s="1">
+      <c r="V85" s="1">
         <f t="shared" si="28"/>
-        <v>1941</v>
-      </c>
-      <c r="U85" s="1">
+        <v>134</v>
+      </c>
+      <c r="W85" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>1941</v>
-      </c>
-      <c r="V85" s="1">
-        <f t="shared" si="30"/>
-        <v>134</v>
-      </c>
-      <c r="W85" s="7"/>
-      <c r="X85" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X85" s="7"/>
       <c r="Y85" s="1">
         <v>40</v>
       </c>
@@ -6084,10 +6553,13 @@
         <v>40</v>
       </c>
       <c r="AC85" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD85" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C86" s="1">
         <v>808</v>
       </c>
@@ -6098,16 +6570,16 @@
         <v>151</v>
       </c>
       <c r="F86" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J86" s="1">
         <v>8</v>
@@ -6119,46 +6591,47 @@
         <v>1</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>682500000</v>
       </c>
       <c r="N86" s="1">
         <v>20000000</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Q86" s="1">
+        <f t="shared" si="23"/>
+        <v>3141</v>
+      </c>
+      <c r="R86" s="1">
+        <f t="shared" si="24"/>
+        <v>3141</v>
+      </c>
+      <c r="S86" s="1">
         <f t="shared" si="25"/>
         <v>3141</v>
       </c>
-      <c r="R86" s="1">
+      <c r="T86" s="1">
         <f t="shared" si="26"/>
         <v>3141</v>
       </c>
-      <c r="S86" s="1">
+      <c r="U86" s="1">
         <f t="shared" si="27"/>
         <v>3141</v>
       </c>
-      <c r="T86" s="1">
+      <c r="V86" s="1">
         <f t="shared" si="28"/>
-        <v>3141</v>
-      </c>
-      <c r="U86" s="1">
+        <v>194</v>
+      </c>
+      <c r="W86" s="1" t="e">
         <f t="shared" si="29"/>
-        <v>3141</v>
-      </c>
-      <c r="V86" s="1">
-        <f t="shared" si="30"/>
-        <v>194</v>
-      </c>
-      <c r="W86" s="7"/>
-      <c r="X86" s="1">
-        <v>40</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X86" s="7"/>
       <c r="Y86" s="1">
         <v>40</v>
       </c>
@@ -6172,31 +6645,123 @@
         <v>40</v>
       </c>
       <c r="AC86" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD86" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W87" s="7"/>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C87" s="1">
+        <v>809</v>
+      </c>
+      <c r="D87" s="1">
+        <v>8</v>
+      </c>
+      <c r="E87" s="1">
+        <v>231</v>
+      </c>
+      <c r="F87" s="1">
+        <v>300</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J87" s="1">
+        <v>8</v>
+      </c>
+      <c r="K87" s="1">
+        <v>221</v>
+      </c>
+      <c r="L87" s="1">
+        <v>1</v>
+      </c>
+      <c r="M87" s="1">
+        <f t="shared" si="30"/>
+        <v>2302500000</v>
+      </c>
+      <c r="N87" s="1">
+        <v>40000000</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P87" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q87" s="1">
+        <f t="shared" si="23"/>
+        <v>6341</v>
+      </c>
+      <c r="R87" s="1">
+        <f t="shared" si="24"/>
+        <v>6341</v>
+      </c>
+      <c r="S87" s="1">
+        <f t="shared" si="25"/>
+        <v>6341</v>
+      </c>
+      <c r="T87" s="1">
+        <f t="shared" si="26"/>
+        <v>6341</v>
+      </c>
+      <c r="U87" s="1">
+        <f t="shared" si="27"/>
+        <v>6341</v>
+      </c>
+      <c r="V87" s="1">
+        <f t="shared" si="28"/>
+        <v>354</v>
+      </c>
+      <c r="W87" s="1" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z87" s="1">
+        <v>40</v>
+      </c>
+      <c r="AA87" s="1">
+        <v>40</v>
+      </c>
+      <c r="AB87" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC87" s="1">
+        <v>40</v>
+      </c>
+      <c r="AD87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A88" s="2"/>
-      <c r="W88" s="7"/>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X88" s="7"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A89" s="2"/>
-      <c r="W89" s="7"/>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X89" s="7"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A90" s="2"/>
-      <c r="W90" s="7"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W91" s="7"/>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="23:23">
-      <c r="W92" s="7"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X90" s="7"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X91" s="7"/>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="24:24">
+      <c r="X92" s="7"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -6205,9 +6770,9 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="W93" s="7"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X93" s="7"/>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -6216,9 +6781,9 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="W94" s="7"/>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X94" s="7"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -6227,9 +6792,9 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="W95" s="7"/>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X95" s="7"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -6238,9 +6803,9 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="W96" s="7"/>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X96" s="7"/>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -6249,9 +6814,9 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-      <c r="W97" s="7"/>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X97" s="7"/>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -6260,9 +6825,9 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="W98" s="7"/>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X98" s="7"/>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -6271,9 +6836,9 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="W99" s="7"/>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X99" s="7"/>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -6282,9 +6847,9 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="W100" s="7"/>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="7:23">
+      <c r="X100" s="7"/>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="7:24">
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -6293,9 +6858,9 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-      <c r="W101" s="7"/>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X101" s="7"/>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -6305,9 +6870,9 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="W102" s="7"/>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X102" s="7"/>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -6317,9 +6882,9 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="W103" s="7"/>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X103" s="7"/>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -6329,9 +6894,9 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="W104" s="7"/>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X104" s="7"/>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -6341,9 +6906,9 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="W105" s="7"/>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X105" s="7"/>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -6353,9 +6918,9 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-      <c r="W106" s="7"/>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X106" s="7"/>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -6365,9 +6930,9 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="W107" s="7"/>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X107" s="7"/>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -6377,9 +6942,9 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="W108" s="7"/>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X108" s="7"/>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -6389,9 +6954,9 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="W109" s="7"/>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="2:23">
+      <c r="X109" s="7"/>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="2:24">
       <c r="B110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -6401,9 +6966,9 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-      <c r="W110" s="7"/>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X110" s="7"/>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="G111" s="2"/>
@@ -6414,9 +6979,9 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-      <c r="W111" s="7"/>
-    </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X111" s="7"/>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="G112" s="2"/>
@@ -6427,9 +6992,9 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-      <c r="W112" s="7"/>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X112" s="7"/>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="G113" s="2"/>
@@ -6440,9 +7005,9 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="W113" s="7"/>
-    </row>
-    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X113" s="7"/>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="G114" s="2"/>
@@ -6453,9 +7018,9 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-      <c r="W114" s="7"/>
-    </row>
-    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X114" s="7"/>
+    </row>
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="G115" s="2"/>
@@ -6466,9 +7031,9 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="W115" s="7"/>
-    </row>
-    <row r="116" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X115" s="7"/>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="G116" s="2"/>
@@ -6479,9 +7044,9 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="W116" s="7"/>
-    </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X116" s="7"/>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="G117" s="2"/>
@@ -6492,9 +7057,9 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="W117" s="7"/>
-    </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X117" s="7"/>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="G118" s="2"/>
@@ -6505,9 +7070,9 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="W118" s="7"/>
-    </row>
-    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X118" s="7"/>
+    </row>
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="G119" s="2"/>
@@ -6518,9 +7083,9 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-      <c r="W119" s="7"/>
-    </row>
-    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X119" s="7"/>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="G120" s="2"/>
@@ -6531,9 +7096,9 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-      <c r="W120" s="7"/>
-    </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X120" s="7"/>
+    </row>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="G121" s="2"/>
@@ -6544,9 +7109,9 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-      <c r="W121" s="7"/>
-    </row>
-    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X121" s="7"/>
+    </row>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="G122" s="2"/>
@@ -6557,9 +7122,9 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="W122" s="7"/>
-    </row>
-    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X122" s="7"/>
+    </row>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="G123" s="2"/>
@@ -6570,9 +7135,9 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-      <c r="W123" s="7"/>
-    </row>
-    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X123" s="7"/>
+    </row>
+    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="G124" s="2"/>
@@ -6583,9 +7148,9 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-      <c r="W124" s="7"/>
-    </row>
-    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X124" s="7"/>
+    </row>
+    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="G125" s="2"/>
@@ -6596,9 +7161,9 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-      <c r="W125" s="7"/>
-    </row>
-    <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X125" s="7"/>
+    </row>
+    <row r="126" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="G126" s="2"/>
@@ -6609,9 +7174,9 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-      <c r="W126" s="7"/>
-    </row>
-    <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X126" s="7"/>
+    </row>
+    <row r="127" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="G127" s="2"/>
@@ -6622,9 +7187,9 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-      <c r="W127" s="7"/>
-    </row>
-    <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X127" s="7"/>
+    </row>
+    <row r="128" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="G128" s="2"/>
@@ -6635,9 +7200,9 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-      <c r="W128" s="7"/>
-    </row>
-    <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X128" s="7"/>
+    </row>
+    <row r="129" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="G129" s="2"/>
@@ -6648,9 +7213,9 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="W129" s="7"/>
-    </row>
-    <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X129" s="7"/>
+    </row>
+    <row r="130" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="G130" s="2"/>
@@ -6661,9 +7226,9 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="W130" s="7"/>
-    </row>
-    <row r="131" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X130" s="7"/>
+    </row>
+    <row r="131" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="G131" s="2"/>
@@ -6674,9 +7239,9 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-      <c r="W131" s="7"/>
-    </row>
-    <row r="132" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X131" s="7"/>
+    </row>
+    <row r="132" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="G132" s="2"/>
@@ -6687,9 +7252,9 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="W132" s="7"/>
-    </row>
-    <row r="133" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X132" s="7"/>
+    </row>
+    <row r="133" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="G133" s="2"/>
@@ -6700,9 +7265,9 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="W133" s="7"/>
-    </row>
-    <row r="134" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X133" s="7"/>
+    </row>
+    <row r="134" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="G134" s="2"/>
@@ -6713,9 +7278,9 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-      <c r="W134" s="7"/>
-    </row>
-    <row r="135" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X134" s="7"/>
+    </row>
+    <row r="135" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="G135" s="2"/>
@@ -6726,9 +7291,9 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="W135" s="7"/>
-    </row>
-    <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X135" s="7"/>
+    </row>
+    <row r="136" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="G136" s="2"/>
@@ -6739,9 +7304,9 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-      <c r="W136" s="7"/>
-    </row>
-    <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X136" s="7"/>
+    </row>
+    <row r="137" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="G137" s="2"/>
@@ -6752,9 +7317,9 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-      <c r="W137" s="7"/>
-    </row>
-    <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X137" s="7"/>
+    </row>
+    <row r="138" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="G138" s="2"/>
@@ -6765,9 +7330,9 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-      <c r="W138" s="7"/>
-    </row>
-    <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X138" s="7"/>
+    </row>
+    <row r="139" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="G139" s="2"/>
@@ -6778,9 +7343,9 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-      <c r="W139" s="7"/>
-    </row>
-    <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X139" s="7"/>
+    </row>
+    <row r="140" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="G140" s="2"/>
@@ -6791,9 +7356,9 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="W140" s="7"/>
-    </row>
-    <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X140" s="7"/>
+    </row>
+    <row r="141" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="G141" s="2"/>
@@ -6804,9 +7369,9 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-      <c r="W141" s="7"/>
-    </row>
-    <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X141" s="7"/>
+    </row>
+    <row r="142" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="G142" s="2"/>
@@ -6817,9 +7382,9 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-      <c r="W142" s="7"/>
-    </row>
-    <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X142" s="7"/>
+    </row>
+    <row r="143" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="G143" s="2"/>
@@ -6830,9 +7395,9 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-      <c r="W143" s="7"/>
-    </row>
-    <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X143" s="7"/>
+    </row>
+    <row r="144" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="G144" s="2"/>
@@ -6843,9 +7408,9 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-      <c r="W144" s="7"/>
-    </row>
-    <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X144" s="7"/>
+    </row>
+    <row r="145" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="G145" s="2"/>
@@ -6856,9 +7421,9 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="W145" s="7"/>
-    </row>
-    <row r="146" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X145" s="7"/>
+    </row>
+    <row r="146" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="G146" s="2"/>
@@ -6869,9 +7434,9 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-      <c r="W146" s="7"/>
-    </row>
-    <row r="147" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X146" s="7"/>
+    </row>
+    <row r="147" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="G147" s="2"/>
@@ -6882,9 +7447,9 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-      <c r="W147" s="7"/>
-    </row>
-    <row r="148" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X147" s="7"/>
+    </row>
+    <row r="148" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="G148" s="2"/>
@@ -6895,9 +7460,9 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-      <c r="W148" s="7"/>
-    </row>
-    <row r="149" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X148" s="7"/>
+    </row>
+    <row r="149" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="G149" s="2"/>
@@ -6908,9 +7473,9 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-      <c r="W149" s="7"/>
-    </row>
-    <row r="150" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X149" s="7"/>
+    </row>
+    <row r="150" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="G150" s="2"/>
@@ -6921,9 +7486,9 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-      <c r="W150" s="7"/>
-    </row>
-    <row r="151" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X150" s="7"/>
+    </row>
+    <row r="151" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="G151" s="2"/>
@@ -6934,9 +7499,9 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-      <c r="W151" s="7"/>
-    </row>
-    <row r="152" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X151" s="7"/>
+    </row>
+    <row r="152" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="G152" s="2"/>
@@ -6947,9 +7512,9 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-      <c r="W152" s="7"/>
-    </row>
-    <row r="153" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X152" s="7"/>
+    </row>
+    <row r="153" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="G153" s="2"/>
@@ -6960,9 +7525,9 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-      <c r="W153" s="7"/>
-    </row>
-    <row r="154" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X153" s="7"/>
+    </row>
+    <row r="154" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="G154" s="2"/>
@@ -6973,9 +7538,9 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="W154" s="7"/>
-    </row>
-    <row r="155" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X154" s="7"/>
+    </row>
+    <row r="155" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="G155" s="2"/>
@@ -6986,9 +7551,9 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-      <c r="W155" s="7"/>
-    </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X155" s="7"/>
+    </row>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="G159" s="2"/>
@@ -6999,9 +7564,9 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="W159" s="7"/>
-    </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X159" s="7"/>
+    </row>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="G160" s="2"/>
@@ -7012,9 +7577,9 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-      <c r="W160" s="7"/>
-    </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X160" s="7"/>
+    </row>
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="G161" s="2"/>
@@ -7025,9 +7590,9 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-      <c r="W161" s="7"/>
-    </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X161" s="7"/>
+    </row>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="G162" s="2"/>
@@ -7038,9 +7603,9 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-      <c r="W162" s="7"/>
-    </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X162" s="7"/>
+    </row>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="G163" s="2"/>
@@ -7051,9 +7616,9 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-      <c r="W163" s="7"/>
-    </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X163" s="7"/>
+    </row>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="G164" s="2"/>
@@ -7064,9 +7629,9 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-      <c r="W164" s="7"/>
-    </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X164" s="7"/>
+    </row>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="G165" s="2"/>
@@ -7077,9 +7642,9 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-      <c r="W165" s="7"/>
-    </row>
-    <row r="166" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X165" s="7"/>
+    </row>
+    <row r="166" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="G166" s="2"/>
@@ -7090,9 +7655,9 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="W166" s="7"/>
-    </row>
-    <row r="167" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X166" s="7"/>
+    </row>
+    <row r="167" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="G167" s="2"/>
@@ -7103,9 +7668,9 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-      <c r="W167" s="7"/>
-    </row>
-    <row r="168" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X167" s="7"/>
+    </row>
+    <row r="168" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="G168" s="2"/>
@@ -7116,9 +7681,9 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-      <c r="W168" s="7"/>
-    </row>
-    <row r="169" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X168" s="7"/>
+    </row>
+    <row r="169" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="G169" s="2"/>
@@ -7129,9 +7694,9 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-      <c r="W169" s="7"/>
-    </row>
-    <row r="170" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X169" s="7"/>
+    </row>
+    <row r="170" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="G170" s="2"/>
@@ -7142,9 +7707,9 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="W170" s="7"/>
-    </row>
-    <row r="171" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X170" s="7"/>
+    </row>
+    <row r="171" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="G171" s="2"/>
@@ -7155,9 +7720,9 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-      <c r="W171" s="7"/>
-    </row>
-    <row r="172" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X171" s="7"/>
+    </row>
+    <row r="172" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="G172" s="2"/>
@@ -7168,9 +7733,9 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-      <c r="W172" s="7"/>
-    </row>
-    <row r="173" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X172" s="7"/>
+    </row>
+    <row r="173" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="G173" s="2"/>
@@ -7181,9 +7746,9 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-      <c r="W173" s="7"/>
-    </row>
-    <row r="174" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X173" s="7"/>
+    </row>
+    <row r="174" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="G174" s="2"/>
@@ -7194,9 +7759,9 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="W174" s="7"/>
-    </row>
-    <row r="175" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X174" s="7"/>
+    </row>
+    <row r="175" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="G175" s="2"/>
@@ -7207,9 +7772,9 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-      <c r="W175" s="7"/>
-    </row>
-    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X175" s="7"/>
+    </row>
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="G176" s="2"/>
@@ -7220,9 +7785,9 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-      <c r="W176" s="7"/>
-    </row>
-    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X176" s="7"/>
+    </row>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="G177" s="2"/>
@@ -7233,9 +7798,9 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-      <c r="W177" s="7"/>
-    </row>
-    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X177" s="7"/>
+    </row>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="G178" s="2"/>
@@ -7246,7 +7811,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-      <c r="W178" s="7"/>
+      <c r="X178" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SoulRingAttrConfig.xlsx
+++ b/Excel/SoulRingAttrConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1076,9 +1081,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1542,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1581,17 +1586,17 @@
       <c r="N3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="X3" s="7"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="X3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
@@ -1630,17 +1635,17 @@
       <c r="N4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="X4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="X4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
@@ -1679,17 +1684,17 @@
       <c r="N5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="X5" s="7"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="X5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C6" s="1">
         <v>101</v>
       </c>
@@ -1750,7 +1755,7 @@
       <c r="W6" s="1">
         <v>0</v>
       </c>
-      <c r="X6" s="7"/>
+      <c r="X6" s="6"/>
       <c r="Y6" s="1">
         <v>1</v>
       </c>
@@ -1773,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C7" s="1">
         <v>102</v>
       </c>
@@ -1845,7 +1850,7 @@
         <f t="shared" ref="W7:W15" si="6">W6+(F6-E6)*AE6+AE7</f>
         <v>0</v>
       </c>
-      <c r="X7" s="7"/>
+      <c r="X7" s="6"/>
       <c r="Y7" s="1">
         <v>2</v>
       </c>
@@ -1868,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C8" s="1">
         <v>103</v>
       </c>
@@ -1940,7 +1945,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X8" s="7"/>
+      <c r="X8" s="6"/>
       <c r="Y8" s="1">
         <v>2</v>
       </c>
@@ -1963,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C9" s="1">
         <v>104</v>
       </c>
@@ -2035,7 +2040,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X9" s="7"/>
+      <c r="X9" s="6"/>
       <c r="Y9" s="1">
         <v>3</v>
       </c>
@@ -2058,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C10" s="1">
         <v>105</v>
       </c>
@@ -2130,7 +2135,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X10" s="7"/>
+      <c r="X10" s="6"/>
       <c r="Y10" s="1">
         <v>4</v>
       </c>
@@ -2153,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C11" s="1">
         <v>106</v>
       </c>
@@ -2225,7 +2230,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X11" s="7"/>
+      <c r="X11" s="6"/>
       <c r="Y11" s="1">
         <v>40</v>
       </c>
@@ -2248,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C12" s="1">
         <v>107</v>
       </c>
@@ -2320,7 +2325,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X12" s="7"/>
+      <c r="X12" s="6"/>
       <c r="Y12" s="1">
         <v>40</v>
       </c>
@@ -2343,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C13" s="1">
         <v>108</v>
       </c>
@@ -2415,7 +2420,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X13" s="7"/>
+      <c r="X13" s="6"/>
       <c r="Y13" s="1">
         <v>40</v>
       </c>
@@ -2438,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C14" s="1">
         <v>109</v>
       </c>
@@ -2510,7 +2515,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="X14" s="7"/>
+      <c r="X14" s="6"/>
       <c r="Y14" s="1">
         <v>80</v>
       </c>
@@ -2533,7 +2538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="C15" s="1">
         <v>110</v>
       </c>
@@ -2544,7 +2549,7 @@
         <v>231</v>
       </c>
       <c r="F15" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>44</v>
@@ -2605,7 +2610,7 @@
         <f t="shared" si="6"/>
         <v>164</v>
       </c>
-      <c r="X15" s="7"/>
+      <c r="X15" s="6"/>
       <c r="Y15" s="1">
         <v>80</v>
       </c>
@@ -2628,8 +2633,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X16" s="7"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:31">
+      <c r="X16" s="6"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C17" s="1">
@@ -2671,7 +2676,7 @@
       <c r="O17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="X17" s="7"/>
+      <c r="X17" s="6"/>
       <c r="AB17" s="1">
         <v>1</v>
       </c>
@@ -2725,7 +2730,7 @@
       <c r="P18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X18" s="7"/>
+      <c r="X18" s="6"/>
       <c r="AB18" s="1">
         <v>2</v>
       </c>
@@ -2780,7 +2785,7 @@
       <c r="P19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X19" s="7"/>
+      <c r="X19" s="6"/>
       <c r="AB19" s="1">
         <v>2</v>
       </c>
@@ -2835,7 +2840,7 @@
       <c r="P20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X20" s="7"/>
+      <c r="X20" s="6"/>
       <c r="AB20" s="1">
         <v>3</v>
       </c>
@@ -2890,7 +2895,7 @@
       <c r="P21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X21" s="7"/>
+      <c r="X21" s="6"/>
       <c r="AB21" s="1">
         <v>4</v>
       </c>
@@ -2945,7 +2950,7 @@
       <c r="P22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X22" s="7"/>
+      <c r="X22" s="6"/>
       <c r="AB22" s="1">
         <v>4</v>
       </c>
@@ -3000,7 +3005,7 @@
       <c r="P23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X23" s="7"/>
+      <c r="X23" s="6"/>
       <c r="AB23" s="1">
         <v>4</v>
       </c>
@@ -3055,7 +3060,7 @@
       <c r="P24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X24" s="7"/>
+      <c r="X24" s="6"/>
       <c r="AB24" s="1">
         <v>4</v>
       </c>
@@ -3077,7 +3082,7 @@
         <v>231</v>
       </c>
       <c r="F25" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>53</v>
@@ -3110,7 +3115,7 @@
       <c r="P25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X25" s="7"/>
+      <c r="X25" s="6"/>
       <c r="AB25" s="1">
         <v>4</v>
       </c>
@@ -3121,10 +3126,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X26" s="7"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="X26" s="6"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C27" s="1">
         <v>301</v>
       </c>
@@ -3164,9 +3169,9 @@
       <c r="O27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="X27" s="7"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C28" s="1">
         <v>302</v>
       </c>
@@ -3209,9 +3214,9 @@
       <c r="P28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X28" s="7"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C29" s="1">
         <v>303</v>
       </c>
@@ -3255,9 +3260,9 @@
       <c r="P29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X29" s="7"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X29" s="6"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C30" s="1">
         <v>304</v>
       </c>
@@ -3301,9 +3306,9 @@
       <c r="P30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X30" s="7"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C31" s="1">
         <v>305</v>
       </c>
@@ -3347,9 +3352,9 @@
       <c r="P31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X31" s="7"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C32" s="1">
         <v>306</v>
       </c>
@@ -3393,9 +3398,9 @@
       <c r="P32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X32" s="7"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X32" s="6"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C33" s="1">
         <v>307</v>
       </c>
@@ -3439,9 +3444,9 @@
       <c r="P33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X33" s="7"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X33" s="6"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C34" s="1">
         <v>308</v>
       </c>
@@ -3485,9 +3490,9 @@
       <c r="P34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X34" s="7"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X34" s="6"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C35" s="1">
         <v>309</v>
       </c>
@@ -3498,7 +3503,7 @@
         <v>231</v>
       </c>
       <c r="F35" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>60</v>
@@ -3531,12 +3536,12 @@
       <c r="P35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X35" s="7"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X36" s="7"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="X36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C37" s="1">
         <v>401</v>
       </c>
@@ -3576,9 +3581,9 @@
       <c r="O37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X37" s="7"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C38" s="1">
         <v>402</v>
       </c>
@@ -3621,9 +3626,9 @@
       <c r="P38" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X38" s="7"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C39" s="1">
         <v>403</v>
       </c>
@@ -3667,9 +3672,9 @@
       <c r="P39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X39" s="7"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C40" s="1">
         <v>404</v>
       </c>
@@ -3713,9 +3718,9 @@
       <c r="P40" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X40" s="7"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C41" s="1">
         <v>405</v>
       </c>
@@ -3759,9 +3764,9 @@
       <c r="P41" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X41" s="7"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C42" s="1">
         <v>406</v>
       </c>
@@ -3805,9 +3810,9 @@
       <c r="P42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X42" s="7"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C43" s="1">
         <v>407</v>
       </c>
@@ -3851,9 +3856,9 @@
       <c r="P43" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X43" s="7"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C44" s="1">
         <v>408</v>
       </c>
@@ -3897,9 +3902,9 @@
       <c r="P44" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X44" s="7"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C45" s="1">
         <v>409</v>
       </c>
@@ -3910,7 +3915,7 @@
         <v>231</v>
       </c>
       <c r="F45" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>67</v>
@@ -3943,10 +3948,10 @@
       <c r="P45" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X45" s="7"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X46" s="7"/>
+      <c r="X45" s="6"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="X46" s="6"/>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C47" s="1">
@@ -4009,7 +4014,7 @@
       <c r="W47" s="1">
         <v>0</v>
       </c>
-      <c r="X47" s="7"/>
+      <c r="X47" s="6"/>
       <c r="Y47" s="1">
         <v>2</v>
       </c>
@@ -4103,7 +4108,7 @@
         <f t="shared" ref="W48:W55" si="17">W47+(F47-E47)*AE47+AE48</f>
         <v>0</v>
       </c>
-      <c r="X48" s="7"/>
+      <c r="X48" s="6"/>
       <c r="Y48" s="1">
         <v>2</v>
       </c>
@@ -4198,7 +4203,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X49" s="7"/>
+      <c r="X49" s="6"/>
       <c r="Y49" s="1">
         <v>3</v>
       </c>
@@ -4293,7 +4298,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X50" s="7"/>
+      <c r="X50" s="6"/>
       <c r="Y50" s="1">
         <v>3</v>
       </c>
@@ -4388,7 +4393,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X51" s="7"/>
+      <c r="X51" s="6"/>
       <c r="Y51" s="1">
         <v>4</v>
       </c>
@@ -4483,7 +4488,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X52" s="7"/>
+      <c r="X52" s="6"/>
       <c r="Y52" s="1">
         <v>40</v>
       </c>
@@ -4578,7 +4583,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X53" s="7"/>
+      <c r="X53" s="6"/>
       <c r="Y53" s="1">
         <v>40</v>
       </c>
@@ -4673,7 +4678,7 @@
         <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="X54" s="7"/>
+      <c r="X54" s="6"/>
       <c r="Y54" s="1">
         <v>80</v>
       </c>
@@ -4707,7 +4712,7 @@
         <v>231</v>
       </c>
       <c r="F55" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>88</v>
@@ -4768,7 +4773,7 @@
         <f t="shared" si="17"/>
         <v>164</v>
       </c>
-      <c r="X55" s="7"/>
+      <c r="X55" s="6"/>
       <c r="Y55" s="1">
         <v>80</v>
       </c>
@@ -4791,10 +4796,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X56" s="7"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="X56" s="6"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C57" s="1">
         <v>601</v>
       </c>
@@ -4840,7 +4845,7 @@
       <c r="W57" s="1">
         <v>0</v>
       </c>
-      <c r="X57" s="7"/>
+      <c r="X57" s="6"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
@@ -4854,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C58" s="1">
         <v>602</v>
       </c>
@@ -4910,7 +4915,7 @@
         <f t="shared" ref="W58:W66" si="20">W57+(G57-F57)*AE57+AE58</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X58" s="7"/>
+      <c r="X58" s="6"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
@@ -4924,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C59" s="1">
         <v>603</v>
       </c>
@@ -4981,7 +4986,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X59" s="7"/>
+      <c r="X59" s="6"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
@@ -4995,7 +5000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C60" s="1">
         <v>604</v>
       </c>
@@ -5052,7 +5057,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X60" s="7"/>
+      <c r="X60" s="6"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
@@ -5066,7 +5071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C61" s="1">
         <v>605</v>
       </c>
@@ -5123,7 +5128,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X61" s="7"/>
+      <c r="X61" s="6"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
@@ -5137,7 +5142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C62" s="1">
         <v>606</v>
       </c>
@@ -5194,7 +5199,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X62" s="7"/>
+      <c r="X62" s="6"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
@@ -5208,7 +5213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C63" s="1">
         <v>607</v>
       </c>
@@ -5265,7 +5270,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X63" s="7"/>
+      <c r="X63" s="6"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
@@ -5279,7 +5284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C64" s="1">
         <v>608</v>
       </c>
@@ -5336,7 +5341,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X64" s="7"/>
+      <c r="X64" s="6"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
@@ -5407,7 +5412,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X65" s="7"/>
+      <c r="X65" s="6"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
@@ -5432,7 +5437,7 @@
         <v>231</v>
       </c>
       <c r="F66" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>112</v>
@@ -5478,7 +5483,7 @@
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X66" s="7"/>
+      <c r="X66" s="6"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
@@ -5492,7 +5497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="7:24">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -5501,9 +5506,9 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="X67" s="7"/>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X67" s="6"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -5512,9 +5517,9 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="X68" s="7"/>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X68" s="6"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C69" s="1">
         <v>701</v>
       </c>
@@ -5554,9 +5559,9 @@
       <c r="O69" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="X69" s="7"/>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X69" s="6"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C70" s="1">
         <v>702</v>
       </c>
@@ -5599,9 +5604,9 @@
       <c r="P70" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="X70" s="7"/>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X70" s="6"/>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C71" s="1">
         <v>703</v>
       </c>
@@ -5645,9 +5650,9 @@
       <c r="P71" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="X71" s="7"/>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X71" s="6"/>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C72" s="1">
         <v>704</v>
       </c>
@@ -5691,9 +5696,9 @@
       <c r="P72" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="X72" s="7"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X72" s="6"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C73" s="1">
         <v>705</v>
       </c>
@@ -5737,9 +5742,9 @@
       <c r="P73" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="X73" s="7"/>
-    </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X73" s="6"/>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C74" s="1">
         <v>706</v>
       </c>
@@ -5783,9 +5788,9 @@
       <c r="P74" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X74" s="7"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X74" s="6"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C75" s="1">
         <v>707</v>
       </c>
@@ -5829,9 +5834,9 @@
       <c r="P75" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X75" s="7"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X75" s="6"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C76" s="1">
         <v>708</v>
       </c>
@@ -5875,9 +5880,9 @@
       <c r="P76" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X76" s="7"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:24">
+      <c r="X76" s="6"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C77" s="1">
         <v>709</v>
       </c>
@@ -5888,7 +5893,7 @@
         <v>231</v>
       </c>
       <c r="F77" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>123</v>
@@ -5921,11 +5926,11 @@
       <c r="P77" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X77" s="7"/>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="8:24">
-      <c r="H78" s="5"/>
-      <c r="X78" s="7"/>
+      <c r="X77" s="6"/>
+    </row>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:30">
+      <c r="H78" s="7"/>
+      <c r="X78" s="6"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:30">
       <c r="C79" s="1">
@@ -5988,7 +5993,7 @@
       <c r="W79" s="1">
         <v>0</v>
       </c>
-      <c r="X79" s="7"/>
+      <c r="X79" s="6"/>
       <c r="Y79" s="1">
         <v>2</v>
       </c>
@@ -6079,7 +6084,7 @@
         <f t="shared" ref="W80:W87" si="29">W79+(G79-F79)*AE79+AE80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X80" s="7"/>
+      <c r="X80" s="6"/>
       <c r="Y80" s="1">
         <v>2</v>
       </c>
@@ -6099,7 +6104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C81" s="1">
         <v>803</v>
       </c>
@@ -6171,7 +6176,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X81" s="7"/>
+      <c r="X81" s="6"/>
       <c r="Y81" s="1">
         <v>3</v>
       </c>
@@ -6191,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C82" s="1">
         <v>804</v>
       </c>
@@ -6263,7 +6268,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X82" s="7"/>
+      <c r="X82" s="6"/>
       <c r="Y82" s="1">
         <v>3</v>
       </c>
@@ -6283,7 +6288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C83" s="1">
         <v>805</v>
       </c>
@@ -6355,7 +6360,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X83" s="7"/>
+      <c r="X83" s="6"/>
       <c r="Y83" s="1">
         <v>4</v>
       </c>
@@ -6375,7 +6380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C84" s="1">
         <v>806</v>
       </c>
@@ -6447,7 +6452,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X84" s="7"/>
+      <c r="X84" s="6"/>
       <c r="Y84" s="1">
         <v>40</v>
       </c>
@@ -6467,7 +6472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C85" s="1">
         <v>807</v>
       </c>
@@ -6539,7 +6544,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X85" s="7"/>
+      <c r="X85" s="6"/>
       <c r="Y85" s="1">
         <v>40</v>
       </c>
@@ -6559,7 +6564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C86" s="1">
         <v>808</v>
       </c>
@@ -6631,7 +6636,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X86" s="7"/>
+      <c r="X86" s="6"/>
       <c r="Y86" s="1">
         <v>40</v>
       </c>
@@ -6651,7 +6656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="C87" s="1">
         <v>809</v>
       </c>
@@ -6662,7 +6667,7 @@
         <v>231</v>
       </c>
       <c r="F87" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>129</v>
@@ -6723,7 +6728,7 @@
         <f t="shared" si="29"/>
         <v>#VALUE!</v>
       </c>
-      <c r="X87" s="7"/>
+      <c r="X87" s="6"/>
       <c r="Y87" s="1">
         <v>40</v>
       </c>
@@ -6743,25 +6748,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A88" s="2"/>
-      <c r="X88" s="7"/>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="X88" s="6"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A89" s="2"/>
-      <c r="X89" s="7"/>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="X89" s="6"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A90" s="2"/>
-      <c r="X90" s="7"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X91" s="7"/>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="24:24">
-      <c r="X92" s="7"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X90" s="6"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:30">
+      <c r="X91" s="6"/>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:30">
+      <c r="X92" s="6"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -6770,9 +6775,9 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="X93" s="7"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X93" s="6"/>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -6781,9 +6786,9 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="X94" s="7"/>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X94" s="6"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -6792,9 +6797,9 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="X95" s="7"/>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X95" s="6"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -6803,9 +6808,9 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="X96" s="7"/>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X96" s="6"/>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -6814,9 +6819,9 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-      <c r="X97" s="7"/>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X97" s="6"/>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -6825,9 +6830,9 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="X98" s="7"/>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X98" s="6"/>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -6836,9 +6841,9 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="X99" s="7"/>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X99" s="6"/>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -6847,9 +6852,9 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="X100" s="7"/>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="7:24">
+      <c r="X100" s="6"/>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -6858,9 +6863,9 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-      <c r="X101" s="7"/>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X101" s="6"/>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -6870,9 +6875,9 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="X102" s="7"/>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X102" s="6"/>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -6882,9 +6887,9 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="X103" s="7"/>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X103" s="6"/>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -6894,9 +6899,9 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="X104" s="7"/>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X104" s="6"/>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -6906,9 +6911,9 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="X105" s="7"/>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X105" s="6"/>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -6918,9 +6923,9 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-      <c r="X106" s="7"/>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X106" s="6"/>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -6930,9 +6935,9 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="X107" s="7"/>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X107" s="6"/>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -6942,9 +6947,9 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="X108" s="7"/>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X108" s="6"/>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -6954,9 +6959,9 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="X109" s="7"/>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="2:24">
+      <c r="X109" s="6"/>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="B110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -6966,7 +6971,7 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-      <c r="X110" s="7"/>
+      <c r="X110" s="6"/>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A111" s="2"/>
@@ -6979,7 +6984,7 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-      <c r="X111" s="7"/>
+      <c r="X111" s="6"/>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A112" s="2"/>
@@ -6992,7 +6997,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-      <c r="X112" s="7"/>
+      <c r="X112" s="6"/>
     </row>
     <row r="113" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A113" s="2"/>
@@ -7005,7 +7010,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="X113" s="7"/>
+      <c r="X113" s="6"/>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A114" s="2"/>
@@ -7018,7 +7023,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-      <c r="X114" s="7"/>
+      <c r="X114" s="6"/>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A115" s="2"/>
@@ -7031,7 +7036,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="X115" s="7"/>
+      <c r="X115" s="6"/>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A116" s="2"/>
@@ -7044,7 +7049,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="X116" s="7"/>
+      <c r="X116" s="6"/>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A117" s="2"/>
@@ -7057,7 +7062,7 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="X117" s="7"/>
+      <c r="X117" s="6"/>
     </row>
     <row r="118" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A118" s="2"/>
@@ -7070,7 +7075,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="X118" s="7"/>
+      <c r="X118" s="6"/>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A119" s="2"/>
@@ -7083,7 +7088,7 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-      <c r="X119" s="7"/>
+      <c r="X119" s="6"/>
     </row>
     <row r="120" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A120" s="2"/>
@@ -7096,7 +7101,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-      <c r="X120" s="7"/>
+      <c r="X120" s="6"/>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A121" s="2"/>
@@ -7109,7 +7114,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-      <c r="X121" s="7"/>
+      <c r="X121" s="6"/>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A122" s="2"/>
@@ -7122,7 +7127,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="X122" s="7"/>
+      <c r="X122" s="6"/>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A123" s="2"/>
@@ -7135,7 +7140,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-      <c r="X123" s="7"/>
+      <c r="X123" s="6"/>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A124" s="2"/>
@@ -7148,7 +7153,7 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-      <c r="X124" s="7"/>
+      <c r="X124" s="6"/>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A125" s="2"/>
@@ -7161,7 +7166,7 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-      <c r="X125" s="7"/>
+      <c r="X125" s="6"/>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A126" s="2"/>
@@ -7174,7 +7179,7 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-      <c r="X126" s="7"/>
+      <c r="X126" s="6"/>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A127" s="2"/>
@@ -7187,7 +7192,7 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-      <c r="X127" s="7"/>
+      <c r="X127" s="6"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A128" s="2"/>
@@ -7200,7 +7205,7 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-      <c r="X128" s="7"/>
+      <c r="X128" s="6"/>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A129" s="2"/>
@@ -7213,7 +7218,7 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="X129" s="7"/>
+      <c r="X129" s="6"/>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A130" s="2"/>
@@ -7226,7 +7231,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="X130" s="7"/>
+      <c r="X130" s="6"/>
     </row>
     <row r="131" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A131" s="2"/>
@@ -7239,7 +7244,7 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-      <c r="X131" s="7"/>
+      <c r="X131" s="6"/>
     </row>
     <row r="132" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A132" s="2"/>
@@ -7252,7 +7257,7 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="X132" s="7"/>
+      <c r="X132" s="6"/>
     </row>
     <row r="133" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A133" s="2"/>
@@ -7265,7 +7270,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="X133" s="7"/>
+      <c r="X133" s="6"/>
     </row>
     <row r="134" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A134" s="2"/>
@@ -7278,7 +7283,7 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-      <c r="X134" s="7"/>
+      <c r="X134" s="6"/>
     </row>
     <row r="135" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A135" s="2"/>
@@ -7291,7 +7296,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="X135" s="7"/>
+      <c r="X135" s="6"/>
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A136" s="2"/>
@@ -7304,7 +7309,7 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-      <c r="X136" s="7"/>
+      <c r="X136" s="6"/>
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A137" s="2"/>
@@ -7317,7 +7322,7 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-      <c r="X137" s="7"/>
+      <c r="X137" s="6"/>
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A138" s="2"/>
@@ -7330,7 +7335,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-      <c r="X138" s="7"/>
+      <c r="X138" s="6"/>
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A139" s="2"/>
@@ -7343,7 +7348,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-      <c r="X139" s="7"/>
+      <c r="X139" s="6"/>
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A140" s="2"/>
@@ -7356,7 +7361,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="X140" s="7"/>
+      <c r="X140" s="6"/>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A141" s="2"/>
@@ -7369,7 +7374,7 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-      <c r="X141" s="7"/>
+      <c r="X141" s="6"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A142" s="2"/>
@@ -7382,7 +7387,7 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-      <c r="X142" s="7"/>
+      <c r="X142" s="6"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A143" s="2"/>
@@ -7395,7 +7400,7 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-      <c r="X143" s="7"/>
+      <c r="X143" s="6"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A144" s="2"/>
@@ -7408,7 +7413,7 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-      <c r="X144" s="7"/>
+      <c r="X144" s="6"/>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A145" s="2"/>
@@ -7421,7 +7426,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="X145" s="7"/>
+      <c r="X145" s="6"/>
     </row>
     <row r="146" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A146" s="2"/>
@@ -7434,7 +7439,7 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-      <c r="X146" s="7"/>
+      <c r="X146" s="6"/>
     </row>
     <row r="147" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A147" s="2"/>
@@ -7447,7 +7452,7 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-      <c r="X147" s="7"/>
+      <c r="X147" s="6"/>
     </row>
     <row r="148" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A148" s="2"/>
@@ -7460,7 +7465,7 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-      <c r="X148" s="7"/>
+      <c r="X148" s="6"/>
     </row>
     <row r="149" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A149" s="2"/>
@@ -7473,7 +7478,7 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-      <c r="X149" s="7"/>
+      <c r="X149" s="6"/>
     </row>
     <row r="150" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A150" s="2"/>
@@ -7486,7 +7491,7 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-      <c r="X150" s="7"/>
+      <c r="X150" s="6"/>
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A151" s="2"/>
@@ -7499,7 +7504,7 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-      <c r="X151" s="7"/>
+      <c r="X151" s="6"/>
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A152" s="2"/>
@@ -7512,7 +7517,7 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-      <c r="X152" s="7"/>
+      <c r="X152" s="6"/>
     </row>
     <row r="153" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A153" s="2"/>
@@ -7525,7 +7530,7 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-      <c r="X153" s="7"/>
+      <c r="X153" s="6"/>
     </row>
     <row r="154" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A154" s="2"/>
@@ -7538,7 +7543,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="X154" s="7"/>
+      <c r="X154" s="6"/>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A155" s="2"/>
@@ -7551,7 +7556,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-      <c r="X155" s="7"/>
+      <c r="X155" s="6"/>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A159" s="2"/>
@@ -7564,7 +7569,7 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="X159" s="7"/>
+      <c r="X159" s="6"/>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A160" s="2"/>
@@ -7577,7 +7582,7 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-      <c r="X160" s="7"/>
+      <c r="X160" s="6"/>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A161" s="2"/>
@@ -7590,7 +7595,7 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-      <c r="X161" s="7"/>
+      <c r="X161" s="6"/>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A162" s="2"/>
@@ -7603,7 +7608,7 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-      <c r="X162" s="7"/>
+      <c r="X162" s="6"/>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A163" s="2"/>
@@ -7616,7 +7621,7 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-      <c r="X163" s="7"/>
+      <c r="X163" s="6"/>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A164" s="2"/>
@@ -7629,7 +7634,7 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-      <c r="X164" s="7"/>
+      <c r="X164" s="6"/>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A165" s="2"/>
@@ -7642,7 +7647,7 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-      <c r="X165" s="7"/>
+      <c r="X165" s="6"/>
     </row>
     <row r="166" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A166" s="2"/>
@@ -7655,7 +7660,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="X166" s="7"/>
+      <c r="X166" s="6"/>
     </row>
     <row r="167" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A167" s="2"/>
@@ -7668,7 +7673,7 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-      <c r="X167" s="7"/>
+      <c r="X167" s="6"/>
     </row>
     <row r="168" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A168" s="2"/>
@@ -7681,7 +7686,7 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-      <c r="X168" s="7"/>
+      <c r="X168" s="6"/>
     </row>
     <row r="169" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A169" s="2"/>
@@ -7694,7 +7699,7 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-      <c r="X169" s="7"/>
+      <c r="X169" s="6"/>
     </row>
     <row r="170" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A170" s="2"/>
@@ -7707,7 +7712,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="X170" s="7"/>
+      <c r="X170" s="6"/>
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A171" s="2"/>
@@ -7720,7 +7725,7 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-      <c r="X171" s="7"/>
+      <c r="X171" s="6"/>
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A172" s="2"/>
@@ -7733,7 +7738,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-      <c r="X172" s="7"/>
+      <c r="X172" s="6"/>
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A173" s="2"/>
@@ -7746,7 +7751,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-      <c r="X173" s="7"/>
+      <c r="X173" s="6"/>
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A174" s="2"/>
@@ -7759,7 +7764,7 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="X174" s="7"/>
+      <c r="X174" s="6"/>
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A175" s="2"/>
@@ -7772,7 +7777,7 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-      <c r="X175" s="7"/>
+      <c r="X175" s="6"/>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A176" s="2"/>
@@ -7785,7 +7790,7 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-      <c r="X176" s="7"/>
+      <c r="X176" s="6"/>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A177" s="2"/>
@@ -7798,7 +7803,7 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-      <c r="X177" s="7"/>
+      <c r="X177" s="6"/>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A178" s="2"/>
@@ -7811,7 +7816,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-      <c r="X178" s="7"/>
+      <c r="X178" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
